--- a/dat/dat-rel.xlsx
+++ b/dat/dat-rel.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="461">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="931" uniqueCount="668">
   <si>
     <t>Timestamp</t>
   </si>
@@ -1211,6 +1211,630 @@
   </si>
   <si>
     <t>data:image/webp;base64,UklGRiwOAABXRUJQVlA4WAoAAAAgAAAAfwAAoAAASUNDUMgBAAAAAAHIAAAAAAQwAABtbnRyUkdCIFhZWiAH4AABAAEAAAAAAABhY3NwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAQAA9tYAAQAAAADTLQAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAlkZXNjAAAA8AAAACRyWFlaAAABFAAAABRnWFlaAAABKAAAABRiWFlaAAABPAAAABR3dHB0AAABUAAAABRyVFJDAAABZAAAAChnVFJDAAABZAAAAChiVFJDAAABZAAAAChjcHJ0AAABjAAAADxtbHVjAAAAAAAAAAEAAAAMZW5VUwAAAAgAAAAcAHMAUgBHAEJYWVogAAAAAAAAb6IAADj1AAADkFhZWiAAAAAAAABimQAAt4UAABjaWFlaIAAAAAAAACSgAAAPhAAAts9YWVogAAAAAAAA9tYAAQAAAADTLXBhcmEAAAAAAAQAAAACZmYAAPKnAAANWQAAE9AAAApbAAAAAAAAAABtbHVjAAAAAAAAAAEAAAAMZW5VUwAAACAAAAAcAEcAbwBvAGcAbABlACAASQBuAGMALgAgADIAMAAxADZWUDggPgwAABBBAJ0BKoAAoQA+oUKbSSYjoqExdQ34wBQJQBh8x0sv1Qzq8noPUBNasci8aHTqJSchthcEgWRVDFLDpuxSQfCvkt9sQdkquPGcu8JK/At9fHOAxV+2I63pCPFh4Q18V1rcrOYuKdVqvbSPouu94WOi5sipvUa3LurvHJI0YEskILAyfQIi5vQW0D2VhFtaot/rfyIkZtiGR1YHjvZi8qFI8JZqYRO7ZSVo+Xh6HYnEBcwjZjiZIIzv6V/tEvXltWaRdKbzpSlcb1oqO79grBZMZT9XDig2rAFB37fZ2QKO60PY+5btxQN72qEY8BT0qzLuoSs+JyLl+PDLAthb4hkN91ql64ClAgd1IllL7FcvkxNIwq33MiC8DrnssyaeGwTolYse1Bx48tf0C0K6MWJaQ1+maRDaKjk6PMnXPGy4ogzx+OOltSsJid3gdgr8LfPIjAhDOlwq5O55h6sR/3LmQr3p9tanu+nseA+KBBMP/i6E0xj3rwAJ7gsAOuSwv9sPUUWDI8LfzY4+WbxJfRUUeZ1if/n+m4Zz0oDYM4CzjIC5HMgY6IJ13XrWYvEqj+XXdXmvS6Sq9k/dw3833BR7HQdK8k9VOMmg7p+pLtK4yvDHUljVbzJa6fGsrmNPkurQ4Rx/agFxNXkKYhkjPe47cTmtPJSvgZU60SG4yTD16WqOJk1WZTcdKGit+THQVgAA/ku+/9HZWpA1udhblO6q3Q/FDXwEWyV0kJaA8nUKRVe9PwKyMXkakRHXP+3zwg9371PY6dORRug+Eyf6vKo1hbUDA9csoq51eXilmYf9WEKaM91NyfOXbpf+tExGa6/8ATF4liGvjYX81kLGTKKelJC0WSYTP/AwNM3bDq2W8jAZuD/FLuCcDsf4kzIVq3HkNL3ypQ3CoRZrkUDlX8/dTEYBLdDXt/eHd2JDJIj5AWZZ+UILVz4VDCgrH1oZAvGbDBEgQzuxa/D1DNO3Uv8HQ7uyTdMBOV0rm5VRJXDAaF5MVkjutYMR55+9DPYhrELBC4+4evTD8c/iG2WRvPxJQ6bkQ6nl3CjS4UyuF790CmTT9i25lkRXkhl9vAz4iqTGiLEwYcQF7ZjXIYjpRhS7BxRaxhYnPMWrJ6+mGEwcbmksI7JaDGudZXs00rKyCbEZU1O6Smq/+qu62qsqwDQDSWtxZRijN7mK/EUmmadFToFjhRxU4WK3HyeWcvomqdwsIBzsxqUnKJSjOzNK4GXvfXabJOrsmHFDF3vil7I/qcnhr6/3mHH+Q9Addj034OvlVVvkPyyhr4FUSTOpjeM93ZPnBKJTMbRtMKxoZ2e/KZFu6Wb89pvZUu5V2RLZdaoAznbVMpm/c1M5a1SsetRZWFAH8GCqBvpA0qGYitz+3FIQswIf4tgMjFG0GV/PPjFPYp6/LD8mZPPV2+Hp9NcyI2XpIG257lXqSNcNCX3vSGZmsVYmAycOdO8UOoaMlw6oFMXGX8S9PaQA7qggRYcIJVabAIB6Lm/QUn3nZSentdb0rvaRmFwX5GefDYKiUwaialLpLW6fPA5PkGG44uxjFBmYhtTJwduHrodXsqx3eV17Ob7btftZxsn6IPg28CpgO0/9bMYjMLrF6P1VH5xkVaZS21fvZxDz5FBAE9wAsD0+eJhRqW69l3uLVYBngrMN8UE2W5RW3ODkVKqFJyIpxPEw1XjCDia5IhDyIGbiQd7ug6hTpnmClUnXc6fPVVmLxBqNrhUSDfo1Ld4YSCGZVgi5Cwstb98jIGUyZaQxJ0/taCxtqQsAHtTVn4Co7sPeNTTFKkJ43Fp/YEOpfHeLwN7mlYZGJlO9e4AYmaXTcM9p1kEVhLylqF/MyS/Y0EIE7KEfrRbThBs0apzCQc+3MS3/ySxU46wqzfmsAERcoRXuCUQtc6L5jPPQasso5e0JegpJs0rxhF20+au5AkT62V+pebOfts5joZqluv+pi7RCmWjYdf6wsMw3nliDqPgbWJq5gZHZr8STBvpL/h3oxZxYPfI9/6FdQTO60P5wKKyA5/muAZKh0T1mXRSAPlt4+tI9FTUhf0BT8EHXQbFRGGRnssdoBAstIqpRRIwnK24wuLLfbK3PHocoCfqKN3nKdUsceXPWJVBQKT6iWAnpOL2WUa+3JtUNfBcg6Bor/+9idf4ZfBxqqnmQSJIuwKk4A1omUHFyikgkXZ1sim8MNSQdyUsn46fyHZ/7Ki7QLl67NRFm0fZsejbtj6/0zewD9+RGP3/JNMVsLvNEB0cT3p+HJfkFmU0p/UBvQViVHPL/dMr1y8ra/FiYY+gZlObznfWT4Glxd651naCHM4Rw7UiCom7aIdQzw7ppoiFfWEEnTMB0K2oub1ikyl0MZX8MrNrlz+rayU5TxH8XoO6nfFj/QRG0Gq1cbF5CwSQn5OJyAICY8EdQxFYcG4sfeY+68bBE7Dun+zsmaF13q5nAwSRHa7OtQrOachjsep/GrvY3063UlvY9sGRAGh6RrfUTzlHv4IZq1dkFjAoBJTuoakSpF36AwQLpAOKoa9I1kEooy2YWb3qyUM5twHsjZ28QyNpqXeQoholt7kQmRMqFi6oWaUE1qvXQZTrQXVJDEr8kZGtC5HzxSH9AGNwt70DqtgJ3lKHYXqnxxLixAJr15ZU9s361Nc2i5+8fL8iabrRzNDDrB8QoSNcPUjcOdx+wKDMAMIe0X9Ng8pMjQ0RXMguo/Q7fpX/aaDiuYhh1KxkdqLlmtcIXyljd8HwIeqGiR4sBeFFkreMZCNrxICCRYARbX18Xzy1V6QwRhKxpbEuwIHTpxrtpb9T9BgZU3rUjCLqmyddp+gc+DC2rf3hURAcQA3TsdxODmUtjHsqyOKsmQJptPorkO2+9q/aBojCDlF7cb7dIwwgDfWtm/uES2YZxmmwwVJRA2ldZBlJ63f12ytkKDiWxaqk7PNRlolhExjwaFTUvWK2HswTDJhmdOwYZlqmQ2Wmetazq5ozDxMQmQ2yfAapToabKsESTeRfBZ63cu+H78TlJPU2UyPGRJ+M5og8NdVZy6FSzF+9xkr9d+O7JAK11VOu/DC55CazJILbma4O5NpHGUQznBpqJOlGSM/6ZdbAN+KStRg68PhRHaUMb5SGqECEy/U/7CH3kRp7phWqjaqENA5xmFY05ZhVDouG6FoMJpkA3DDGVwZ/Rt+6aowWuAj9L06Fx4TDeTZ49vROtMxNs7jm3HpstlKRRYdSpR0L5yv6L/aYwb+V2V5mhb8UXK41O0clQ3z0ZEFVcDugktJhMjsXY86kBhwzrTnnk5UedaFXU0rDPqTX789M34bM/p/a5b8tICBgRFxVpMzVTMdmSe/2A2ljj1SScC+Qz/SGCHawhsT0xPpNvcQBGkPmHYJs3rz07TjtrQCj+Lgf0WsZjk4Z7IoiHBKGwZHdxseBiSn1WONW48Jcw9ntxu3B/QQeoqbyXw/flzs3atfPkIrB1QnAF0mMQsieXuAaZ8REHokqZTIWjNFNASN3Dn1Fsjfc53aXM++a8Uyzzt2QL9P+OK6AVjfmKl2Jb4mNPkrRwP7qz+ntI0kKhmabQNrTJsh1vhOfy1vj+LamhbGOmfu4X4Cp6TfEEQRAZTCaRwn/d0+RtcFXgysz4pYKx7QuQ3a7rRPBqAfnj1TlgtsyiaZZVcW7AhAKJpBLb8ZZYq0ekcTnUbiAAihJFoKLFdDz26T44uHn4j2NAKaCk6/xyMiHOAkvXH+9j9a6KXcFZ7vuMcbjkZDk719lh+A7f08mDWP4GIWgPGYVJt1li2idqkzYbxXAA94iE4q6WO1nBWBoKfTUaX6h2A2b8jwB4wFBuPycPn1IKzHxbc5jnosy75jWuOty/a22sN63P6SpdulvTGG0XqbAtICxHQmG5naTdcryOKRVgz6zX4cEvqSAbIThnjyvbS2x/gjBCwj+podrwwJDIwNlhf7mh4wWRjAVAFjZP+JJGPbgNoIe60LYTvGdojYtM5IgaRrbT/0XQXA7yyTWTj53aM1sRJWY7gXUzNBDAklONn4Sk/qfZQ9+KDbWglZNKAaIAAZk8xHVA9iUu66GGu/1xSuWphcAXHElO3Nt2dW1Doi8nXzsQSNfGdM8FNeyjzNWwd9hXMAEDNsw+zYfcK/F37j5APjzxnSLyUnWaaaLWuwzCzgmzCZdgpwGzdgAA</t>
+  </si>
+  <si>
+    <t>MONJE</t>
+  </si>
+  <si>
+    <t>Eduardo Andrés</t>
+  </si>
+  <si>
+    <t>24-05-1969</t>
+  </si>
+  <si>
+    <t>Argentina</t>
+  </si>
+  <si>
+    <t>09-11-1996</t>
+  </si>
+  <si>
+    <t>28-12-2000</t>
+  </si>
+  <si>
+    <t>+5491135435054</t>
+  </si>
+  <si>
+    <t>eduardo.hsmi@yahoo.com.ar</t>
+  </si>
+  <si>
+    <t>data:image/webp;base64,UklGRhQLAABXRUJQVlA4WAoAAAAgAAAAfwAAmwAASUNDUMgBAAAAAAHIAAAAAAQwAABtbnRyUkdCIFhZWiAH4AABAAEAAAAAAABhY3NwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAQAA9tYAAQAAAADTLQAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAlkZXNjAAAA8AAAACRyWFlaAAABFAAAABRnWFlaAAABKAAAABRiWFlaAAABPAAAABR3dHB0AAABUAAAABRyVFJDAAABZAAAAChnVFJDAAABZAAAAChiVFJDAAABZAAAAChjcHJ0AAABjAAAADxtbHVjAAAAAAAAAAEAAAAMZW5VUwAAAAgAAAAcAHMAUgBHAEJYWVogAAAAAAAAb6IAADj1AAADkFhZWiAAAAAAAABimQAAt4UAABjaWFlaIAAAAAAAACSgAAAPhAAAts9YWVogAAAAAAAA9tYAAQAAAADTLXBhcmEAAAAAAAQAAAACZmYAAPKnAAANWQAAE9AAAApbAAAAAAAAAABtbHVjAAAAAAAAAAEAAAAMZW5VUwAAACAAAAAcAEcAbwBvAGcAbABlACAASQBuAGMALgAgADIAMAAxADZWUDggJgkAAFA4AJ0BKoAAnAA+SSCMRCKiIZrKZOwoBISxgGPTHGyfTXOb6485CFgOcI9VarZDZeaQmBsmHlvyMgZWlNksrlM9Z2XMn4RVJL3UAfxxpGrtlT8VvbAIxjJDZtppLBG6WUPQEYLYcwLVjBKUmZU2MgcIa3+GC93mutSK5P8oedfFAz7W8Kg6F0IlCJa64n+uBMCc+Uz75kRGN5LwiE7tOis8Pd/JmLTFmTCiddVltm4PS5ieT/H/t5kU+LeN+2W/5YQWM1BVDP8iUQPkG836ncsXNM+0cwbnAPzo9WRRcr4i7wlJfHoTHhChjhXk+7yOQN6hbin9olRkNDG76VlmUMMJ8D0F+RDff1Saa4m9Lyp3G02fQ8plyLjopTr5khDiJm80bXGH7tk/aMYKAv/U/E8620O2ZKtmhY7ARtaEtSTNtFwRXNIK5nqwwQUiFtA42XdeeTG6bKazBRF/mFSp2tVkITLuVFmVg5ReroOQx6RbXaIVtB2t/QS6V2yodB5oPrmfFNe92YOvuZ6N3651DF6SkDFRM+zgAClCRErgM3etKOT9nsBUb6PM9PlxEPWwviX6o5uDQNnfrj9hGkXRJ+M5gu7SyrAhg2EVAAD+8TkK/8aj99P256Kv/FSfVJ9Umn8e3xhqxvvd+q2ZG2qTf5nS9QTg6q6tDe+VhM9h3WkKCrVVSZ7dda9WE7G08+N9hWrx0WSqJhfmcVBk8ve41jKyGsuO4oIy2klbL4mZJpyZjpWGRVTPuWU5wwgdbYNT2Clyb8e035YREnW+BsNtBTfYmABb7SNb8CpVstzQgvs3unz4p7b6/eOjI4Ha9WC100KJ7KKd9i79lhHwokq9mfvanmCDXg6boc8Azy4k2mMp+mygCmZvr+ynY9UrmYs/DtobIsjb4UFdgfqaAY1qHTt9InYz6b700Xk9lLEF13OiYgmKGfQ8Woq+jZ64wyL50D1K3zZ1fx10UXmleN7/akeM9zJnCdDeK6O2JF0COK1tDQ05qzzocpoC2aIYmX3SgmfqnB0eK1xREXZV5p8bfjdGrQeC5NRsV+zk+R3404VI2dcdI+oTxB64R1N1540OLuhhq8rQp4i5IDo3GTRgknC5aFKsmV9fSJ7Lt1R4/XgGu9nN4zGgKXpJKjdYL08JgjNPjHhurbyoViR4UCdW0I4UWATNnUxASLaJBl6P3fOoGj2dcBGyY9x0DBtg9go4Kb15szUbrcYGQRVunJ59KDN6LlmOD8sPgsyjyxvoDqzV1mlaz60YtLgrhzNghcpRezSdCyYibYDget53aCpUHsckj2max7ZQGyONgowUdaLqGxN/NRzAL9lqtDF//uL7dPFpMijPeZ/GBZpG8kvqGM5jdmTTk0Aw1AJTSSAx69XSnrg9EivGu72D6DHHU/Ib1LFHV4/+++Bn1XRlGSDXAGI61ZFMJRk2qTjpENqUaPUInUmTBj0KovqTPU+t41URsG5esaKi9M5zADllC+QBk0z0HM+61/pnPA2Fk2OXr+bClkp7lZAqBSaqnX7MoAf7FL6CZRQe3rAOqn30mjjdG5i5z4BSnQ8k4TRX8U76wvOh95jW4tqDisp0hhqAQRICiPv6rhBXYdfWXTCZN7qKcs3Xm9Xev2yOks7BrJD46HNDter4/Z5/449MISyJ2L3PVWHsWIQvV0oVIdSWbOXA3M8Lj2j7ttc+Je0jL67OaN3WDpgAvLjcD0VY4RG23z0hzDoKlubb/yjO43DOnfrBfp1cMiWfOPLp5zxkN+t4H2P1EI1lbWDAXu+ADjx4oylOXuUme8RJhNTz0OnM8HSfXRkMYzMv2r5qkZWWzluPCYrYaZWEgEG13K+axiBpJoQgf32IL7T8TWbmdbsnRcBBN9ejUXkCRhdvGwL46OfD7OKx/7aEH/v1YOBKoOZDaWcKCKCKmj1jVtMSpjewCC55Vhm3cS9iyP6sT2u9JreCvA5IZj+gDseBYnhhVZAlMuSZlMsE7fHObrDmP74d5GhP7jpQAj066D5hjaBgeuLzqnSEX7htb4k5yXbURByMRRk/wLQDiqGRWPlqz+N+L6BVv+q2p99kq063G3Uvp7z1zv25ORYA7R6FrB3mRWUCrb9r2FzYD27JB+4+rQ6XB6OakJHzS2mnoJ+T9UjlKXo4c2eftyvUp/NsgV58x53q0wCN4XoVKCjB0pfFNNCOvycfW2cEE59hEjVMMwis3MFmh+ZC8sytKW1qkx5w+cbB1mr34n4/e8BlAx66Sq6HYaBFvfbVw8xm1QNyV6lUHal7lVMIreuWBsDEpfIAvivxlTMYE+42caxz6FyHMFPupckMkiDpNEA2uczRyi+bVSlkBewnY2yXrW4Gch9nbJpo+f0x/f+vFXYmpPrzJRQX8D7Bd5vwh8WS1h2nMeSjwq0o8clSU5hVPcvpSfvuQ+iU9TL6jQNcD94gbdB8KDEvgkoeKbnNwRumR/vJGpuQ6JrNthT/KeUVDIqH8BsgVjiKvTgJr6OOrBotq/UYw5/casdapOWfVLuAdji8ZK0eBVMtuGHgs3G8pIs3SleMV3yN9BTDBwOvShPHrDMXfCl0Va/5ICdPP3F92Uxspc0jeY2NzV9MDok93MESzX7VDO9W01T7ewFPIRlgPprkfuztTTUrNukZmC8IMrwHO/Hg4u2hThjX23HXJes70PJATbPTQmuBKCgADweCamZ2dTxMr2Bh/CwmoT/7sTepZJlvG1voTgsMwkqtLiZdOlzGFH9kaGNFAJZe7N/EhQShl/rRMxIJ/frUGkvwAPXKDIpAUpNQZL9z0eICYmBw8A5t+ozub4uxAbL2r8DUrqQbdtVK1r616/+W5daw61m6U3qWJWlJoKTihula4ow1/ByPCNiNNOw0qSZ/uZnnIHQBDvfu4pLVhYZcTrWkrXTYRq7gZM57katc/Lmy2gkTPc+EUU6C43YVZJd95CDh2UQ3nQeZwTC5mVVITS2fHvFD0CTKnlHI9FH9yMsxacwNyu5Xpc6lHSwEv1HFn4tYsldzUEwtyZc126aNlx8d3UsbbOLPlZft/TivJ4+OFA94HZ4WGQySRRsnczFNI64Q+0oRB9rUS7O0Bd+p86w8rG2jnjhNBynbqyJ1zveWAAAA</t>
+  </si>
+  <si>
+    <t>OCO</t>
+  </si>
+  <si>
+    <t>Arielex Salazar</t>
+  </si>
+  <si>
+    <t>18-07-1977</t>
+  </si>
+  <si>
+    <t>30-05-1999</t>
+  </si>
+  <si>
+    <t>04-10-2008</t>
+  </si>
+  <si>
+    <t>+393280131272</t>
+  </si>
+  <si>
+    <t>ielexo@yahoo.com</t>
+  </si>
+  <si>
+    <t>data:image/webp;base64,UklGRuYLAABXRUJQVlA4WAoAAAAgAAAAfwAAmwAASUNDUMgBAAAAAAHIAAAAAAQwAABtbnRyUkdCIFhZWiAH4AABAAEAAAAAAABhY3NwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAQAA9tYAAQAAAADTLQAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAlkZXNjAAAA8AAAACRyWFlaAAABFAAAABRnWFlaAAABKAAAABRiWFlaAAABPAAAABR3dHB0AAABUAAAABRyVFJDAAABZAAAAChnVFJDAAABZAAAAChiVFJDAAABZAAAAChjcHJ0AAABjAAAADxtbHVjAAAAAAAAAAEAAAAMZW5VUwAAAAgAAAAcAHMAUgBHAEJYWVogAAAAAAAAb6IAADj1AAADkFhZWiAAAAAAAABimQAAt4UAABjaWFlaIAAAAAAAACSgAAAPhAAAts9YWVogAAAAAAAA9tYAAQAAAADTLXBhcmEAAAAAAAQAAAACZmYAAPKnAAANWQAAE9AAAApbAAAAAAAAAABtbHVjAAAAAAAAAAEAAAAMZW5VUwAAACAAAAAcAEcAbwBvAGcAbABlACAASQBuAGMALgAgADIAMAAxADZWUDgg+AkAADA0AJ0BKoAAnAA+SR6LRCKhoRrL3RQoBISxgGLFCazPS/NbybPjPm1uC2Q1+mh3lLtAuvGRDAltQ6nNKvXV3bu77sRcZAc4kw5pA3BnOdHxGhAasz9g8EPvEIjauaGpe+rW/2xFSVl0kZ1x6tU/TMPk407vULlFXyyqn6gg4GFOZHrb8sPjP8nAQvisuxeM7daoH4ZNkqIA755iAikk0DU5HrYpk5BW5Z7/NF6YdZNJKKzbrnprymNRmQrABgs7Vz+qwBrQmKlp2wEo9/OnJ8alOgvVsfcBzhfUvjbQPM5eO/xId8VtMRTm5XjTnfPW9EKniN2vfJp/+7ik2d7DBCpPcahOonOjlaV+qZh5UIq2lAzdbu6GY6DopJ/v8TR0qlW3pAS7IYMrCis9Pspn2aZWPbI4P5rC9ZF7ZynLdDbBxPxuEs69miBCWaySlJ1IVJdMWqL79TKNRqcNBXyptyUdn07/OKOM3MNm5SEHcYkY0Dvp9xcLyaC4daI9ldTLEFgMypcSKm9IW4CdUSPwOOoX1zhKwIbllLATCw8UH1QUJ422Uc8hIEkqAAD+8PeHbv+c/I58jkWf1l6Ad8pFU9c6LPqv0BuRx66l6VHK2KUpdlEiPZX3EJLkyJDA2DWMrp/NAuo7mZvKgwnxAq3um/Bfke4Fzp+K7OuWMv+iaKuvEg30usHmlrfJ2rVTAyHin59XwKLxbxMuHZdsAJhFSkf+wobOpfhAEh9tieFdNrH/u3L6vwQPxiFz/gpP8WHPQIs6YI+WOMctr4Q4HkvuzkwD3Rqs+edcJ5awRMWlny/EBfRrKeSK04QEwBrCef/SVHd8mF+smPbYrAW4euVILIUB39vTWO+xkEwfvuEamiH7hF3a+6IjM4PPiKKvfzgSvgCmfVSLyvha0LFqZyIZAXk+JooLZ3hKEcgNG9nGWSxMmU80Rhq5xZJm86ts+nWeu0IgGPTwrhPwpY3KlMehnb3dyyN8u4cFBqCQJZD/fl+OzQukghfc4lZUg9kQozGI/47Cjr+pWer1ofpRJ4JLloSGso0LA0IYC+1TXIw6zxQRSEgtZ66JKbvEP4P2Elselt6ZMyGTs9ZL1kmKFNKlobyeTZvjlzt5VBMk8Bx/aefghM74Hy10nUlYUPxAsS1lnk7Ropsc7nslAPvztBWrGfKnyE16b3VVXEoDVH4C0E83ytndsOGrW9ZvPaYTrkXyHvXNuisxDJP2BLpvhJp7AVIKLEV4Dl1H8hbVjhAG2xPXqmbVL9TmR8YoxiUzwliBWy6nQ3o5TQlA3PogfiNuVAH+ClHtWAKU9grA+YMe1HNlQdlSDAMMPVxi7mUFUH20d9j3pvhl1iXGsYiu+2esf7SI/OEoNypYUP5NXHD77G3ozJ4QSE7NH4DPLfcboORAQr47XzKHPidKrl06ZSuy6T+W1AOlfq2eAJlR9P+purWy6iyfv28HPIWNrllVI1UTSpSEHAm/AM+U/oMEPlRkkxUCl+hW/63zdLyHYz+SBK4QVeCG3DMVi9q4ZaCHUPdB2VPZDjD2avJTWgoWnPOVjgrRb6gb5BYaqDTms8eprFeig6tRTmjNq0k2kmqpm0tUqmpD06+NufEJMISeOJj0KN4NxrT6+ysGUTojRrSMtdhbV+IUlpUD/CF7bGhHw3qQcRQa3z1XFj44lAKHTDJW43L5ZjzBk/yyTi3Q34Ci5PMZWi1XXLQiK7QOBmPOcNmz3pkMnv3pHXhQEZvtPzEqzTncCtFGcV9wf5czzu9e0Fin5HHT2+oXAWhF8MIUCwxvfPZyKqbla+OREsaShfPX6gVLo76PJYp9UxKnYtLaL1fWV1a3OJdV3jjp9y/c1PlUZoXkAK9AeIqndMyvs14XVfV88jKmA/Op5J4mU3+FtWi+DGCrVdeXI3MPk9B9aWE4dVFhbTF3VtWct9LcGWFjByr6mEuSB9D58Q63QdAMG5XrEiDr3hdu/Axb5X7Pf8rfcZw0kl0kKPVYVFpiulnlUhchJUdxqHccM/u8euNacTchAjpkFWQjd/19dodzW5Ht9s1yYIukCLF4Qw+O9sp0d6r6eRob48zYbHgLSYG1kIp8tV8ZcdTlHncuoTf3fIIljzSHrpF0x3CWVbxRNuNeG6o65yjqGchxWR4N+Q28UhwKPtkIUq4kHOTK5LGiwp5NHQHuslvBwcZe4NcHdGEYm+XEVkH7bURPvvDVOIScpnj2YIaMGoYMoswtboFBRnuKK+hcw+OjWu4T2TSuF2TuDbKwmot3F2VvpUa4PPTvF6C3Q/AGhx5dLVFmXC2Kxv2wsqui++iszhjsOVsxKrF2oxmb0mL3pViH4oBZdskSevcDxQZCnfVFNMx7i5awT0Gy0SDKXQsGXUu69kAiJNECUBelEmx0ZXG4BLy+rm+ddehGvHRIyhUB2ladv6lJBvTKPuPIRmCRRyrrak0AWhAfVGFoF+dJFKro6jTvULH5nJ+fgbbvLnCJ78vv1xCBsCudYwA3gYW9gtazzXJAVthOncc5rbxYAPw2sLWsJjNBXygVLu7FYk7pXhxwNR+VH/FyuHN5v34VCTzL+RIOjT6C+iCpcmFpq4d5JTb+5PZcCD+iap+adfeguRtbv3D+2vnDlgdOWn7BDnsp/aP4f+4DzL8pot73rx/l17jHEdPKOuKJWrUWibGtjgHGBtAYnL5X+2elXTbeKS3eu+oq+D2/HnmHtzqm4Gqvj5Ib2HUm4+rhVC2AcgGv7p1o3+6gnyrzthknGGtiZ8+ZM8TSZXWfl8eAuDyLxxTRqvX2qkwyW+xKcYLZ47R7RM1xIqGLFjENjGnclfTTRCtYFo/hjP9cfqTexOjl81CGQ5IkERB17plg7P0m1drxhDiV857FrJ/F4dW9v9/UF4luTrgwY+tIL71sCcAwEc3b1LiPeKuUudcZ0vXiVhwJ8YZGUjA9KkQnrj8xxfascpwoNyCDIEq3FRfyW/NKQ+/wtXTXWFx/BGsRntUKACUPf6iulVCkc05B4jcDn8I57hMatSMeNh1xp5uRCiwJuCAzV0Lv6wSndDG9oK/pcr9XR7nHA6+JUMAkRkK9NBCy0zPX/Qk7rhz0gHWzpvGVkNX6VfcchLyTDrcey7qwHwScRlBAOJWrD8rw7oxsODp6J5f8CWZ8v3Upg0tiINjV+uGBEpExiI/mmtR3dUeeJSNs7KwrFeT/zB0ELQwCkJNGABycWesq4oE+KYWRaETxHusMliFxk6PSgd/uC56NZO4f75d7lZjJW/+XJwNQsG178yYadjM7/Ixyn6cqtVU2yeveaIu64JUyFHiqeqlNKAPY2cwtMuxWSG4iNX0qyM5gUD8M5T6+qRO0y35NNdjKwpcfm2Ll4ANfyOek0iKn3L0b0ZMF9hYRq9lG/+DemNrcQAAA</t>
+  </si>
+  <si>
+    <t>OLIVARES AGUILÓ</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Pablo Felipe</t>
+  </si>
+  <si>
+    <t>24-02-1989</t>
+  </si>
+  <si>
+    <t>02-02-2012</t>
+  </si>
+  <si>
+    <t>07-09-2019</t>
+  </si>
+  <si>
+    <t>+56944152660</t>
+  </si>
+  <si>
+    <t>p.olivares.cl@gmail.com</t>
+  </si>
+  <si>
+    <t>data:image/webp;base64,UklGRhgNAABXRUJQVlA4WAoAAAAgAAAAfwAAmgAASUNDUMgBAAAAAAHIAAAAAAQwAABtbnRyUkdCIFhZWiAH4AABAAEAAAAAAABhY3NwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAQAA9tYAAQAAAADTLQAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAlkZXNjAAAA8AAAACRyWFlaAAABFAAAABRnWFlaAAABKAAAABRiWFlaAAABPAAAABR3dHB0AAABUAAAABRyVFJDAAABZAAAAChnVFJDAAABZAAAAChiVFJDAAABZAAAAChjcHJ0AAABjAAAADxtbHVjAAAAAAAAAAEAAAAMZW5VUwAAAAgAAAAcAHMAUgBHAEJYWVogAAAAAAAAb6IAADj1AAADkFhZWiAAAAAAAABimQAAt4UAABjaWFlaIAAAAAAAACSgAAAPhAAAts9YWVogAAAAAAAA9tYAAQAAAADTLXBhcmEAAAAAAAQAAAACZmYAAPKnAAANWQAAE9AAAApbAAAAAAAAAABtbHVjAAAAAAAAAAEAAAAMZW5VUwAAACAAAAAcAEcAbwBvAGcAbABlACAASQBuAGMALgAgADIAMAAxADZWUDggKgsAALA5AJ0BKoAAmwA+TSCLRCKiIRqZXQgoBMSxspQo5hAfwHOTzD7Wze+uPVwXEA3CdXa/K3a+bNDLryx3GhlUh8skPNFf//1j0mXNdJeLlOs8ByGMn9yZXLL8MmbfQK9A94OotY8tKLPb+pA31c396RfJWp3Gq2pPTn25VzoZ+Dikn2pFQxU3DrK2CrWf0VyLpGQ8VBUQQY9K1DWbE8aCUhc/XDMokymaUhEBx+6eCDylvtI/nZIuKPa4YyEsCXj+02v0h1K/GFviaFARg+fjGIM4dLPmCcnXiZDX8CWOPVoLo+vHC71/t7uBPROYXoT9T0906HYbSz9SuDwNnr/84q7pGqZKYC9Ts8w8auOcbF/MsodArl8RldtqWZQX5AhT9ydeWLUj0xJ7+1CciJHQKE8COu7sOlgh5GH43FvzjpCvrUUQizrvnLNVLi4IUKz4SXvOgklLfnhDnDHkTXxK08VcW6mSVBe9Gpk84Nbn2PKewxY0lEILXnTSzQLsAQDFaI9HK1sYZlLQmCOrgThibWi6KErV0crSMuqfM/rkdFse7SaO4u19PfOgBZYIcnOcMeAPKAnifkOosy2VOUNZ+Am9EcwMvsfl8Q6sbnog8dRqcG2BXjAAAP70eeL5FnP4cCQ0kT1a7Ufck37HqV9GHD+lpc8rvfHInH6is1PQOsAcbMWiSqU3YY9VkGPF4fOUf9ZPInx3fE7U0KNxPSS1ym6CjmsQMU/AZpa8XQmaY3Q7Qd2coTWQUwZvbmhFlWlE6x2XJ6WmKdKafvpnNeYWGhFZ8mPHQjX/neHWK/aF9KEtixG01twO4KzpL3vv01oWIZvupj+mTGG7NOIuQ6BFFc/AU2G6jmIRIDXtLghd3vPuE6jO0C6vcm7oNUxsYrJboymQtCJobQf90VIm8gPoWJzFZzp/gbR8D6tJNdxZG/7bMKfnYCG+9kELnzNMgca0qNky758GvuZNbcAMTYry6ffys9l9quW9ujkyEN8cfUP0hROTR/kog9NmsWNUebOKNz4ZFWx4FUC9abpICsUtKLoEwdUW/oBkopwi0WenudmpvnHW9HVFLquRyy2Yvx3jeFV8jN1rXQdnzJyBrWNNJAuj6xX0t/S1TYwCeSAG8hgxBPIZ4ki8glP0oR96kgABLCs5xW9KQFz12S+jbSMSO1wSPZkZad0o1Nn2h+ClvVF/AiJa626vztjI7I0dY1T9EcXEvU1yrxVEWxS+FT88APVD9yatVpJF0I6nAQvp8bfhtDPfbpN/QzlHWCBHvbOMGw/J+bHS/EU83Lv/tReUc+ViQzTIMY29U3gzZ4S6AC85+ptb1lJUoMSefz3Joc0qB6V82GkAeMzA7UEFdigDHerQDerXqZA0rXlcETIL8l7JuGjAg9nLt7RB0mswW/T/zBvPTuEkmlgYMFckVulT8JxhVqrD2VoC/qrlvguOECaiuWCxAHD8Xp9SyxIWeNjCGqRJlHWzJoRlpd56SxuoVQnC7eN7bdfKSe7xcwz5LFP+me/oppE7vyP1AqUVojl7af3wXq/DR9RjrIJTIyWOmrz5wFCzBFR28bRIvWvfDJ+LpJSsqHgg2KEGxy8SbhVPY2T+J3NJjxWu6Ppv8ze3aN4lUd31FGtoJ9jlp/RepJlek5MqYBaMsHdSrKNWAbDeoV1eKhWn680Z/Ax7pQWeSPICTO93bOeSAyYyVe7jGDtmhpol8S/J4D+Z+My5dP7KAkd1H2LL8OdmbEj/VrfT8dH3MeTRmJdOMxnT3Vb2PVcw/54ug0n+E61widdMrRNQ6sGOp3GRLt1JIci7W4vOFsTwYptAz8AoCFUsRWbb4kQ55iFSvMSXhxHkCgkAN76dtAHlrnzDG0bzEKPAAoDZCtHtVPRd9vVKF/wqu2idNJccUG5Q3fnpTmC3CPCWaAmEwEzgnofwU1f2efcXBi+slvdYMzykdi2dT23o6fRfq00EXtDHdhytikPnmaLTmliGP9yCRcNpkpJx6n/O5Dw41vQuJmtwVo0BJtkn8lmyRE/wyRrdPjC5V9dPy4c3EGfE06up92g2ANksBQHnWoVkTDDsGXU9NSZdONKZKDo9H9hpNCLlbkaD6Ke7TH7Lix02pBOEe+vMxv4kt5emfKuT09aEAXLfmzpJ0r41xHj3nJs03nflCwWm5mDTkrd49CNHx5rddgMslca8dVqrAc7pOQzpevOt04OAgemxUc+Is+pB7jCICtdjBp3JxiNeykzZV1QnDtCCjHUBY96SBEZjpCSS5nl7jQFUkSjdIl2gBKlOIJ6yOvDKPyhJSoXccMHyMaUA/m28NUnJyveaeujJ4IEvDmytxJbXT5NO25JRNuAybNrrJ1hmlCzH6W3YuJOP1PpSg5y44QLtsfJcTU0BK03WgxPfp+XLPQNUiYfx7pb+gaSn3IVAK7pkGXCXBYdTHaqZZ0aTepwPY/lgeIAuyXBwESX648d3z9nKmC6PwMltJxcOF4hOgl2V/PZ/Kj+SKL1Z1LfItR4aiu4gqzyq3GPEwPQ2dOPxQqjId8VQTaKlUMgTGlz9pyzjZaC4tz/BaSXBLdcLwM8eeo3bqNPXHhA//t7TWKIv0Ajsjissxls8LJDKGGhB08tTTOVPN4SyQ/bP1Wl7WFgQ4LkIAVpT67UlMT1YTiZXrn2YJakBCjbBU2VxA7wxwKLBMnKyQIzf6Imr7/TBb9MlAQsq58Z2pPA9vzGRFASVY82ExNcCmXnNUE1sljeYDG/2/EnO518KpNwP+AbyJPvbynnGjfxZXjgrEJHJlZ7/tZcyyKn1Iv7I4ypa84yHpJFNQkChYXVY4Q/7yW2miX52CvGP7vEMlxhwqkyFyN28kc2dNVYwE8vXCviJQeVcai4j+jLAGGVYYB7t4x85harsGLZRln4mWaxcgvKLjxLgiUI8mHIyHtK/gzS4ssAuyaQkpKIIGR2WlMFsoYnLiDBIuEr/5i4A2F5Dg4WmJJOyxJZvYgRd5R9N/AXjfwvH0KabHvT2gwq/CAnAjazA0NLjVmZZqmKoB351pTqHGU1VxSj7EwJFSEsCfu/lD2pZa7INro1GUGPXCQZmHS134VQFc2uyALnSbUJdpSljsHr0QSoQASpYrHD+bO5DtqTELpEsgRYIkTeCK4FXDgLjehP3DQuSG9pnuPRXwU22Tzevd+ZLrWC/aQ33oEhjJ+dq8xXC5SGtxuIwm5PGFFyxSJGyYSnt65+JEGj1gNxlJD6S3XVPrFaA0XLYvAo+j6Ejmf1lz+AbRe4+TjmEQd8eT2Vu4hA2sk6Re0dNiw25dc96i4NIEdtlkridFZwfgoITMQJFwJ49zb2pxMl73qxICjN3mXTFPEvABBZePJZghL6ldkZQPZAysGtOrKphcK6o4obL/jojiYtADwM8lRaEEAgprKYA5WhIz0F+zAbxEmJmOLiYctXOuk8INoE/LUw75DAWfEbSJczbHAEqJKFMvIqMqBYO7x7awjb9k5lptNS+87CX+aT6NQAEIfg5OiZZ1ehy0OuKYETnmBho0AL//4PmwKQl7+RmvGnVw9j0YADc9t3Bh/hnCNSOwU6iDgV/NzFRCa6UgpRd/fQ4RWn1Lad1WaXeUnEszalq+tcUa/dz4kUqb6mbGDKBop17Dq0dxoVMqxXHny1UoS2VN+/aEP22I9vE+rwj4MhnXpeCv/8YPrLuFnnT06gKCwXlGEeMmJ+GdVkdAoy3gN0d7WmNRHh9d/c1SrNWTUld4T+SzLznQXmFdNV2vo/pgCR3bin/UGMbdJ1uIDW6ufm7tT/24m5/bqflprLsl+KZr49fhOjGzAAA</t>
+  </si>
+  <si>
+    <t>PACURA</t>
+  </si>
+  <si>
+    <t>Piotr Adam</t>
+  </si>
+  <si>
+    <t>13-12-1976</t>
+  </si>
+  <si>
+    <t>Polacca</t>
+  </si>
+  <si>
+    <t>+48725546968</t>
+  </si>
+  <si>
+    <t>piotradam@yahoo.it</t>
+  </si>
+  <si>
+    <t>data:image/webp;base64,UklGRpIKAABXRUJQVlA4WAoAAAAgAAAAfwAAnQAASUNDUMgBAAAAAAHIAAAAAAQwAABtbnRyUkdCIFhZWiAH4AABAAEAAAAAAABhY3NwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAQAA9tYAAQAAAADTLQAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAlkZXNjAAAA8AAAACRyWFlaAAABFAAAABRnWFlaAAABKAAAABRiWFlaAAABPAAAABR3dHB0AAABUAAAABRyVFJDAAABZAAAAChnVFJDAAABZAAAAChiVFJDAAABZAAAAChjcHJ0AAABjAAAADxtbHVjAAAAAAAAAAEAAAAMZW5VUwAAAAgAAAAcAHMAUgBHAEJYWVogAAAAAAAAb6IAADj1AAADkFhZWiAAAAAAAABimQAAt4UAABjaWFlaIAAAAAAAACSgAAAPhAAAts9YWVogAAAAAAAA9tYAAQAAAADTLXBhcmEAAAAAAAQAAAACZmYAAPKnAAANWQAAE9AAAApbAAAAAAAAAABtbHVjAAAAAAAAAAEAAAAMZW5VUwAAACAAAAAcAEcAbwBvAGcAbABlACAASQBuAGMALgAgADIAMAAxADZWUDggpAgAADA0AJ0BKoAAngA+SSCMRCKiIZr7fFAoBISxgGLf+SkqWtyn4nBPvBFuC2e/VvNXjR14V/SeX4kQx2ljTTd4L6SskiRLhTXZ22jdWzjWYkZgcc6fXhiRtmRoRD7MdhNOwwfaG7MsY1qMA6B1asHHYF/QFIedzZL+J5z3taTyNMcsvXyXbJAcKdrJR7zA3p4cKWBEK1ryVa0myBUA8WAO87crvxKlfG4NYQrf6W5UZmDPiTLDUt40gmvrEx4JNpOcRxRcmCO2cX2uz0PBs+XGGl8OAtw9g3IZ0nNKT3gXjsxbrx9CFpQxw9uX7fDZvQkMx+dv3IrnOEm0g9t/b22vb/cncRK0FW5zjCSjMO9tNSW3iU9A2DpWHAsoAzVY8Ji7rLnnXt0wUBD8gz5rRECEyVRjppXI+nTALQopKfJ9O2Jnl4aJlQzdarsND9FO3xVoncA0YUL6ac4bM7yTsyl80I0KkcBNvvJun9wlRNNvu12U7lAGcHK1c/NF6CsXVG1T68jBRISmlPgVVNpl8Y8kQpSRJYFGeOKH0ck7CVJW8mV645dNkWEvW695wAD+/HCflBvcE/8B9Q+oafO4GHNam3vNmOoIZlwHhUnow1v2vnRC9TvLXNKNccWuZ7lG68Y2jkPO6z5DgX/pLZPOgroD829WRMayHnRokRAHBtDpS8ZyXl0u82IR7k6KH4zSSvHgmOHC3gDGqxztvO36FeXws+SsHD/fHkvwm5hkOUuKiapjCzg/6SqzM2VNgZdCTaMJqDPSSCfdnnLHmW9Dgy0dUUJ2ugAYjgLUQV/WV+1fmgxHvNusRLq71gJfovHBQEI1zboftNbS4Tm2IoXdgX2R7UAUoiTaelBrCoq8WAvg6ckRSitJhqA6fUxj3A2dBh4vMxUF3RyTLh9QHad4EGKbCj9oBDzgRkwDQWoOeajh15bawADjFYBnQTnG/z+6/O5FJv2DxepKD+EOx3eVSyZPmXGdgg8WXeYz6Ldq6qDnS9R9zaTigbDPbizPALm/SL5oW4SqW+wS/szhtCSIrmx4/301M09TT4j5QN1BQIqoczBM6aVs5hOJ/DJK2qo+8Fc87Rfz0cAZahTvAztBWImOfRxIMiXfrkLltD+OkmndWBdRHD2zt2jf9oBrtkDsJvCWvLMqODIPWoMq2nY87eyic5mqQyTvvEgu3zFz+NtcyM9JLQwTzc9H18yNtaYsGxx//naFzSPkO7uRh3o3q0nsAsBc7L0vpsuT12Qh2UIr2RD6cV9AAwCTG99QlAZT+LzIdI0VQmvVHPDSaTAJv9/AaUANDAaoUuCIDgIQe+r81dflQwt4xJ2xDn/4H2DTK/ZsSQUupt+YpK8OtTZ9y+1MyX0Ty3YSaWCAUtNMnRW1zpVZmOfzl/6p5W6VHLkt42FrMaFytKm1bAb4gawZm7jto2+kLPr2mH931uleQmdV+Uox5RKr9DOfYr8vaQot3qhhu0nTDf9GfVWuBV5GVt6aJpKFV5aBUtxKC8rxfblLux4Nb+yfvICCn2S+FGh/DDw4BCif7ojU4Ub+WVIeM/GN9WAznC5sXRsaRELCBjd96Pph7QIyWav+tpEmSnCJjsA+e6OeeUODe66Sfrg5gUgAPz58aU9FFU9AJnDauZYHTESNxG7/iLqWVGTlRo2gv5M8lUz0NpDE40badAa5VQLBap+tn6he2CDcSbnn95bXJN93wMP6O5YkWkAAwC2bA8noXxCdNc6JOFxBQ9xYIGKoM60ZlUOZPHdfvjZ9UkCa9aVWHgwbg0nqRbyOJTqtDOylJQufmACFxYqNkPrVRskC7KkbppsGrpb30LKWiQZDMGSz2Wp9R30nyS3PitKfixlaaKmnEf+yvCOTyL2wlDqVQrmfnlqdOTKC/lIkENiPoEe+Hz7cNutjZuZKvH7gGzBCiWprcp1cuxdKtmjEC4w04bfcSrkcKvxrjz+AzU9dzPW7i6CmOcPacFYmhBTTQbPSujPbOviupnFL0JmvDMuSFYe0VNnpNFIDXkIwo+GQ6L0U+ComyBg5b6zg5/WDgU2hstH6au8lkpZTn/RVy2tzTDt7oxva+zHmWyv830dfZ/GjXj2gsw56dpF8Pn4+yC5tQ9kJSayE4Z3UkI8BtHUUHVp38venTZ8nV2y7juLtBPrXVwXoaU0agEydi5vfpjirbuLRdahT9MqqvrtMRt8ff84a2LzbZMoEnjozPZ+EY7e2Dwg4tWO3RKJYrHEdxFNmZ9Tw8QRIHI4j3d+eBN99H6lt2ZRwRrVWmcIHdk6VPGpXLJgMV/DtrOEsLw86q06iqQam0i5v4xYcPLbxaItqQDKNAGhk2wq7nVCFDqchTmfki4n3TzBLq7p2H754LJoPy7z+BJ/Qi/XjFu3nbex1hy6+DTZFaNJCOpeMkhzRcGOZoRuH5pE25fAcaclPxZpUtm3eF+64R3IbQo+u1a9/lhQMSYhZsq1JODQZTfGa/F3yfXEaOSrYlmPrLvZZZsr3C/ta+NTLqZv5sr5qGSC0WtphIAaUeJlIUL8V7ZDx73wEVFgFpLgprVfOiZn6lN1ZLfwX7ABvwLHljtYRnLfJR90KXygetvGrnwwfhWYIaSxOFAvciq35N36Ua3RZ//CMKQqQPSoJ641ooP1CdfAmFYX2qERWNMuEmX2PMvScwOJase8L1tE7yqeS4T6v17tn08VeStXC3irA+llqRZ3cotHcJAhF6uZlnwjYO44iA+fcG59h4zp9GSf3eTngvxUvglb6+x/nH6GOuvIKoz7LQZcYW1WzL88PdnoMVCuxi3U3c9n6jILcfDtt0t36M885ZZunhb3vtbCt7xTNTyM7lYv8QVnfHcD+k6pe44X9vpgrZNY+YJoIHfywzw72AAJinOLYAeQ4MOjvXL4Qw++pbUiH5pfzYQkPqp35yE6isHsL384TWIIHVwBPHtc6mpzzTwIfgAA=</t>
+  </si>
+  <si>
+    <t>PAJARILLO</t>
+  </si>
+  <si>
+    <t>Jhonny</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 21-08-1989</t>
+  </si>
+  <si>
+    <t>11-01-2021</t>
+  </si>
+  <si>
+    <t>+5491138921733</t>
+  </si>
+  <si>
+    <t>jhonnyjp.pajarillo@gmail.com</t>
+  </si>
+  <si>
+    <t>data:image/webp;base64,UklGRjIMAABXRUJQVlA4WAoAAAAgAAAAfwAAqgAASUNDUMgBAAAAAAHIAAAAAAQwAABtbnRyUkdCIFhZWiAH4AABAAEAAAAAAABhY3NwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAQAA9tYAAQAAAADTLQAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAlkZXNjAAAA8AAAACRyWFlaAAABFAAAABRnWFlaAAABKAAAABRiWFlaAAABPAAAABR3dHB0AAABUAAAABRyVFJDAAABZAAAAChnVFJDAAABZAAAAChiVFJDAAABZAAAAChjcHJ0AAABjAAAADxtbHVjAAAAAAAAAAEAAAAMZW5VUwAAAAgAAAAcAHMAUgBHAEJYWVogAAAAAAAAb6IAADj1AAADkFhZWiAAAAAAAABimQAAt4UAABjaWFlaIAAAAAAAACSgAAAPhAAAts9YWVogAAAAAAAA9tYAAQAAAADTLXBhcmEAAAAAAAQAAAACZmYAAPKnAAANWQAAE9AAAApbAAAAAAAAAABtbHVjAAAAAAAAAAEAAAAMZW5VUwAAACAAAAAcAEcAbwBvAGcAbABlACAASQBuAGMALgAgADIAMAAxADZWUDggRAoAAFA4AJ0BKoAAqwA+TSCMRCKiIRkaPVwoBMSygGWwKF3fsmSzswdKPDv0Hif2nbb3CQdCsqZ7amDIk4qXfhz3T1v6XxivFghBZcNa4Y0IH1dexFcnsGuh+215KgvQdRms7h1zN4+sLhoVPT6AI85/Sh4HSjnLJ81FsSJNxPY0fnog8PI0e4R4qjgZixGwi9ZsHgj5zCA4OB7ayfH8L1vur+dAdvj5WNZbL80k8l0GZVSMP/6tyN3A3UXVRFTg+JuP1abDmAIh9JsPyJgsFKxtFjG1jkvLJzsgcZrToQkS7XTPaqZLfVpA5fU/ZvoTgtpep+RKeUK+PGfr+XyCcVKfQEf/ntHKclCxPDSH3CS5Kr8p8oXAS6M1HG/9bQX6I42N/p/rxvaOp1JId/Lm2YXFUo9t3UFykJWNX6pIRtn0sZBrY+AJCPqDnSni7/08qYcOZJgFOEHZo+j6FpzzV86cXBYMz8t5M5dmYkv+FwwQJwa02J91jqUt4OukKsnLJjw+pqI9RU94eo5OMhzs0zxqrWy2/e7Ea+dZFjs5rpSyWhZy3Ld1FSxYRgATEeHSGtWDSy9d6rsdDLSrlW1mkhJIfGrJG4RwHqn0io3KgAD+/U5e+4XBdgSY1VfBxz4MG/LJzcjm1pyR8JjwfbagnMKeLMPFamcz6HZc2Cze/p3cqIz1aZnrzD3OHtE5uZicCX00Uu65JTJ+RYLGS/7DzpcTH4No9MnvqFl65RMU9qqIr7x5xgNeBPt8KqKcMRHX87ej3rDf+K704vyPhXm7hp+L2p5fsi2zKFslozSOiOydtf6PkYJDg40THJ32PZGBKJOtvUjKN8tkpGqJPFe73BKwKptaeXxfutGNbW9x9BrzE1nAr/in8er4i8Sr41T7XykonOcmbmpMIOB5DP9L/drhzR9ZVGtTNH4FIW8pk4eYG8sicr1o/IDMr4ap2rq+rIatE4wFRJ9zBg9NkWR7Okk0LWDkaF0vSNOitbo3bnHPgkZP2/r8I6BpEXFBE6m8iaO9aqWnKxSvQWqef9LtMxeTjGIMcWzdIhDjsF3SWMuOt2RB5zADnFcb0Hzmq62q4mmzhJuyXC8oDf4H8d4qGW0bpTCVorSrOZwcHIjY7iAp95N461CSFf5Fz3se0vsldsIKnj4Q3D8yvjKHeM5V+t5ek2lSTlYnvbMIrfUtw5RBI5/61pvzVFpaDNx8NicddgLHsV5nfWU0yKhGJCTUVvvEl6cFiXxUfQddtl8qTRHjboEEMHRsvyaUTH18I6K1LDSjgNTWX+pFjHw85/fMIekrc84SYNkzNvqsbu+PeCVgeGMvQ+qowiZRIrOuJuhZbqxt4jYIEzWUkGkocy+oXS1n903FL0MUjsfQCJF6HWB4Lx7dOxS6bW2yroIHzYN30Nf2qzm7gKexlhxsqzVvlkgOlvqYj9NbJ/6rplZVxmbK3F/8wwrCc1t6eqzROEHCrJTTbDnAcR+u8kxr/+082MqtvIxz0ALmEptLgWJYoVS9VlrB6I7rrj6wSQyOxAQYvNF+XlGb5PRms/4Lil2nTL+60xqVOsXhA/Fyf8iSrvapXiYrejrVMi1Wh6lXSwIEVahe0KmEVnrsLahOVcQVKMH/9KuDe7plr32mU3HjlIlmF3l/TvYcCWQ5vNdM+4Q3HHAaC9PNDfeebpnj1aKBYZtlYq+c9YrkMb5OTHVotlJFeiGLBlkud4H6Wn+9lKOOgpmP/LONIcqHCszxd0FuhpPRDrHrGRxaY2l2OXEeEjLLLrZFLMWgVE3BXW8dIgl12I8mHKSxE34IlWFMpbn9/BDb3iYIaLqr7xv89YkoAGBL9VxDHDxRvZgO5HPuFzCF6qFvx8jiXM+doxDUNFvUHJbdhymO28eMM7S90Au1QmigH+Qh63UrLtPaLhX5/7zRzMwqo2UDxDgRdWzCQuKlUsUHuw9Wr6oVjorBg3Dq9bPfdmVPZ57jIADHUJp/dwPlTXe0e5VaChyNlJqSf2AEXEVcrNnpjhEu1BETeBtGfpQeX1tXmLKR53CRp3Bsxeo4v+KmGrSVpl8a+SG1N5ioTTtXWau0PlMSc0rh5qA0qsSjw4FSpLiPWYgkXyYSqEM7Kuelew8Af+NvWQythCV7OeeM7QVmFL8Gy/t/8JEvti+VFzH4prBsPnJ2tg9cJxMk5lxxnJTnwqap2POWGUJLmqvA2qkP76B7vErFeO7jtw8XFcHMe5nBhhu18U32OjJkXBgRhUpGyuRe0zl3hK7rUx4V/XtTZXOUH0MS1MziLRPmeorQFckrXPVFu6jPj8LigxM7+wVHj+W9sO9cwJyQIjxdPUEuLZEY2sjcTCaseCjgbCzTWZ0/wmPmYDRbsq2Z8gCj6RBrQasS1/VwLbwbRcSHo7TYu0g6w1OxRQr2k994pSMoEK9vf0AmCKVNrtK8q2mIZOpY6KdCwulWWULNuqPmOeOUqcMk9oytXRHpgv1O4N0CE4UhGdCQxwe3duGt6AZyb4/mtdtXWxIM40s2ilTqjhqW7ziTAZmr5TdBztsTQYYyMEIcbSsXXz2loRxLRhA6Yy6Q62akgSVDJv5dutkn+bClslnP4NG4mzcqcvM9hERFecAgpHOWk784hpmCQQuB04d8fTDJFP8iP+vjP3tfFQ6qandLOFb5xICND0vf0Qzvg6/HajH91aSTGJ6KEiYdjjVMQPDsGkd6wY0xJIFAXpMonZHtMKYGsKLagka1E+8gtTZiOc2JX69McUNYhHfQ7a/hiZaFgRtPF8axoNtEjmRToM3oLoRahlOKF7Zb9ZUm/SA4xSAZzsxBoCV1p35BobQDRxcqNd7lveprTo6gP+yLACNkeq8md22OUY+N1J+dmsJmb35sYA7k1ToJdzNxqHvW1JNt1vfncX5AN/KP63biNzRjiMTKTUKYxQBeCZ8yfHBXNO3RUVoR9O1mvQYVmyZz8kFjtrMh87VivEmcnu0vH4QiQMu788EOGDTw9Y7Z6paJrsERCslNeC2enFccKvzMYHYpNAnL1g/7F8YT2FrXIImTSaaQto3Ui7j/SHhE0Oks+EopqUYWcI+LqeDcptqt2/4qO8YjjGqpnVmBAn6UYIESbLtrEVmaKBIkCsFpfnGnt7ar6r/Yp/GjljHY2Szjy7xabmyUHrAA03Obj3LLW9Er8eLE4LJRiqoOvKPSmncxtfduVgSPsp81pKLfjs7lqqs6Dp8r3JkFLFFB46xZPwgPWp6fJmXnk+i0H4R73PQDC7v//gQ5eamL8VAjn5SU2nd891ZLDFmgrpfzKhdBJFi4cWD/W6jX47IQItDK5hKBKpj3WIHK8l8FCnj0zburuBUCfQtoXq4xYzqTFor47IXVTohTIUrC/IOh6KSF3DNy2w9p+UEyiNd99KPzFAjbLaysMuqfx00e8KKbR7y7AgqBSdRWspSQ5cGyyjlIYTpGfhS1uAhv8eHBDTECrhD708fop39PJUmZg5PUPyQl+wuvxvWD+Anh2XuVsWk94AAAAA==</t>
+  </si>
+  <si>
+    <t>PALOMBI</t>
+  </si>
+  <si>
+    <t>Valter</t>
+  </si>
+  <si>
+    <t>06-08-1947</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 29-09-1964</t>
+  </si>
+  <si>
+    <t>06-05-1973</t>
+  </si>
+  <si>
+    <t>data:image/webp;base64,UklGRiANAABXRUJQVlA4WAoAAAAgAAAAfwAApgAASUNDUMgBAAAAAAHIAAAAAAQwAABtbnRyUkdCIFhZWiAH4AABAAEAAAAAAABhY3NwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAQAA9tYAAQAAAADTLQAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAlkZXNjAAAA8AAAACRyWFlaAAABFAAAABRnWFlaAAABKAAAABRiWFlaAAABPAAAABR3dHB0AAABUAAAABRyVFJDAAABZAAAAChnVFJDAAABZAAAAChiVFJDAAABZAAAAChjcHJ0AAABjAAAADxtbHVjAAAAAAAAAAEAAAAMZW5VUwAAAAgAAAAcAHMAUgBHAEJYWVogAAAAAAAAb6IAADj1AAADkFhZWiAAAAAAAABimQAAt4UAABjaWFlaIAAAAAAAACSgAAAPhAAAts9YWVogAAAAAAAA9tYAAQAAAADTLXBhcmEAAAAAAAQAAAACZmYAAPKnAAANWQAAE9AAAApbAAAAAAAAAABtbHVjAAAAAAAAAAEAAAAMZW5VUwAAACAAAAAcAEcAbwBvAGcAbABlACAASQBuAGMALgAgADIAMAAxADZWUDggMgsAADA8AJ0BKoAApwA+SR6LRCKhoRqLlVQoBISygGHR9Gt2V7fu77IiiIqrGa27DDH7ynv3hcIO97OXlhpX309iqX3rquvQou5NDRdz4A0l4T1MNp/OLomG4/fDP7uS4eyexyhyZBs9g7E0ozVvVxNdP5mKwqBj3j54nXN63uNijs6vpPRI0YAJqayAL4logt9spQKNmXjytNIf2xZHnCmM3GqQkWfP6feDfqNZXGKpOWgJKW3Iz3Jjz9YLY42dTcfKoDXVUUvT1MOYAmTk2/mAr78q0bt8Wjwq9Atg1qYLu4ER6spduJh8XkSFnb9rMz0N4eaDCVawRPtKbrxz7ag8eagFC5QnXg4rGLXJV8wxCqB5JCVmsCL4WN/odWjZD8rYniWF6k/afJJvYMyEHRzcyeDdsD0Kah3/Cg3CDHysjNXfy09N7QJmzAZLBIeqODHP+RkxJNfJ2njGujF6F1UG8FgwYoFDSZ5udKavkDBmmScee3YIRAxCAijsygzg6VLyFpYC4c8hhAR7Xx3UMW0oIS2QFG+t7lZZ5GzJ9zx5ne/hWj/wPy6Y2iTROAqmN3dYfbRiYsIgzhabi6RrTun5wi39yAl3QL/ti9Inc/PaZBcDMBD03s5BZhuP609e953mRyNeMEcPp8ZWpAAA/tg98MyzLiX+ig1ZBl4WlXR12x1V9wORL2srn/ZnZ3EOo3nwt/q2qXvmLinTlXGgYHMfZ/gzWDEhHBhzAXByuY1/4URgs6l9hfx9nkJ8dS5qs3hFlVrJk5mV3Yk+k0UbjBI2nCVdHA7ePV7HL+T9AsHtNkD7QVXNPAMY54HOVfQyoQMqKzwUbcY2JDNDLvr/f9wHSmLxdJEYQouqisTQyxL5g/BbHez2PaR1SnL7luKgUf5SjtBnNEK0TMs9n4RpC0fDwGmo+qutkUB45swEFQQVOqQnbj2twNQmljBpNo4bhpsv1tvoUkTW1znnBy7JhocXSDzFZ8GlxRc/IULiT8vVJ0flKI1zTISv5PkVxsrpf09UPhuD9EyVT61NZYyrqQAulhUv3CJlOWZZKHpoSTX1hJuEWHPNXy7ws4WvC2htmUt+YKNqj9gYw6Aq4dU5OJH4s4OoUNR4UXnEWIs5szSyvJTeqkSbqrCgDEYjrL0nhSXHO3TPLj4ApuUugB5aXg7ZV4wBy993p3AqMYZRJXS2mthITQnruNy0auH/zYdjCZS3DsxBFXTSWfuoE72cSU3V7lTG1hVjBfHFbCr/VMBXYG/8rMnIm28I/jx5F8DMaLobZEDU0qU39LSedNnOLn7SxEf0qnW9plWeKYk/0aUaOhKYiQH0v05BsbooCKnthL/mHdV9K0zCFnS8acoIYAkf1j0yFaMMX5cZnvqKBNn+efXbn8M9gBnAwhWZlfdp0XL5sFSl2EuSGZfg1nCex9eA8Rhzzh+d2d9kfaVWAo+C4xUdSIJlrFvjflMdGODQJngfkbg6j638pxk9iEO1mEiw0QLS7hQdXTl7hsZpU3/gAI4uIthYXr99JfZ3gO/oV1THl6BW6OTwhfBZZYvuZilXm00/bYR9SoV4hJfMYqwyXQD6n/BgxnbaN0XBoTDHbbeqpdn5+wjyw3309XUbGN9Ba6cyZjXxWqvaO/+DGriFX7edOKHgdM9spGnX24gveQMV6s4O6wdmi7+NO1U4t2usCFPEN+rqKoJcmrJHvBIz11/ABo/9mhxW68N7/1SfPto5fbdew7JN3Nx/1VXGpgN1NxJTSkjHtoSz8+I8/+jUBpvCLL5sQLhb9959M+o0w1wrqqOAaWSG7Elg1OWu86kCHDYelXcpzqWNhYxEFp0vPkUdTMlQTrsruLvt9OwRx+aXR0CNP/lSiY0mvgcgin6U0uNud2D0ep+2UDjvw1h51KXwJp3opycq9mB8S/N7GJjAKgsgtCAWwalwAtYT1JflDBbXACSNSYhWkh/qhqi2pPDin/otFiF+6sFubS7OCAbE3+PYNI5uNEsduw5IG6OkuTTYb/mM5b/98dbRxQbFBZyB0U43Cu0DRugU6rRoXV0VaCGfW++TqjlZXZVwk8p80KCc/XwkywRBIcm5HNvVTbndqvt9o0di2IIO7dQuuf/TdVc9mwZ+dXpUbpE+IEe8dEg3eIVh7qDAeBuXGmxOSdKJh/pR+U+aGNMd+O3WzEQjuPkcftCHLGdPxT6Rj8dayhDecyQh0Y47X6yLveunKTfpTwKCyHp84XtQj7Pnac4u3LoT6XiXoau2jbH+Uta/H114N8cxN5x90Ian3ZOdyNzo/1fNU6p61TySFdCQtDJHaIuHW+izE/07b8CLzoIY8F7xw1ocEiI8F3BDcEx3wc9q0QgGpL3onicPg/j06gq4P14dSr0xCoE3sUhKp+2xZZ+qu+hbdOcgvTnHATvtEtgb6/JkX/BXsN6eCVlIj2lwerZa4jaJfdtKyNtGhOpd7l/EpChHwcZSHmGNddiQ9TnHbpT4ZJyVd9redk8r9mY/9+cSf9vrv9n977VLzBOVVblPY7dokis+MZvSWJYjG4omnFkbJml8PKxKLz/G10wrc24idNJX8S1GDRZKug9uO3dKrPefwQXponrNtcm3Vk3VPOsK+3IH/0KgmmXRzAXn0WgjeuLsowR6cOqqQKnoKjkCXZhombq1mz3Gw97v11H4vIPfZluzhmFuclKESGD9bwhADjxfTU+VZ3CtUGgKCZkp7XNa84ixk8NX4pQwcogDzD3y6vDSY0GxEOA/NJ2jcNFKEfFh/jpmHM7bKmCHjdlcNDZZUc5LRW9+OLSJJ43LulQS/yCsalHwxSYT3I07zqQnpe9JkhLQWF+vStsGknlPvDDEYYZWtxdparAC+ntSRNt029qUDjv5ZeMUWi621IY50HPskx4bv7IAFusV3xZbBP/T2q6L1ynHL5lohUmjeLyaWwHl1AqhXQSNsaOe3ut833TFhZjALFVxlefqrlQ2V8bAWwfxpe0fHzw3llhVx40179DvBV14lLNB/JDRyWIHSKS3o3FKX3KIaqOiBRSfIRPdNXMGAJmR/jscHFQfFE8xzuhoelHt/lKcQBWgkpxvMGeUxE96n6ensncyIOJmU3Pum9WjDjx+7lW6QY1PlvEFjGnp+YnbMGi/01uUuUUSJJqxXLCX8wNCtRmD3AHTdhH2rEuV8LJv665KlCCyRP4169QluGjSKMgm/C2p9L6y2+x4uVm5sOBBGadAQsetTo5oGFnUY5UqmFLuFgEdtuB/WVbSeOCTWNDUld0Ko0VkC5aQAfCV1PxiUplpuV6o+QzfpyBGoLR6obbwjbuUUL/C4YpGNl8qqNAzzUrYGZkXrXqxn61dA17VVhIPwvd/R/sAaCJMUEwNXpmCurTWFbFX9D+Bo6rWJLrQyoXEf7sl+L+D/5U+aNq9Qodu7vbKs18W00ADN0qU+n/E5Ioal2095EdwCpWY3FCm0ZIKuQdGlZ12IylC7HaqOzd275ALFZAgA/CLwtdf04Ax7NejWbWAPEp/sovCmSBW7QBdQqEBtnlyNMhCymqhvfkK5a8+0JXOBUrZ2ibhHjnZlTv3IooPIAiA9mWV0HocONXmdbUl90r9dhJRdUGCmuMJn4QYawzN13VYWtyvenKG79XwVgyZdWyfU8dhyWHL+8yEezZB/TodEr5w8IGp9fh4Dj1v08u9XsOq8VvyoADok/vM9QQglMXoPU4WursJK0VCaJhImDdhyWc2MZ/mOpANNEM7TCUI64QelVXEETn79Ku5Y3vBIilGa0Ar7LfsLGnxIduYO5j1t241AW5QANKzVHbiJqISAABb9VhmoEgyyKqAAAA=</t>
+  </si>
+  <si>
+    <t>PARENA</t>
+  </si>
+  <si>
+    <t>Ivan Vincent</t>
+  </si>
+  <si>
+    <t>05-04-1997</t>
+  </si>
+  <si>
+    <t>31-05-2021</t>
+  </si>
+  <si>
+    <t>+393513096188</t>
+  </si>
+  <si>
+    <t>ivanvincent0909@gmail.com</t>
+  </si>
+  <si>
+    <t>data:image/webp;base64,UklGRtgMAABXRUJQVlA4WAoAAAAgAAAAfwAAqQAASUNDUMgBAAAAAAHIAAAAAAQwAABtbnRyUkdCIFhZWiAH4AABAAEAAAAAAABhY3NwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAQAA9tYAAQAAAADTLQAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAlkZXNjAAAA8AAAACRyWFlaAAABFAAAABRnWFlaAAABKAAAABRiWFlaAAABPAAAABR3dHB0AAABUAAAABRyVFJDAAABZAAAAChnVFJDAAABZAAAAChiVFJDAAABZAAAAChjcHJ0AAABjAAAADxtbHVjAAAAAAAAAAEAAAAMZW5VUwAAAAgAAAAcAHMAUgBHAEJYWVogAAAAAAAAb6IAADj1AAADkFhZWiAAAAAAAABimQAAt4UAABjaWFlaIAAAAAAAACSgAAAPhAAAts9YWVogAAAAAAAA9tYAAQAAAADTLXBhcmEAAAAAAAQAAAACZmYAAPKnAAANWQAAE9AAAApbAAAAAAAAAABtbHVjAAAAAAAAAAEAAAAMZW5VUwAAACAAAAAcAEcAbwBvAGcAbABlACAASQBuAGMALgAgADIAMAAxADZWUDgg6goAAJA9AJ0BKoAAqgA+SRyKRCKhoRubhdQoBISygGokGmt2Vngu9DJAiGqrLa768/wOK1Ev7+4XZ06ywAWMUw4YKIpLmoY94zdNLdp3l6oYvv3C5O1/l0oWfjtfTQymHactVCU8eHifGwVoflxvKct4WvRJ80CvVlI91mxh2IJx/PJRzuz1n8SkxoKlh/3XDLQ8SvlUKo1OWYMIgB3rP7a1y3U0b9dc8t0jIalWTyiLpDCHFSNDxs3ln48nGTrHUufFCQ8JyzozYpckhe8CnB4baLZFx/aa6bGgEH8vPSIGG+ZH4sqNmTkqkSwXALXo0+SXbnq+T0whWAaovu4CpcsEJkJVtOs4Q2Z4ntiAndH1LVcaTeeW4WSvuaWp250rRV/pT1I+me7XcQmNEgBq/llpJxLXhSl2pYr1PTp2JM4mMnnaLLBsMt1Y7DOJUeFxonEGEougPoTBqOlTsMdjzQBvZFzbXgAD7PgHbIZlmO9O5ErH4oYcW2w+1kPqhIe6T9p7DV346AD//mG+W9/zbmPrAIGHztth7EmoI2jhK8lqe/zb8+ykk/1HkzH9tLYTxAg9/zAZSp4m1MC/7svw9LVCwUV4ZGxhzJAzzb6DcZC/Cn7e9XRPo6Bj8AZqAU8Kgxoi3dZdphrusFk+o7qdcbOthINkDsaSWAD+/2oBnESaChhpBE7gNmTmfII1eOo1/0Sa0xMy+MpZVomJR4ne01S4PN/gdaY86Guopa/uVMQ9+aN9r0xHSZ8A3Wp+rAppGg06rM/MlNLxSCL4yaPD+vu7/SgHqONbIDD5hdPF0Nut3ukgIvKdcxx7TQWsydNbmUbkZCoYfXg3MXr/zT+t2Py2wkmVm/QqiISEuE00lh1gFJ0Da790OPTXj1JWgZzm94Vsx8Xh8RgzFs86Uk6Rgyprh5ncyn/33EAu4Xleysiz1zl1zbK8hAt4SlTZJsqOlbq4xglvpS0HF9JDl7c8+OytUXX5m9Ho+dyOHdxnvaGcscUkXU8n0WhO1p3XbduxDsFlqmTFjJs5dc0OOqOBfeS5BpRppyIYc3uDacPlOu22JRQFTSrZIHIVkRnUWjj+m8spasNTqbNa2TXSmeO+wGBvgNMuWlKgifjEuKSVuill60uBXQ4A1Ja0NXPJjoObso1lUqgza0O8vsOrT6hmdQX6WFBvZDKj9TOeAL9gVamrsLxOwAsBuvprZcabw0dthorl3CHZ6CUcPxJYS/KtUtKaOz5GqUk2x3UJE6gh4h4X9QQyGuSHXzTPjnTzl5NwFgrj4Ks4WHCKOx+YTanYQ9p51YoDaEEg4imWkgTLeR0ZFro+fjsB625APgp8wcwJvZ0/6S0uWmjxOo/1nPAlceqS+tW+xDN/wrse+QhPd5ts2d/Ik1zduy/5EnSNw8Gq7FRaLoVpnyeLWwZzRp6uqPDHA/n1hem6MykRfeJIXBNF+sETVkqDrksQUsniR2MJiDH3AR0i5p63FCySGCzAytvV0O8F6enrAvMFfz92fEmiuevKmUma3hF9iWdNihLZwkJRbFkH53vde1034G4pck2OlXa0WuNK5hCyusxAdjda+u3TatQtf6ZashZjcDuheeDL1pSFjy2bPHVIUbHDABHrzFZmH/8wDXvntNw3QMUgjVXWNnJKotafWhbdhBbqBbtZPJK1zNuZY1jXoLIVx4LzWMQszFGIknMq8jqXKygeRBSaPNFAUCT6RkH4DiT8NDc0EYGU3N+LbHzBAX7gyTxzIIGSPY9SVHfRZ+nUgIc0QHo//QcWgCi21WYzGCaGkdWiA/XQrtech2E+6ZSFGz+LKn2OK4gykkqX0t0ME5C23Ld8fI3oZEtInN8iQOMYy925jsdHF/VSTXLeBSgScCFcOMujXHCWGpX08D8tQOl6n6aysT4NN/U3a08MXQSnU1X/Nm4xLYSj/+1/KuntvG52U7mq/rbZv9EPlFkKptFBczmSF+Q+c3nOzpoK9pmS855yudx7DRR0Z7psEULLTyYHoFU6Xa82yo9nV3NFgIkhFfj++NkcRLzWbG6PcYkhUNMm82Qej1Q3plvuHbIGTKEuhho9cxBcLhN2uI5mhhJLHud7DVrT3N37bsafY2aK4KGzSAxTTnjVZn324c1ETjjvkS6kwJFr8Jbi40Q7fk94DYx3xwgw1piQH0P5OEmSG1mB5oRi0vlGIPWoPPI1rVfsSZJnDUFi0S0RYu/6+06Gkg0jpMajSbagdBgAllhmWdk2e5UNaZLodWcQWfwQO06BGoVomHpNZ5JKzsLfmBf2BlUI0Sl/FDlFbIV8BZau5kq92/oNy85lqL8KRBoxWegsyVw+wSmyFRRBgfjDZ0tmrQdIAo6EnDAjq4xBE4GQU2jfrOTHH/TGGuGxRFftPpaGd3mVw0PFCHyr8t0vbZqLtcJ0iMvsEPCzjMahXMZdFRSd3Bu4OgvDrrLD0/06YnEf4b1Cz+ayNGANNr/A19oZDlncaURHiCCzkpcI4EHV+frChLNy4QRxZEgE4VzeG+hTxiTjQdQmEiQEw23KlZFEH4YbMAOv7/0ZJwAxCxj+rYoZFU3vHgaU58al9J4r3AyffSHjeEqpdcswLqygbg1okNKNPMq8C07D4wCve4Oh5dui8FzeaGNqsgqRqXC8XHcsgTN0RDguyqMdB9vqWqDWZdF1GAXNkkRYRIY5PpJEN2BnCDhRCkPYLXd9dsDjwZDDxMjd9zf/YedSuwo5KkTMqgnc8/AaLtYjvt7EvskWHgjTt+YRj3yB3T/Xj3mFLm+bRHY6SYb4n5NCELzelTRdTmmreNK2tjnbfa8cdjTG582PaQ633wdNTmksnxEXwrWawoY0SneYzbICGXlcC+6wTpRDIeXTO8I8PiUaonPbUtBPRf2j8uf1WvGJF5mH5aog5Cgdv9PHtq/hTIY+/iEidjmEDnE1IsUoAzq+yh6rUn8OSaRmGM7Z+Ma2mDDxlJ/cusTSHmiO0Ss21WzZt8XLcJRSLHl/EUcbQ5FsatXngVlBCUiMt/XHJ8D6VXJ9udPv+uDFhBeOZYMmOWCXvtpW/ZRIfkSwHlYB61KqWEgMmZmhD21yU2z06xZKYTgBIKruvyxLbVtvPbu7NRxDhYskwy3WHVVvkv/swOI+fStGeno4wKhs8mhkTXMzkpfJs8O/fsnUkNxeFHtvMHWFMPteo+jhtlEIJrFtx8kylR9/hGSDOLAkQa8/WXRiTZAEHzTqVVEh+rC/74TESrMuJx0mOSNKIANCssW1lQugKs9O1fIj0X2a4E1TRhtB5fqWZ5GwNxNJp8yTmOEb5qXxb+x8vHnvPjiTTq34Mo4d1kZ4bHHJGFwWqlY84jkDoiUc5rXUSlS/5SynP+sEnIB95UuVTgSZrzwFNeVsgA6lITytm1RbP7GeOtLn75JU/ckdADvCpxR6TCnfVstIhqdOue3tjRYoJW/X32Y++LnKMIaaoS7CcUGKnyivKxM9UA2MEg4yCyOZ3UNo/8kRAnBVq1KK7ONda3b7w6KtNtoHnQJYAB2riWniu9d1mX12KrURBwKJvZYKs0XfIDs0scvak5A8EOh+d4fw9AvbiE7RB/t1DZiCU1+lXExfEqSTOfdjLwXkhAwKxINKbMtpITE/HNvmYADe9NMiCxXz7RNRKnLAQ6aw0UHFB9pUxE7P7Tweb4CtsO+zZfd2oh34Y/0pEP0wBPAPKgFjh19xi0MjsyqhrtnFCQcrM3JBWkQAAAA=</t>
+  </si>
+  <si>
+    <t>PETRELLA</t>
+  </si>
+  <si>
+    <t>Antonino</t>
+  </si>
+  <si>
+    <t>25-08-1939</t>
+  </si>
+  <si>
+    <t>29-09-1956</t>
+  </si>
+  <si>
+    <t>19-12-1964</t>
+  </si>
+  <si>
+    <t>data:image/webp;base64,UklGRjoKAABXRUJQVlA4WAoAAAAgAAAAfwAApQAASUNDUMgBAAAAAAHIAAAAAAQwAABtbnRyUkdCIFhZWiAH4AABAAEAAAAAAABhY3NwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAQAA9tYAAQAAAADTLQAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAlkZXNjAAAA8AAAACRyWFlaAAABFAAAABRnWFlaAAABKAAAABRiWFlaAAABPAAAABR3dHB0AAABUAAAABRyVFJDAAABZAAAAChnVFJDAAABZAAAAChiVFJDAAABZAAAAChjcHJ0AAABjAAAADxtbHVjAAAAAAAAAAEAAAAMZW5VUwAAAAgAAAAcAHMAUgBHAEJYWVogAAAAAAAAb6IAADj1AAADkFhZWiAAAAAAAABimQAAt4UAABjaWFlaIAAAAAAAACSgAAAPhAAAts9YWVogAAAAAAAA9tYAAQAAAADTLXBhcmEAAAAAAAQAAAACZmYAAPKnAAANWQAAE9AAAApbAAAAAAAAAABtbHVjAAAAAAAAAAEAAAAMZW5VUwAAACAAAAAcAEcAbwBvAGcAbABlACAASQBuAGMALgAgADIAMAAxADZWUDggTAgAAJA6AJ0BKoAApgA+TSCLRCKiIRorJSAoBMSygGPuI/Yb0USA2mk8gjRkPUjZaadOT7XIuBYRq73cR6rjtW1vWCg6lqgrWrRn/Nz4+j9zmkcJh6MX5E/ifRHX3j8Ql0dvn1RJJtDnbHp30fjdsHDruf7TJl1MZSPhSkK4JHmuQAYViAinZIKCFWE6QZIaNSx+qHLTSKuOF4SzhCWWD7eV/EOj08S3+IkxnIe9L8Cu9apqc0k3ZR0LJ2Zs24F8RxBOCIlyXRQ99DYQMVKOdhajBJNh8X8yOuTLoSrLHrUnsKTM4FJ3v5k+wbhu3j9iYHaieP08AIGoP9Z000EccnxIXBs15VJLCZuRkY2RN9JkjPR+88JWpbXnPU0rSgx9PXdGUeiD1TrJCNWmAlqTNlrbb8ljt1zByFi9QBInrI34e4OY4EISL+Z0XCCXcEE94sdhbn8ZSAZtjn//cFo6hub/pdae/8Vg3OlpTSPuxBI5X//ZBPO00rhm2et0UDBLBsRsp4OzNHnxgIYNleV2vSd1FUoTv9e6j7hIqgwp6Jg1mnVfj2YIpB2aiuh2pzm2o8IkxP70kFPipzxGdY6BA/MdWzwb0v0GTZzs1jxmhEZ8CYAwFOwoHfWrQ8xuWhL0AAD++csz6k89evYddMyRT80DSermE8qgCSr0E5ENBqNnIAsS5MxQzj2SvTXgfwCCNBi/wNYjlPaQCFXfVdhcBZjeqDV9J0H92FdJOFJlnsoDJXt2C4WR98tiH5gTnU3b2NdXltOZE19SKwDLFNxmwm1KRgiLnzWL/4lclglp62paeWYH3rLwDVRAN+JR2OKqcCJZUhrwPd+SAh6U+qBnAL7wMWKp8j29MGurKD5XQkp1LDCbloWrm8qIcL2hoDyWQAsT17Vg0OkOh385AOaYMSVUOYsLfpWHlqx30s1FFey9dG5kN9wIZ7bDHsGsxoVIpVJPT9KEmvlPFMM9eDDmwC1WsJxg3SBnKA6v/6nkNCczM2WzCZ2fYbb//wTFSIFRRMEN7EZPy6HohHOkV23+qgzKVmwEDVZg3GYKJIti8bfJpNua/oPmnrKgbCa7uGZkjDl+AcwY+oEAfvbNsGn4LW2UUVkjMrn3S5oYLN0yJoByIaoYVhh+21OadXm2Z7Bc1U6xdgBKfDoAERDdltCW2QtcMVpVHXKnCGCjOXCCNFInQgcMvkjUy3gzQKLGdC80rJvAZs2atNfG9AIP5eWxD289cbeKeVQpALAG+rB7dPllkNl2GJpkxk0lkZNx17tKcwI7z3dnHWPqjNzeUy66M9KbAH65y+N8VLaSYxv/6/GrreI/NjOOySlMiUKmHeG1OYjY4o2/1OhlcdxEjY5RyV/gqqdP989SuKd7cG+ckLz1qkqlqhCe0vLftc7Dzwu0j089B2wTYTOqnPvRK4JRrzwgt43HQaKK7qLhLVlre8UNHwqyKmQwxCQAv9nUN5iyk5Gjs5dBci/MmAp+oW9E+HtenfY4FZHw2WxWQsdTCbEZiSBF0iE+TCMrdq5drBvDf5BLLWrMoHAUVjFlDFTuUHajz5vuItunwbeKqukHeeoGBgi+uj3sBo5eGnFHa0oS0BuBLe9XkqKMnqEtdrYetg2juuU2s5bM5B/MYlc3F8jQt/23i2eZEBz9doZ+FC+uhkzxkoe/6brWbxcNcQIS2D3ATA1VifCIX2+fc30p6+UiT3Dwclz3+pRSlD7Qq8Mf445GYxZmIBojPykyE5xOOLVRQEkdIo6wr7IomnX2C+e6vjB5z3QCYqzAClLv1axNRiFeNlH/Rs7QBPAPlb16NQ1ikAiRTfqgrZYa9coYZvg/8k+cpqZZ0VV8qBOmnldyRh5oLZnn4RJTLjrIwtYMVdux0k9z7irbddrr4FayGBQYN+y8ZtDWMGrmmrecFXW/bsvSnO7r2+fRTPgokCO2BOmmzhMJcFRz2oqxxtwGGdnkb4h30xzP7yNaAo16XJ8gW3gv79UIpfj90CW1jrPoh7fFlfvsIQiWaWP/oSfWcrIVSbV/sEHs17mMUZ22ezrMI6EEvpWbb9BYni+hpeW0IF1posl97CxzxWuqwZpPpfPSMi7oazq/Sg1twCzxgisR/hNj7/8M5ZLGMeM8lKGUFdRu4PQo5LaRlQe8SH0salxY6Z0agIM14VHe6e5wFxVE/TKd8qvBY7lWyzJCMc1OTbIhlMAuTvbQFilXj6/5/9CpCBBpvet9a1tU1MmVDwWciPb1o/PKflEsI0pfjS3Zc1HWu1QAaq8Zrvwh5iAZ7iGi5ayNsnLXB9aMDiDZdoigZXGu+CUr7NVxF2NXG2VpCQ4f1XruNtvD8+4LMeghdGW5rdL9lEozfPB9wkOtRWZHIYtgTo3AGdY/n+usyQUDmSaf/K0jDwZv+5AF21ShO2u3oRCpkDs+EplvxJFbuSRztgqHWJsVYWGmCQzznM9V0TMyuT2P1stgXuuoXLdcAte13dzMWdhU8+K75Cu38O424DaInRV8SUm1kxMY/NgUa+uW/oE7RJB9ov41c6egU9oy6/xpyLns5wF4TN8iPrqMNlKLfs6oFk9QvSeN1hecRTsx5lyrtcBduTu3MI5zJBmXItOLDdb2plecsuo9PqCLVhO6cqA0z06VCGzqQ51ipmifz/5bH3WmaU4ERJGfOsv1Yy/AlOaF0dJ/0vnfn+YpnulgxjR3E4sOmDloAiNypl4mkKki7OyLl8JOwh9cM/AAerY/SJGg3utwfrTxx/VimJ5fDgXV/Qi1nEaVIaNhpGAZkE1ekPrkKwTjvDmrAhnNoAARnLUCLPPi2JjDcgj42zN1QJK3E+ekB7Na4tAAAA==</t>
+  </si>
+  <si>
+    <t>PIRLO</t>
+  </si>
+  <si>
+    <t>Paolo</t>
+  </si>
+  <si>
+    <t>08-05-1964</t>
+  </si>
+  <si>
+    <t>08-09-1984</t>
+  </si>
+  <si>
+    <t>07-12-1991</t>
+  </si>
+  <si>
+    <t>+639159835632</t>
+  </si>
+  <si>
+    <t>paolopirlo@yahoo.com</t>
+  </si>
+  <si>
+    <t>data:image/webp;base64,UklGRl4LAABXRUJQVlA4WAoAAAAgAAAAfwAAoQAASUNDUMgBAAAAAAHIAAAAAAQwAABtbnRyUkdCIFhZWiAH4AABAAEAAAAAAABhY3NwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAQAA9tYAAQAAAADTLQAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAlkZXNjAAAA8AAAACRyWFlaAAABFAAAABRnWFlaAAABKAAAABRiWFlaAAABPAAAABR3dHB0AAABUAAAABRyVFJDAAABZAAAAChnVFJDAAABZAAAAChiVFJDAAABZAAAAChjcHJ0AAABjAAAADxtbHVjAAAAAAAAAAEAAAAMZW5VUwAAAAgAAAAcAHMAUgBHAEJYWVogAAAAAAAAb6IAADj1AAADkFhZWiAAAAAAAABimQAAt4UAABjaWFlaIAAAAAAAACSgAAAPhAAAts9YWVogAAAAAAAA9tYAAQAAAADTLXBhcmEAAAAAAAQAAAACZmYAAPKnAAANWQAAE9AAAApbAAAAAAAAAABtbHVjAAAAAAAAAAEAAAAMZW5VUwAAACAAAAAcAEcAbwBvAGcAbABlACAASQBuAGMALgAgADIAMAAxADZWUDggcAkAALAzAJ0BKoAAogA+USKPRSOiIRUYTVQ4BQSygGWzMi9fbYoPCOi/3Klsv0wvHXE4eLIdbvwcbnSx9DPSdjvn/9EvcpaSXHguY0RS6fzntzrxh4U4s8IbD+hujitkISyNDkJ0SYVjnARWMETsYaRIHUamSs382jz+KH9l++xKtpybE2syoU8Lb4iAyVQY+cHxN4T27mOZB4r5vJ+SZ77TfgwUnOT9JaF5qiB8W5X9HuIvn0/ud/E/hA/uoXmvjhVx8TFo8E5pVLZDlM9spMn6wYp+bPt0fUJbv8sv6uOysVHogahnSRYpY88iXsQqVYO74z91vNGcu92IYGaU/vtUl3mm3Age6uO3Muz1AVrIvh8MPLrK2RpSK01dTJOTHjONReyxJTQEaqSYAwbQ7/HZtc7VBAyWWuSk+XBIcEH97NXHIbHg9bnmt9gLkKdr4gMte1YRFfkZwSxv9mp+5+gUZYLEAKeC4KyxwqLCsuvM9nEOz9GQTo1k/CR3RQgpQxfI01ZlF8dUus8gYVYtYmsA5wry1dI94GQTgLbTMuX9bGQklr3XMfEgAP7Ux/TH0J/4YreHDgq7s/4sm4i8+WvGtP67+WP/4MHH11fbkVa1fUR8Y2jWZynLpmQvbW6+kiPDCFJ/nKaMJFP/7/rdw58QhplU8E4G6gP/2mKRwvcqQ+JVhYUI6WTRTseoXo53yYwm71pxEabNEhH2hcnJqAgPsLD3txT5CAVDsJ7tEibaEk9WzzKNlAfsJZkrMilqd0z1YBpJaBl17O9J34I98WQDuWWDqGAfZPg3IFCbc51P7QvHzbBJqs0ZJQpGCH8LpNAeeeXuEo7FUbI4rzr1ydhCVGthNKAtTvxvyGvMDcY0KtRiAjuigxfGdcSik2rktyP0jWpkSOciC+L0yWzJx+zHezHySdzaECORnAz46fUQk2jb/Xe5UDvBIdXjZTA83xfeFUq5SJMMW9zOqmRRrCHSYU4Azy2X4oAphBzTMXTXZdloRO10PoQuJW+hcAXk1IXxuz55sD0ysBvF9eK/IGYlWBYW5Xs09MZssb3/clmWYPQwq47UU0/khVBCQZcgdayEzaTRnVOpAuu5hrZQNp29nevgq6TPCoPly/LGSpshufpcy2U6biTUaMV1Rzp9uvIbh9K8YNVRzxOqWzyF186+SzoY0vIucQEwqSvbDcOctRRykXzk5S2a9vGRvcvNut5Agfd6LCAg5W1jG/Tq6uWjqLkECN8EOpUMQ1ac8Xg4thHzsIVjua1ZTh26xEqrsWE+hzEpthE3e2krbgUwPlT8tq3gfPrIFAcA5LWYCGta8ZGP7U3gRSI4NdACkzeZUw5OfAnOVoxTFoWRQ/rIgvgZ55eZ8HwCAq4kh8XTdJNNkdjhs9OBl29SN72Z+rt9ZNxr3G/Ond5DWNFF05mAcNE2pKzjX33WWyowRG8cu4GeBKGaFVOGHvmCC2vWeJHbfzeV6Eqv/+d45ERzFgl0veFzPsl0HQPeXMBlOMY/8B1fDWVvLA5a4RYjfxfE713D/ddUtCIDiaIUaMq6iZKJSVIxv1XSua+4WBpEqwRWmtIVOvTgAojRDRncE28fOlPnV/SWFWv0VBq/3RGxYvLVvE/XyOPoPyqCVpdA/x0DtiCtH5s58rAZblw94UhLCxN4o6eaOmo9/y+y8YEbCHOWJcwfd2rGNjlHzzEbbw2ZStVaOebuAG/KbX5EHhVh3JSRFG0UFcdRZrDV98LSoxJO5xOZ2oRSykamMlsRterqbcH3rDnHamWqg4Ufz/LpQkWVmEcuwumruAU9IYFU/r4CTSe/b1rRBf4Jc0pZkfzNaNlWHKMpG91krYCxBnThtcgeShMtiD9VPxU5O4Q8WDvHr2YErp4Hl3NAtklZclrTDdE2qftBSlacuEPkQc1BfuB3SQ4w/whck6HiHGwtOPVI3uIOXTA1M3r5u1ZcM7jBiC5308vVAQ1CE9uNeSvtu0QY3hkwo0gkayGa0eL/BerCWXYxrayZS7z2wPVuYx2LiKrjv38CZeb6hPgIaJqi5GP216Np+d3Q1kQFU9D6Ubkx6BGhR/4DXL1WKM9vYv1BkDnBS2P15rADYLRJlGdWO72cvZJj/ktWqF7YfUOBUpkhfDyEi9Goy1aWxdVAjhoby4Lsn5EXD2e7v2yKanfIpUHK6SYqYjJGl+ZYp3RbuiyeVs1lEuPHW/VaJiFYuhTLw5ZDxa+L7JXWShTsUCQ2KWZtxqlcrSqF6QEEEwxY79yBvwfuaJzAlauKZmS+iNJDO+RiyQZVY6PWh1J+78Y2zqwUotcnVc5JzM+HsSXNtEh+/2p3VccEW31T0oddXTtfC5NrjXLzNXAHAJOThVtUM374eADpTVVxQuDwLIBVk+YskAUPLDPloNxETSxC2/kV6nyaZnXsuzB9r3SCO2wSpjQSSz3p/jRjm2qEosS//J1Ifmv6rwsjNINCddFBsMfII3grGGPqWyT85RkOK4/aLd5GeFMHAvIJ7ZPtZJrMpRTlYQ8Le+JybIAvKNtT/V6nnncEuszY2O9iddbw7oTndbs6Tr6GXj4vtHg2aPXxq9XYK8h3tawUy/3/Csd3LJRXEyA/GZJeA9SlCiXHHX95eXeBIYd5ugIRTJsFzx3tY4f0mDDkdTMQhVydiJbmwvzc4Mk2G+pIYptAFKF55XEI0Mk+cTj3H375eY7gFzO27LcIViWgSYxtRYIlU7N1ccFRvI4b/qLoZKdfw9Y1T8gUULsdDl5CcNK8saokM4MySJbYzf5gwmFWa1D+UxdSbu719OX6XQCJVK6wWZQw+trZmXh2xKFiIPQlEmYuMRLsjpjTrER/xbuRSuBYzCFu2PFmJh9FeFqoOSN+SgmmWgQH/kxQJksy+RWquDFnLOpEBFxtDMG8RClRwb0SOvBuQTROXrFTq13q1P9wy3/Pf2zjS0l1MylggFlF/VdHkUolBcRrBBARfYzyk7sQ2PenRl22qwjH69ItG5KxrqDrKLQ5pf1K6BDrd6I7O9y+vURq+wX4dPCi1gFbnpsmAScD2b44MtyP9xSzkZaNDozbSEylZMX3x7iO5H5/Oep5lv2Dnwz2FbYa3PpHeyGuXZzCOHDiVDQl+0iWQnn4FAgPbEwrpI968UDQyU2kQYO5s5TjnPWjo41aL5PdDA6aArFZ9n18moMHnz3L5QhoumZsx7l8tRDmqA2WrwBqTWTnCf9z8UWrvsQAAAA=</t>
+  </si>
+  <si>
+    <t>PIZZUTI</t>
+  </si>
+  <si>
+    <t>Alcibiade</t>
+  </si>
+  <si>
+    <t>19-01-1936</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 08-09-1952</t>
+  </si>
+  <si>
+    <t>18-12-1960</t>
+  </si>
+  <si>
+    <t>+393472944983</t>
+  </si>
+  <si>
+    <t>alcibiade19136@gmail.com</t>
+  </si>
+  <si>
+    <t>data:image/webp;base64,UklGRlILAABXRUJQVlA4WAoAAAAgAAAAfwAAnQAASUNDUMgBAAAAAAHIAAAAAAQwAABtbnRyUkdCIFhZWiAH4AABAAEAAAAAAABhY3NwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAQAA9tYAAQAAAADTLQAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAlkZXNjAAAA8AAAACRyWFlaAAABFAAAABRnWFlaAAABKAAAABRiWFlaAAABPAAAABR3dHB0AAABUAAAABRyVFJDAAABZAAAAChnVFJDAAABZAAAAChiVFJDAAABZAAAAChjcHJ0AAABjAAAADxtbHVjAAAAAAAAAAEAAAAMZW5VUwAAAAgAAAAcAHMAUgBHAEJYWVogAAAAAAAAb6IAADj1AAADkFhZWiAAAAAAAABimQAAt4UAABjaWFlaIAAAAAAAACSgAAAPhAAAts9YWVogAAAAAAAA9tYAAQAAAADTLXBhcmEAAAAAAAQAAAACZmYAAPKnAAANWQAAE9AAAApbAAAAAAAAAABtbHVjAAAAAAAAAAEAAAAMZW5VUwAAACAAAAAcAEcAbwBvAGcAbABlACAASQBuAGMALgAgADIAMAAxADZWUDggZAkAAPA1AJ0BKoAAngA+SR6MRCKhoZn7NgAoBISgDOMEyUTKQuHdHkAw+lVRtbdkBm95w78ThHl881F68FEM01HVzPCwm4X0RbKYls0HDD3MI0H7d2TbVDCDmJUb+lOW8OfIk5rE7r9PbbB4V+xhVk1CCI+T7pXiGfm3jCNGSCvxeiKKq5IiUicczBSWntyX7qIlk0vUL2k6EEl26Q51GFtjEvfn+zLBGx0UXY11Tc5XhWKiNA6ftwmXfTSnVwwxkvNGu8joS6MCzLkt3clv82owTA8otaff58cG2F3a3jr11urPf74zXpI5q8ymOaDld3uAUHgeS2x0nugWv0Q4z6BuXiB3zx3aFmW238uiM6zqQC97yglNltI+glE6UPGEdV2gqxWdjFmS0HYkGw9WaMynSIP+1yl1O3qrqYkSnO05vcRzSwhwfeuT3hqTM2q54r2iZXoD5Uu2ywzYljAPfkpky6nSQYXZpNktCPf0fwFVljLnai3GvksqQXAkzJXZs2WPdQhQCw6YBiJpNF3CBAHBsMu+HYZwRlseh5DGkcht83lo1JDsaui8cw2tAMPYs4WnEw3QGCGW40XAAP7+VdDD4SbCxBzOzEgqXHoH2xWYM9COZB8SpL9jaMh2mYeadIEFQfd7lCbV4rdtlpV6Usp3YVO5lTHUYNAXQm9i6VaxmSUKensI120qCf9V0O3VWkEktsg+qEkYSMCpDWheLHh53JUYdx8HIPJIYYTD5lSDkqxI1CkRjxSuZrY7LzwiQMCCS7+eRjLny3tfpdv3SDHp6tmndxGByj833XYZis+A60XfwsIog5HtDN3rmQ+q9LWMGt7fLqYVDSCBAE7JivYYA10mBd2jRpcbi0JjV6Yb+2j353rmDO1+X5KcfU092vPWoybsOUlx7casovmMbGKZwNwAqCpnZH7PSN8PblpvhAyyxvC8G6urPC+YqpeDTZisItaVjA0XMt2G2AFVWoHu/g0blLtD0b5LEafTUNQA+DwxReI5wtY99ROWQKvGN1iIPB+JpbvnzN4HKjdF6KhA9Hit1n197JzozMdKw+HtQOWxFVFCzQw9Y2rPRCQL6ZhXe8tCT04awajeuyPN58lomrpVXFkB3/gbFZJFBOtp7+dA8N84sFAzCm7mWT15HIo6tDhcSZVMd1zeUwNI+jjM6+iOnnsUOzGvdUmZQpwCZq+TxUvr2NZn8L/YZ8y69o40AulmuMkB+fsLseYTMqj+RfgCBxtsp2gzdtjJYX8UHIYfZCrmJN4F7683LjbmmFhstarEFw4MUWik8HNEBmhsRiBnJTNCXUyn4iP0ui1HCORo+ra1HrH0TsnVbZo5N41oPW9hRaQXutK2HBzXLmA9VovTiM12lCSPa4H6mTwUN0ghzdc8jXmMHKKq/ASYg/6dsO9HvLHsXY6bGCneZnkc6rcHMDsMfFvM7fo06f2sC7EZyQmWF2X0RjqZczBwtuKkfXs6SMGTnRuJYvcKvdBGdpJuj8dqD7P1II9SQCpOQ9ai9dX1AcG07S3XWeBHJbRrqpZzNu9XyRW7A8Ldfqsl8nXwtEt3Tnc0z9IeDaGZKJR03mtEKNLKNxEREfIk5tm17B3uLfQ93LOC/ZPDkZGGwJ5GdtM/FsuLfsHXy56hXzokvPNNZdhxgzlQNVvq84EOiGQfObk3hOYErWwPio3xKq1TjSg9c4vUJN8IPuT9QioyYZJOaKgvMU16rAT4tFPiysmmJJZWeYOT8ZCy9KWSUvM7Ou6Z/47YR1L4q90jiKliBx7UKUcQTANol2s+b2Dyu4QCvYCvs8x+Tzs/7iDXGgXqog8O/iYRbSSGf6A8uPK03i8mT7e7N/ANpRrBhxNj2nx9LaQNDBnlbJa8YlTygvOB6IRiIcHizf9vd+1gquVMqkA+WdWGlz3424VPJG0FquHBMaBitXH2p0E1oZLOKOGfGarCv7KQbz7kfHgq2X7O6c96M+BVv8lUWfP+oUXCJpSOCbwUTUWOzg5FjvePiob59BJkXD/tWnCNrdZRhae/3a2yhEDSGAZ/Xyxi5Wxav8liJ2QFyJ+ZEOj0FSje+vdL1go/qTLtFT25RNY0aD3jOEEZP8RbUJfa9BMabEM40UDXTRbLblIzXxtKJXhsmGVwze/fMV1iZN4ap0y1MuUvVb3DqT/DiqI2RQ/Bxp6SmtgrZawaMhMKgNiusN40RTq67ycYlvOMGW+Os06s55OpiiHvLHGtOkv9EzA9662xc8WtdVUjHz+TnVU8zhopFS12OlNviiMq6Tbn8ZE8gJbfO7O4I7wzbcZkMkweGJHtBrZ7EpHmRIQoJM+7lrZUQ2P27yvWDS8OkYxUcZFrYdxgrPfXnLN2nUL986XsjM/MAWr6EFzQnjL9kBXDXf2MG54hWz1n3yKaA/WsRwHyWHi7s8UoNdnIIE6d7/K/DPkzUrx00XNw8rNpFTtihRIktn4InIEHc4ifCMFXqYJTvM5v7JEVFUC3/RmXVcvHCQg1fTee1PaJ9DQUDAq76nsI4xuSZQoB5ZS0j9eXGRXX68Keu9HfsApOuewqpVxUr06jLwHHHoUnyGnR9rfsDEXCrSwvmaaE8U6tNDjn1/riSgH6Ep1VAtqKyTbIrLqxus7J+CjBFcyY1d25G6Xqi521HtYihbS8hyOIHjfdkUhiiOmLYUlWMor39nwzHrY1tBJqR4V1VNY4om3Ad40JcZzkubBCVabBX2HAYnLLNNIVI0YUqv9KEbT5PKQ2GfW8kvS14sH/gIbuxfCt3kK1VqMak56T+BQKu00UIXVH1ztjJdtQekGJl+GBIGqjXlBMkhGYF9b/uqOmyKX/JQEB5NbwmD912embnlnUYv5vz2Jgcfck3MhlJ+OQkAax9kunC5/He9j/J68NBhSPuoPFne667XM43/ZvuINRXlLFeRXdZfYG3dsZvwuzDloSWKPg1hfn4CkRWOibHnwVIt6fvVJXi0WFXoM6UQvdy+MCjtYN/7iwWIVNcQ3x54PNhbc9dHldo6z1Xi+iHKX4ZnCIJEaP9m8hL245d0/VyCx9U97p5RCctkPs0kHxXwJ1beA4rqMi0jqY0OZaaELc4/PPDOXDm3opFziL1j/QyuNsHOCP359dlRH5du6s7P27bSUgJTXsNExBAkCdEmHtOqlPoK7PF5hWq82kwh+P00X+4pjCPVzFcyJKLLDCc5luP/LfZWsQOwiaYAA=</t>
+  </si>
+  <si>
+    <t>PUDDU</t>
+  </si>
+  <si>
+    <t>06-01-1955</t>
+  </si>
+  <si>
+    <t>08-09-1985</t>
+  </si>
+  <si>
+    <t>06-12-1990</t>
+  </si>
+  <si>
+    <t>+393716284289</t>
+  </si>
+  <si>
+    <t>francesco_puddu@tiscali.it</t>
+  </si>
+  <si>
+    <t>data:image/webp;base64,UklGRoALAABXRUJQVlA4WAoAAAAgAAAAfwAArwAASUNDUMgBAAAAAAHIAAAAAAQwAABtbnRyUkdCIFhZWiAH4AABAAEAAAAAAABhY3NwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAQAA9tYAAQAAAADTLQAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAlkZXNjAAAA8AAAACRyWFlaAAABFAAAABRnWFlaAAABKAAAABRiWFlaAAABPAAAABR3dHB0AAABUAAAABRyVFJDAAABZAAAAChnVFJDAAABZAAAAChiVFJDAAABZAAAAChjcHJ0AAABjAAAADxtbHVjAAAAAAAAAAEAAAAMZW5VUwAAAAgAAAAcAHMAUgBHAEJYWVogAAAAAAAAb6IAADj1AAADkFhZWiAAAAAAAABimQAAt4UAABjaWFlaIAAAAAAAACSgAAAPhAAAts9YWVogAAAAAAAA9tYAAQAAAADTLXBhcmEAAAAAAAQAAAACZmYAAPKnAAANWQAAE9AAAApbAAAAAAAAAABtbHVjAAAAAAAAAAEAAAAMZW5VUwAAACAAAAAcAEcAbwBvAGcAbABlACAASQBuAGMALgAgADIAMAAxADZWUDggkgkAANA5AJ0BKoAAsAA+SSCNRCKiIZorBaAoBISytdwtPcgF8EZ1lGwB55+g8V+03baGfay9OpBG2zfZk17ySjinS4PGojfrogzfRvHvUsU4JFNaEKreUWvt/8H7FeZ3K6nc9zrlGMNJfdZSPU4eeR/AjOIYFJrMJGVWG8mL3Xj385fHJlSs0stnsCLTOB0N1ANHIUYPU3wOMGXAZVQ7sLRDMMoVezdoaGhfOni4qLbv7AUjs2wzYtj4BWXaojShEL0VyDXyzXEHStJYwb1rRwwmijYLthDeskQMVtZy0m6naTkVtdfLqeUhXiwmT2t0ZwF6KCIsaBoDFFmcMz4BPxx2YQtUJLevAsxd/Lqwh8gx5EzHEZOBScIDuNBoqR8zDWRsS5xXGxt+NzE56s2dgZEoXY0/r4GWACrdNCKtquaYOtIAAUKCJRzOvTQAL8IR5wAKddINYQ1QJN9+ezJLP6pKXDt3HjmgvdY1CDZmpmXIc9XUf5Efuj/mMwyaZPhbM+ylCXY5GUhLVsRal/qqp1JkjDIwK42eK1EMQj/18xNHcq+3YUbCAdVfST80PJzdD1YvtThW9SkRVUdODaa1lkja62oekrvjDgwN6KCJsyVRGhB0R2S7q0czAAD+/suoDob/0W/14qI3Wg48BbIj+EpULGZQtjzasZ7Ij23Ye5Wz3nFO3lBb4paNYa5qnLHxZQU8FxZvZC3wbs53uFl8GbpkKURGu4O20Zf6uTA5J2cGM6JBr3vXlT3rMl6VmvODmXem2GZEjzBDto+8MgTwKRmk2QOv7URuwzsUpzHnm0NE1eWD7POzr5pIMcEQ1SbMyT6tfYA+7hU1EI3jD9LCLfM+7B9f5+/Us7R+gCBIUE/R0LTBNF2Eo+W7FqCg2zqXMkLwZUJcNdGR1OFdRe/AkQXokReHkEfMBKMnfDN6vpcYV/SNsmiBi8MWjx3JrNvvK6ak4eh2kopUa2qOvbyBFcrWM16VI4ljlgIQczh5Uaiv1LuJ+fqfKqR/M1mBAdpAI+LT93IvTkuAPJm/FxDOdATJx8s0Q+GldccPcoOj1QmVaBo4+tsWmYSQJfoLZAUTVW3LdK947Gxmyj4H2xfDJzpnS8L42ISWvL+Z0ghRrQWSxQFIcXfBnluloUznWuve2jCIUonVEB1jd5RYL6SlqZeYDC/2uSl0V+Qah4Wli87zcJKi8xJ0BYgVo/f9I0qXRrjFD5pxI6qEqMY8cir8oPteQfYGgeTZCmdxxIg1YhUjF27ML6AkkOoZEpnoizQc3/C8UX6UfsWMhlxMzGmDUBdGVEb7Cih8moY6DdvXiu/00EzNmJx/SVfa1wmwMNGfOeFpN7ZZt39n2qAcixKumQWnB61ks1TKCFq/jr2Yl7CmgKTqzemZ2YfTtJteKPnhBBdaSPnTugIIT0Bos6eoXstvgLpUGbiDjyN6v1MSZ31QuHCIFLvF66Mpr/6R5YyIQgbOogIOX9RBGmahn+BhuLhOicmzY9fWtCyW5JnvgED0YJme3HQzkXWUNV77e2SpcdHXIcd38gABm/ZYeGLsIhReRVaCfaflSNruRk2n43CCLNGHVw5i3ajdQHHFEEdzNICa/ChPRqPpXUr+pgPYtgwgB+BOmCfHoKqraZNBZOEfItMQOnsaQ28Hj8NUNwx3bGAfzEAgohvqe/a6lFcYgWDmKPf9AeJMLDoxRGgpU4gc7tBfkCzK/M+ELOfwe7SV2T4yyM/QSZRHP0045D/ux0Dm97zDI9jECWHO4UhMhaHt0z50mYh7cx6DrN33SmlS7yBfQV3urdlZFxHE9UK0f2MeRhLnkrLAedOr7zA5xVmKNVbe1+DfSUmIKEcuiOojZrp4maeXj1YO9ruW1oPMr55yY7ASIsswCPrzeNYt8iNorhB6dJwoms78jvyVSIcYQDrKPXgBNjFqYUncgPOX7HBub01zZhZwXWNJLAokYqFAwratfsjJIEnL5g97pZrmjniRhXxzW6mzPFmcbxPsnsfY/mAmF0d1vTaul11XG+Llfbbp6oXxVGqxmCoVngLdWRaFmA54+/P2EOoDm2wA6khVUnxdkHNEQzJlHdMugORWpvsg4y5WjIsEqEnL0DfdCG1A6n9GXuhlW7zsB1DDbssd0ugI6SsKwOOenAwz2E7bw+420v2og+oARnjTuZT5q75NcNuoo88ly4rDeOsgX0OThuy8IFI2m9lahuhIN9aGuvGPUQFiVKAk0DMfjwo5gYsQNpoFmlkiUJAFpvlNAsD+Taj1I+k3jhz5XkLCOe1A5CaHVEYyYXpDmfOAOTFAbm+25tsaX98AalAEP5QIJdwcYA4PzmSjZKEhm5NileCSWbXCeVzNa3DImIdb6qlAf9K02Fah8Udh8cjbJ59RHNmGZ8dxOnyGdz6CRmUAkMeWJJo8R3wxU5aLF5OCr3fJHCYStgxkUqDbDrpvuKCW9mSCq1cbdUrXV03fMOEuje4qB/zOvefvpm1/s0HkU1Ka+1h4Dk9mPDvur7kL2mAkkXIu4UJPUJ9jgeSomS/hHfmXAOHMrw2DbRWG7IwYn4tNjbR8yl8kTIlq0qY8OsiK8LE+6clGYfENOUySlAPvbELCd11Dbs9g/j3zlQ/oRm2VEzXJk5dKpEBNOeUxDr/v67wJJEjYuwfy+bxzJv65fWjdOg7RsyYzjMUjdEHuAzUYITvkxQiR5KicNvOwmRyasSk4TFANyQjc4Lg3DAjWEQdzW/YEfbgiUoFuP0we4zO26GU5zS96qJTVJ25pKliLGi4IGJbvGsIGPMTZxODj+vTrZ0MRj0IgXZqKIxR6xVoCy5bFfM7b4lFq400Quk+kPRTwWJRhrgg65eLf1vSHfMWHqLx+KPMZmQkuAsdPKDZsv637l5tkHv9ccCgSVIgb8CAdGWoPPyyciV0fgvpwbtNNPQ3f3Y1loMwaEh6IArOqud17GiK84YxLN5t9qOP/+/OXfdbmX5WdAEXgIwF+hRSs4zY3Cv+/zovbgfcX2xKHx5vnkrXNlHL3emOx/glZsPaQoTyTrDb+HPNBEm95M/nT7yGI9AOTjdjkDxOFyewbak3BpM/xS7kwES3bWytSemvIiGPGarYNov+5RmJC4NehPCyvsNn8d2n9R/u1nL/QDmzf9yYGou+6g/X1ewiXA7Fin3xVkxNpMZ4yc3bt4bs1GQvcqUWKBJns+gMYsYRYs2SETe9N+iYlBlW59rIwHfyqP9F4dHKqvgl8QA4uio6tVgWS5LBfib/pvMW6UrbIBBmVhgAA</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>Glenn</t>
+  </si>
+  <si>
+    <t>24-09-1988</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 31-05-2010</t>
+  </si>
+  <si>
+    <t>14-08-2017</t>
+  </si>
+  <si>
+    <t>+639087796994</t>
+  </si>
+  <si>
+    <t>glennoidz@gmail.com</t>
+  </si>
+  <si>
+    <t>data:image/webp;base64,UklGRoIKAABXRUJQVlA4WAoAAAAgAAAAfwAAngAASUNDUMgBAAAAAAHIAAAAAAQwAABtbnRyUkdCIFhZWiAH4AABAAEAAAAAAABhY3NwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAQAA9tYAAQAAAADTLQAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAlkZXNjAAAA8AAAACRyWFlaAAABFAAAABRnWFlaAAABKAAAABRiWFlaAAABPAAAABR3dHB0AAABUAAAABRyVFJDAAABZAAAAChnVFJDAAABZAAAAChiVFJDAAABZAAAAChjcHJ0AAABjAAAADxtbHVjAAAAAAAAAAEAAAAMZW5VUwAAAAgAAAAcAHMAUgBHAEJYWVogAAAAAAAAb6IAADj1AAADkFhZWiAAAAAAAABimQAAt4UAABjaWFlaIAAAAAAAACSgAAAPhAAAts9YWVogAAAAAAAA9tYAAQAAAADTLXBhcmEAAAAAAAQAAAACZmYAAPKnAAANWQAAE9AAAApbAAAAAAAAAABtbHVjAAAAAAAAAAEAAAAMZW5VUwAAACAAAAAcAEcAbwBvAGcAbABlACAASQBuAGMALgAgADIAMAAxADZWUDgglAgAABAxAJ0BKoAAnwA+SR6KRCKhoRr8hPQoBISxtbkr/7PVLyn724BJAkPhVcjYHZeaxeau6C62YXViS30GWvbG8RNn4/t9+DWkGdNfTDcKmN5hyO+L3jxgahJqLdnNcEpH0lbuweJ8EoSMFFzdloEtw8pkSXYwvi93ync382ylNnFbD+SaFSvBJtLvlWNS6KF/Dt3MXpIUifxchJAzQsOgv1PYdRR8CUlq0mWN0s9P2SHVgM54m4/sj4FUMgsMlCPenzAKNuFN9KYcRqg/6VKW/vIH5Nu+dJuSH+v45d1oQETPOMSctucqTXnpm1o0hA1QWZGc1M3OuiJUPn1+655VQkN58uo3k9ayI53Lh95GmUGFsYyGhOFAU8KbpxOISzX0PIccRnfvaT6RQqtRj1qzSGlZV2wl2KYJ51y7ef/Sit15YgXqSwFP61PLf6zK4WaUq84+D77d/5Pv5A7vuxf3vPMjcfqn9Y1fvEzrcK0XPlrpZp0spmH+WmclSjscj9CvgS1nn+QtFsc8pa3uo0Sr/A0AAP7/KJbc8/y/x1jMzeTuasvih+f9vSKAYdMU2carX60ypdPv4Vzrdu+seMIzW/1hy0vCnBEf4CMdbvZEgaa4gC4IH9h5ENp7f+9Il/jAuJ/LNXT8iTYmwMYpeWZzrmVmkFZdd5bFlHadUKUgTtIMFBdzajH+I/Ki2UJSaxyCahSxdHPG9eSekwKylmxTORS3L/C4Lh6zQKDBl7RZDQq3KIz1IstPIOYQh9FUTGUuHB//g+cdNLI4DRRp1G3dSF/ot09+hR1qbtGZFZsdcgP6aIrb1YcGiKeccQPTwV/L/aP3Cgv22uCHgnZ3MPm+opVA9HGRJ7YendjKBxis1T6unK5l6GJyJY9jHBjNucW/UILpABBMYvofKIq7IMwV4X/oglwjAIAXLnwZ5lZP9H7fqpdbtlFoBvh9Qg83mTrSP1xC1lDlj3lSpB/irGLFUb8ENHBTFod6WcRh1kZ09/rQFUDEU2snFfnGOgMhdXpc0ovlca5OkM3kTq3Bn0L4c/+/WFlaxBOJtUSG4YADAdUI+FQAyliBBM08iueR9AWML+OFK5oAAu0Ht5SjM6Rc4snobwRDUAH6E3z/ooFnyqVylXyl//dHh8saHQO+Wxl04Aia6FEZBj7RZF50Z+F9mDehwWeK0OXL6vBByE0lfZxhfKWRs3uZXEMOP3rqeYUejRJ1XJhvVgytjPrzGElSsRarNW1kwC48L+pCC7RjFvm8N7DI0l4iK6v3mq0oF9teZBnxm8pLNi5b3uCBa3Zr0YoI2XOLv/AYcnx3dqBhO669ZOBrQJrfM/PTNc9tCACDWqK7URJfnbJN+XU7Pi/vqXGQm+crekHVNG7TPpyMvzOH5kGvEf5A/5QpSh6Y0X39b9JqOdpQ2jQQjW3WM4FOrcVv5pPINZtEdvj4vib5o8CZyuui+crl26mH6tSdmYxHQYLinLlnQsJIlpQWIjYbktJNpQbtCawR0Bbt4Q7fSBfBQB9X06oYtyZ1Lbo2tLa8jSbJh2d3mzcbcolssYtT/sQvSGzpvy30U9cV9FStH161k+C5BvNl6YIkVvolRWcUpQN+wyVf0OYBTRGovrx02ThDj79jM/XjhFgK9KxPyDxyOVm+aW9GXDEn+XWzlrJvjQKaTbnSWkPhaoE3auwPArkiHooYi73bdGMgIs2/IC6Sebhu+ccfojQ7BmMdvmCgN26NyFr8jTp1xI/YGXQKnQ0uwxUdAhsKXbi/yS8Zv1/v+XUtIa8dboUGDonWdGCChLve350pU0aNcQ+ngN/gxZsQVq6Ak5M0cIN4h6MqENhxOMlHH0r+URdOerMtvrbTZimMOJpsfdojwcXbJ0aLp0CNBs5gHGlr/Gf4xh3SbTRUoxhlIvAuGSIg43xfJBgKyTrprGKUh+Kl1Fg6BK4yBrBrr0bajAde8O0awlXAPMtozzRWsf4QKhZPSX7SoKX5jkJDkwopklZQt6pyjnyLHxUZ8WXgFfAB6KjBM1uoHRdRrHbHS84r9/iD438N+YfDXWYqMA7Nd57Co7lXEq1/W+vCT5XxpK05hQD+ncld+HevC6tIksyOIbwKXHpsW0AKuQAV7s9mLnbHO+RxS0k7vC0YU7ytU4tSYHn48X+Lb2ZmIwjgvNwzhixojAPC3wSX6hI23oclSpU37fXkAKi3YkqWbvvHrYxoTk3bvpQj8X63GRrL57tT8pDjDVenOOPLsNshjIeTjJL2JxXswSeQsM4wkSjTaZEGi5WzIwoZFiR9HfL9f0L8mgSh54QjR19p0oFiZw7CvCFhe4hwN7TsRSuwXkNyF/LrLKBpNLcK9A2I0tCJSkat6zqHyf30YkmKH0qEnHIuIakGHPLGMHzgWNlmt1E3OxZgzPcShSFQ7xRWfEobmFymVq3Hj0i2/P3v2A37f/YFRCm61maqOAzCGVO9Xs60yqqUcsOJ7QEsHjTMBtULkaLmKBVHGUh1XXKTFZIgwpXRwgCnVyMeMryD+LYSt8ZtQy33mQMxhioTXkeBAHn5WM5lXqc/e+uNVQvuIo8ilei4ci5zAYKQW431bbzpl/2he+xq32nahULEJXmK+rm/938IgaJbTSS/t28WEacUSgvbD9qgf8yL7L4vNtUdyelHe9ZhSiGl+TlaG3ZmWGPKpFtviIYMXjyXnXP+Jw1N3GEAtQPcyQWMastINUZ4UDlvLnYObpht1x4a4bCvSKMx3Gjfpvy8oy3Rr+7n0y+fvhIGrASSgXgR2Q7lyy0x6mjyyhskxxlDKVVUyljg6LTNGVAxBlNieIut0wJgsdnf66l5AZD/VpVbAPr2OjAKNxKdbYHqyafGVip3fa1G5xnVa6OGsYa/yquyOAN94LRSiEOBkTnoo7v/o28Ts53+s8WzaLO2Efaz1eFTfbCkMYAAAA==</t>
+  </si>
+  <si>
+    <t>RIVA</t>
+  </si>
+  <si>
+    <t>Emmanuel</t>
+  </si>
+  <si>
+    <t>17-11-1985</t>
+  </si>
+  <si>
+    <t>31-05-2007</t>
+  </si>
+  <si>
+    <t>15-08-2015</t>
+  </si>
+  <si>
+    <t>+393715798768</t>
+  </si>
+  <si>
+    <t>immanuelriva@live.it</t>
+  </si>
+  <si>
+    <t>data:image/webp;base64,UklGRqoNAABXRUJQVlA4WAoAAAAgAAAAfwAArwAASUNDUMgBAAAAAAHIAAAAAAQwAABtbnRyUkdCIFhZWiAH4AABAAEAAAAAAABhY3NwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAQAA9tYAAQAAAADTLQAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAlkZXNjAAAA8AAAACRyWFlaAAABFAAAABRnWFlaAAABKAAAABRiWFlaAAABPAAAABR3dHB0AAABUAAAABRyVFJDAAABZAAAAChnVFJDAAABZAAAAChiVFJDAAABZAAAAChjcHJ0AAABjAAAADxtbHVjAAAAAAAAAAEAAAAMZW5VUwAAAAgAAAAcAHMAUgBHAEJYWVogAAAAAAAAb6IAADj1AAADkFhZWiAAAAAAAABimQAAt4UAABjaWFlaIAAAAAAAACSgAAAPhAAAts9YWVogAAAAAAAA9tYAAQAAAADTLXBhcmEAAAAAAAQAAAACZmYAAPKnAAANWQAAE9AAAApbAAAAAAAAAABtbHVjAAAAAAAAAAEAAAAMZW5VUwAAACAAAAAcAEcAbwBvAGcAbABlACAASQBuAGMALgAgADIAMAAxADZWUDggvAsAAFBBAJ0BKoAAsAA+UR6MRCOhoRmqHkg4BQSgDFv21PfJt5D7mPoUTfkrzeyDF2Fydmyn4hCgQqIQKHf8J3iHYqmw7fe89rMY3N6mPzAtIfRnVCU5z6V7lJV0e+2wyornvHoLyoiF8rQXtPUwb1d0timjbHQBAsySe8ikA6902PH6rw6oq3XGLO2pjEX4OOCLy2H7Nz5+g7zE388+ZfYsZr3vaXyai0k6ctCzdVTg04JzHhSAhR7kfZJXAQbMeXuF7MaCQCu/5G1mrhxSFYmk9f5RAqCt88EHWHDhvH2jVMCIuM71Ixae4X68rUis8iNsRViDEL/yKKm58UDL6xezVJ89H4YRB0liAnp4lvtnToh2jcsq8k/8HuNyGWLzaRkyXsckfKDACg1zVNJ/IfBbmmZOJZX83nGl5OQjppDp/hySsEqAcGI6JFQxN69ndEU5ZoN8OtUwX/UDohWdTXzxgGvW+HMCmMY2nwj3UZEsGpef908R2B66zGlUnt48T3qmK31mkD8bwt+ExkoNui9ofbfea4shlJ/JQjnJ5h7C3Z+sF1rrtCr09d3yiBkk8kr+WUiJxyYSH5RzpkFm71jyrN/86VQgGPqUUrqrtFifcElm1VqgFXqWpmG5fS0B28Y6yq3nN63ctrVtaPL9x7zNpxeUzN6BaanR/CJ0aXSJhjcwMEMOQM8ttCXH4mEur581LQ+U8AD+9VFQridm1//CLejvn1UD/1d0d8+VxFdzrw6mYSB5UbGmyrjUIzR+KtbGZ9TiEQqB2BgYqUWtfroad36iUsGS5MB1kgXbRt06EvrJtK5qfOHetm19IFP7H9EJMUmCMF85TSJMRbqNJAiNIfbfUh+vzcWKDKTT8t+70wZjYIid+fpB7x9mp/qg1d2uXnOOauFqbMbHqSiS9gDcSZbYwkFft8fui54Sqps9Ie8scEomSq/U/w5Shwtd+LLxmxEOcVJkjaulKQW/GqFwLfMZlz3lBMg566To59XIOmnPw5iTvspLiLXbOdFWp/45n3FbkHoX+9lUuxzbOi5qNTl1TCpd3pPPQGQzrbFcehtY4kIqoq3roseNxu9Mfrc7NbpLW/3d9o1g3Jv5Z8+2bLKs/PPmUk53fkXTUI7dxzUegKiZNutJoYknWKhNuA4dxrVs9ZqQsD4/qTFvbz8acy2aPXvbsMi8Jkck4hZFpTrjnFEG4mxQqaVhsee+ESkZ50M8xjz8SCgXkhf0fYqfg0jhmHSBYbZlDd3HqeO8r5bMUcA1bT8pc3tlvOu2FGanbBsK0rC9ekSRKEaVpNfvIccG/Q5oej1sEqR7x6sF9OaYV29oxlykAio49J+sh1JRwrpdY+1ds76YVhDH3WqwtU2pOFfiSpJD0VGnAy4+zCQV5U20MRfFlPMu6wOGyWdBSuDZgaemwAfpm0nrXEYkIHw14kXTBhe16YEn8oXfFKwsREGmaeD8hgU0ynIvY9NxVi/GmLcCIKc1DYhVcNBzCraE7X2VHCc7SOp+2P6ZjLwwfjsEPAB70OnqRKCWbtV7AYqiaB1EUsd7t3Q0Rhhe82Dybzr+U+vgMPUQATO5tedPcnAPmwl3nlIKgsfEIC89eDTQjgegLgJBexaF9/7u58kQMxtzPwgmmrjGe9fnrOcvLl1rqZ69UKPDxvwBdIlurEKtl/Frgo5/HuH6wd+3Rv/nItoebklemKI7DP9o/2s2ZrrviKn9NPyq9rg17KZ4QT0gJ+KhrSlT9piT2WrwSzsf8UHGyodvgKCWXHkhYj76o8zI0xoeWWOF1lX5iD4AOqbblTX+D47hlUIOKmP4a3/CKDPIR7cL/gD83T0bmwCti6wONr/80rF7IQp8KeufSg1T+FDzojxWSBUtUuYOP/RIqYAzMyFA3JZNlLPNCSA7t8ggTOLkLycSJIaHXu9H6EEAnpC0+XEa+xNpwxb4BBFw+MC/DfCcMbtqJumh91+Qscd810dE73J7esjilcjnWeyOGDareL/J8X14/tR1GevFau6MgdQJWX7yZs49UCniI7OpLJi+6He0/Ij9tGvnXmlBGkInyU5UGLecaWC9VJf6lDka+/E9oqbKu3ic2rsNkV5EkqGlfHR9cKgvTvT/IQ37kKWie8dt6Z3ho3KrJYpTxfC5CEaztH03OlvGF38jSmioXa10NU6fRAb7l/GT0zCTbTAinVmAUcwr8TF1qzZdU+oqorXBj7+YSx1MFm71kDpzQvj4glV0DvBqjd1awCjPu/I/TsFdhBscNMToKwTHZYXlCu1OETYOPdu5kXniDKQtSav43EEHjI6daqyrXK5q3s8v3nstloj7ODyz+bPc/5CqO2ZLXlIM6XaKmM86bgA42qpKUsAD7myKrMzrV3pfN1YtLFnPisoUDEhpm//M/wsJg4Um39Kgmm5muPwF6eeHu3MRsQpIQcEJJ6tgykEs/rLY4JhFPFyl/OFx0My0vu1lu1Cgw+1LkVtbP/x3Q4lvepWak7WZOpiVqU3cRLd1ObjwnCHyQPABqrEAuPicmx7+MVgMdFoWlci2bSuPxTQz/an6yMibNMzBQEAMJGiUwV9tyUl9/JSfGcb+3R7kMqW5DWnpd+PyssbhIh8MNZq70pFjUKc9ptYDOM0/rDX4zxny29FU2s8MUg2CS3JNN+FSfskXwqzikZi9uH7w7Q5dHHgi+pVhBxzhVo4423VB5pOQO8FJeJCOYdDUMRFFH30+oj9uZJmFbR248aJMm/kbRde25RAWvEk8iMtt/FQCaS6brIaRH1zDg0UkU45l9AD0ZOHBwcXFAwX2sRCaBcqNcL9zbvT4LA2Dj/XZNcwZ1ThFws5hCgT6qcrw0Kna9rF+B6yI6V7Il9sOmv6qYH0n2GODvAoxIr3U+AanklWvi6dPQkvaJFdwufCuRaIfeN3wo2Yipv9jwOUIe5zpLc5B3Kvd4CVwnJ9cMpK6f5eGL4LRGBL/V1I/g8ryj2CQzHG8Lru6aBAA9vrJIddiiu5lY2ncC5c+wlTjpxzYEzRbXF8t/wZnYAsOLwIZP/9sWLG/6FaPk2B4grDURq1LaEmGHxvzh5P+OHdw0xXUfYA6xYLdJxu7bICFUvEhFwYjR5nD5u8AtPKsFN7dgYhFA9O/ZwF76aGEvakSrrbUe8X/voQ4R51Eq34gmH3xjbeBlWEhzQ/CLnIl8qLwtR/zZ3z65LjNHO/05rJ1lVZeMsBU9XJb8ow0B1Wf+S+VFr3NoyqpvnDlNCZ/BLaKzIhSKdztkMzpVZYPHmUlRJBaZ1+siwYAA7So6/83Z4fkirwys0sjVtp359Ffj7pc6ndlKSwDKKp1MuBH+84pzLilmAQ+gi7xhbRVc/P4PW5GOOJxqVn4UhA4fowydUd2THrw39VXGE9VZT9tn1mvGo6cZx1e3aNcN9tYQL1jPtp94p6RErfc5kWOMxJwN7L7hZTr3Bkjs1z0mnkF20kXv304wDh/Dlu1L+KRvOjqbSNq9hmDV45Xzle/xAh2g7P0Fhipzxa9DSpp7E3nFdvrUoRswrqPTTYEx3IuioZ7axkhnsqUnRUBkpSPWZvvQEIidb4lgK5ottWgpIfScoUtz3WOJ/RO9LEB6Wvx5P684Zf1FZ044gpNe5EZXXdwczgYU4gxbgeiqwB15NtvHWjnfMUBaaIAUaritHFywUTRVziWdO6WuVGcIeEOhrzbXU+S+SUiDxDkFYJyT0WXrNJuZpsOwcuRSG04RIROTbwosDkWcHkGF205xk7PswzrxcKuDEqQrvjfVV3SxJhnCvPgjM5+7eiCd/kczokc2Qw9fPHGFJUEvTV/pvQ4HmfZyUHBWvcVbD1cr0F3ztGrsxkKsEnrNdTFSRG4DL6BHCrKtgfKGYfVwIMKueSaT+55vMgxegAAeuXxLNpvHHbgnd3td2xRMfzE/qzvVkdeQAv/2mYcYYYVcAkXAyJqvJ7GOhFmIAPd/DOU3W8ceVQr59ktrE0BKxcWwUvUw27PX4LiFVDkpQI4Xcsda/4ZR39uAAA=</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>Martin</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 22-04-1994</t>
+  </si>
+  <si>
+    <t>07-10-2018</t>
+  </si>
+  <si>
+    <t>+393248423057</t>
+  </si>
+  <si>
+    <t>martinhsmi45@gmail.com</t>
+  </si>
+  <si>
+    <t>data:image/webp;base64,UklGRooOAABXRUJQVlA4WAoAAAAgAAAAfwAAtwAASUNDUMgBAAAAAAHIAAAAAAQwAABtbnRyUkdCIFhZWiAH4AABAAEAAAAAAABhY3NwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAQAA9tYAAQAAAADTLQAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAlkZXNjAAAA8AAAACRyWFlaAAABFAAAABRnWFlaAAABKAAAABRiWFlaAAABPAAAABR3dHB0AAABUAAAABRyVFJDAAABZAAAAChnVFJDAAABZAAAAChiVFJDAAABZAAAAChjcHJ0AAABjAAAADxtbHVjAAAAAAAAAAEAAAAMZW5VUwAAAAgAAAAcAHMAUgBHAEJYWVogAAAAAAAAb6IAADj1AAADkFhZWiAAAAAAAABimQAAt4UAABjaWFlaIAAAAAAAACSgAAAPhAAAts9YWVogAAAAAAAA9tYAAQAAAADTLXBhcmEAAAAAAAQAAAACZmYAAPKnAAANWQAAE9AAAApbAAAAAAAAAABtbHVjAAAAAAAAAAEAAAAMZW5VUwAAACAAAAAcAEcAbwBvAGcAbABlACAASQBuAGMALgAgADIAMAAxADZWUDggnAwAAPBEAJ0BKoAAuAA+7WqpTymmI6Mrss3BMB2JZwDP1RJixN8c3vxDv18t0SfO/2c6jvfHjj4j/KPUF9l+c7E26Xjhefem5a1ELCzHyne7zzxWtn2DFbhemDhWdnYLSPJl4Rk9JolAKrwSSZL4Mk3Qhfr4TYFJEH0tt69TDA/8MG77x20ZGhR5JzmbaW6il4avByAzKb1SZOFdDJmtdJHPQmPiofRIawn1p/HUgMAdYvUbEIH2N1Gr+bGslPe1CDJfU3gjUWacg6lQgWNnuu+wT9Q9ils4jcmvuFhcvDFgcq9nWHo8fwrdw45FJfjII96daUupaFAnmpjjSMZge9ac+C+uQmaH8BDN/OXxmwgtlmSbIVbPYS/IF5v/iLNkAZwCJb3GxXRmv3NUWMCeZcyHBaAgMjATwApQIHM4IfCRfZNcxWX19mKzwGzJIZnni8sFG6nG3XRyrq0e0w8w23THpXDSxGvOqYvcljiUfjIBDLv0j8KxDkxtFTpEilcv468KzX7NPyDGwgVG8jCcp/QcOT34az1MpGXPxRzTvJDa2i5clAjaTaE3aRrOtAdJCJSZJlQpJ4usIsASgc5lt/XEcmpk5/VKBeLVrCTbvfPwnJQ6U7VOHbHBIN+loQbAkHX4mUI6HhIosWcQjO1AzX8lJthHkxLXWPD1L0Dzn111b2IUBvOT/kPHXb6EAdnQD/Rx5Rf4TVhEpXIL077bj+dyeSKbu4cMhoMxa19agnEuS5AAAP0QuJdlbYWWD8uZ/NuQ8R8MHNZ+Jzk0xp7NnXPuM4ELYcvQAU1y2AxafaNF0FFB4/ojX/BSYKeKRNfgKDsGXp4dJCluBq7LC6/RYTYHYCJ3PbufVHXMrLoGtHwKldHxZkUMvGObxG3pLac6panhytVUOpJQusjX+aKaUDC35sX/XWRAcT/W+NK356nLijB8A4yBQZ/0qXwCbrmY7CM9fMZQjFL7YVwP2uE4Uft9+ZM5y7RuTVXYBmzA3nMCXJQDBZf7WJvixCwSRMGDikLPOYEK7njIacA/aKUGechFNcEebf8rxnt0pNhXSWNQxmPvnrQOGRJy4kelbCKFrHAtU2E4sxxxZpSXFVTv/Q69Ij3AzHgnJykJnXqluyOyrmMHOXxc8fjOCRzWNghXE4XNrt+9E5cCMMuTplVJeRIDR+2SbkFTaJXbHu9LxITBr3cBdFz0WMsRRXr5xHf9AgmqAavIxNtE+CWPRKyymyTdpLxq9S4q4yptvwyVaDkcwBFWwyuo3gXc9K+sejzBHqfgdhtXVhjXoSv2dL/Q2CD7xVisQHEaOqrIleireC5i93QmfiIFFjuMPAZFvEvd2pWqArjz5vncSPMbxO7ng++4zPGy7ljaiqoCpY6YFTP3wdL6lmCeX1/S3G+cxJbLBNS/v1adDslHhcpQi7hdLQx068nnThxR+osNtUuwEHO6ITccIp3CruaW4kuhsSoK33dVq0aWZ6Y/F7elwAh+LC7O5VlRGxpHRZKcFwXpFoDZwXlbh10upWmuS0P408p2CdAvwUQasq+m9TO4+ukBXcLJX13k0Wcgh65OxhZLuXec/nwWiDOFfykz1d2MDpa0hJQrqT3uw1XR5KUB7+elcam9GmKl7/SLwngPl3FqVGxTXpv5yJ2lWzsppegsZpizbiRM0kdsMQi9DpDPpz95ASulU7B6wsJc6KMnUexw3kVcsMRiL0DC6EvxgaTUEnjhxdVC6W3xLqmdIykpg5Q/btAQ1TyPtYB4ywGhAxEd6YbMlnANgKyL1otEyO31X6e95nhNtPNVZjxsDvMuNvZ/LNn3UmidCcq6nTdfeZHlEE0aaes5gTEXSNman0ZC5q8u2yY068aKqY3LPCRXa8cGGUv+i6rEQ6L6bfJ3OAcwnAwEEIhkwS1lZ6KaBIFxDMeqDc0RRqTA61uzEEiS/cLgwyis2+jJ318GzTnkvud8A7y3NQpytH0AruRZYiz2DPTdTRaNGYYgLyvqSF8qnzNFbtxxaaHrGqlBPSZoEuB4eBVaAHU+3GKwpMW14pLbNobwhWC+3+bTDqCrPZSHW9c6y+kALcMCZ6wKne07gXdLTBbjBtoHHd9ZgQBAmiyzT4aLdIPoMjsntTROaH8/isJOAKWTv4Z2rHBlL6KpyjoCdtjLEQr1ehwJ9aRBWmu89ibuHpgkw/FBuqPHjagePNKpIUp12YMRaFetYevQHMyD9fEA8xTq18jIJ4LyZjjerm75w1bEXm5OvAH+j9c6SJGgum67UwgC1JnRlUvT9Qg36d4isH1FtPuev2ap4N2w8qKNF2azpsPqJTPQHitEs3ow4eUl9mYxrFd1gvOav7m5TxYURDurekYfvNpcbr8urLNdfncZ6yN6+KRpSSuAqwyso9YamPJnSaS9IuoAXabHRtmQldc8aK+ASZRbC1c14ZuTUFWPiuYCmShR1CNXuC45goTfaGFW9+MgL3R6/t1R4TIgBcFCJtQfJBCvP9Mhy0E3oTUdy2urKm6aGvBb7WHrLqIuryV7+T/HaHsHsR1u1hnf0n+QkZXZcXW8Bf0oqCM2bmuI+dITSY7NDYoQxcndNh5ghEavazpjpgKFSgjLS2NMlAx3hYNIQJlUyUSyDQ7WtTPHwuoPp+xWEB7ZIIidKgi3Nq9RmJu75YYxObGoZsp4N7ntv2phVSnSOHOk3Z2VUL8Sriifrt6behY6tDbLIKDFAbpntvp0HfBw0AJecdKkqhsfK7ukUg07JJsDyyikyr8ICwdoJ2zTkqzH4NIovwqBHWb5rBQdDrl5f5YdnHxU3RCBcwG6x94RTslBBo3Nok7VRchBgT0GoX/gZ4Ue73gMAoXzu/iADcuQy9gZx7ufBWcRehU3jgZX2ervCxt2Ubg3Vm150wgUJ9BTnHj8zi1aQ/6llYPKXszpB9nAjlOGI2Ifu22cpFEj2uzbQh13OkT0R5cUpDOqAu0kdXf5v99SNjlCdMAVZu6PduCyg11bnb2+M2YK+EOdZTEOykzTFfl5vcwfKK5bIQlT6x3MYgPwRQCcTK70EbkeGC4N9viJQHNdbGTfpioznxJ8D6FZy6AQuDArNX7eUNbRfC7HJolg/L0lDmbYP7UNy/MSiOeBMVt+DKP2/enrwkuXw3lUlrA7y1aYx1z3aEJT+Pgjl31oVMOy1VpnnIsuBcpw/Ni1UTd9IQWRZ0LbTBS8f6J9e5ZZnE4+wrvbQ55edf9ytjnNxU9OXpETaCqNfS3p+943ENJZ8xBANw0v1xKB3AMflNzbp02qkspBkm6EozOKzTj7e+p5yqLQebnPKAhDCChaUx7T8mQLbG5Mq70+jEbfpwPQGgiX4X6AJ6cElbRhKPknrO7bqVac+Bw+HDw8JoAE+AqZk+OszyWuvGf22TdoQgrssnKmWksJhf/7o2Rf8ziRaXvwQ4p+X41Om1sW/b1qhzNLijAtq0UdY0Dg25gXn60/I8vWEG39XdnebIuEEdp6/xXSdxIoFXSFuVsoXtHeNXeRRfDtMceallV5uAaeTPAoLqXiV6Hki9+q2QB0g+19vQKL7uL3fISgjUoC5RX606lkJlpL4Hg7mWi5mkWNEliSfZ8KV701XtXtG289N/zqrqPac0xE5xLNB2MxPFiWNBr5XLwO90lzmc+HQhV5cjGTNvpbXWF2X45ixYhi0z/eBAnD5hPaClPYEbXsqDDAL33wAZCqadgChras8TUEFzuZGLQ+Tg/TwC9I8QgEUqHeLTjxEG50fWaqRs/67LvOUJQnARNpHUdS/M8MJdyHwNjnlf05qi4n4nmBl0kw3Hh9y0wjgyXoZaPjmZDWQjUO4m3ZIPU3OjzjnAAMzEuGxfwi8w9Udw/hB7dfBIbf2lgfCHYiNKhyVMPEZD0vJq15g8oUMOwtvCE0dwOg2+CxrPdrjlA7WyKgpx8Fx/IEOjyVcR03lVgU//svEepgfgCVVA+wCjNXQwwMfpO0Ka92Ru2No/6N5LyFSJpVovGlOp+0bsGZt9iEDdv/8ZtyY/nNCMc5607WJw6oy6vEOAD6NpiH82OUUcIiSDKFLm9grml34euVxqWqr+xEdl1n19RkdQMpYOjHmcQP6GCv22CuJnN+KwpZVaL3kAoiwu4hvzA6ixLSUXaWUo6O4JQ1jBeH1O2PePbHm9X7KPlN7Boa15nOWlhJyx2lOcTZc5kdwQwCxDOqS8EDznsVYyFZPGyYBq9a3RADpHkwDEH/3xdxLpEAzrYSGvWYt3RraDD9GrF/s6BIfG61v3iteDx7h0VOABIn5+oIEXiVOMFnVin62KIjaeyJ/wGfzFJnFQwAAA==</t>
+  </si>
+  <si>
+    <t>RONCELLA</t>
+  </si>
+  <si>
+    <t>08-09-1946</t>
+  </si>
+  <si>
+    <t>29-09-1964</t>
+  </si>
+  <si>
+    <t>+393393249902</t>
+  </si>
+  <si>
+    <t>maroncella@gmail.com</t>
+  </si>
+  <si>
+    <t>data:image/webp;base64,UklGRvgNAABXRUJQVlA4WAoAAAAgAAAAfwAAogAASUNDUMgBAAAAAAHIAAAAAAQwAABtbnRyUkdCIFhZWiAH4AABAAEAAAAAAABhY3NwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAQAA9tYAAQAAAADTLQAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAlkZXNjAAAA8AAAACRyWFlaAAABFAAAABRnWFlaAAABKAAAABRiWFlaAAABPAAAABR3dHB0AAABUAAAABRyVFJDAAABZAAAAChnVFJDAAABZAAAAChiVFJDAAABZAAAAChjcHJ0AAABjAAAADxtbHVjAAAAAAAAAAEAAAAMZW5VUwAAAAgAAAAcAHMAUgBHAEJYWVogAAAAAAAAb6IAADj1AAADkFhZWiAAAAAAAABimQAAt4UAABjaWFlaIAAAAAAAACSgAAAPhAAAts9YWVogAAAAAAAA9tYAAQAAAADTLXBhcmEAAAAAAAQAAAACZmYAAPKnAAANWQAAE9AAAApbAAAAAAAAAABtbHVjAAAAAAAAAAEAAAAMZW5VUwAAACAAAAAcAEcAbwBvAGcAbABlACAASQBuAGMALgAgADIAMAAxADZWUDggCgwAABBBAJ0BKoAAowA+TSCMRCKiIRn6DgwoBMSzgGUaUQzch6rC8rMYnSWJScf9pEkXPAh6b6F1SJ/lTteakeK51xqEMRsHt8v8IM5/6OfrLc5OArojxu1mrRKeglBLUxwCrkE926xqb/VAmbhz+F6NLla2SPoPStUA2ZC0R/j07L/q0HHrl0VxFoohLiCehYdU/JuPRNVKuCvX9vAMluiFKTT0xxFeMIxku3l9+Bc3QuALFDzCcF4UTz6rNpVKtDk8AtglUtSKAT6tpNJiP5cd8eFbUhh12wCigzDFTMI1iTJ4F9UG9kshkw8cFxujfQ8aCe94KMZnJc/CQUQIuy02H7t4NXavmHoibgwTw3olymSShQ+nhOw3DqNGaIQAfoGQE5CdlwLFPTWf5olaVp1/a/UXDRMCtoSl27p6uLyva5b9l3gyCflEcCZHWTpflXRTpPIjqWCv8d64XBF4eNnhJKlwPBaCCvAEqYx7KX9E6auCG7UMV9Ox5jQCbF01mqEJQWEKX/SDqKDHr1AklId7lr6aYxw/0ySx+Q4B2dVWanZ2sEUgVDR/q99qZ5Xarj29JNGAoNHuDRxFeXL1k5RObogfDuajWygEu2xy47m9TOgLPksBLOOp/iSNZeuJ6Y3XlqLFlMJyafC56x2e6tg7lxqP3eeEJLBoBSdqN1aQAPXfVq/6J7ALQrXDir3F4qftPUAA4mGujdMX2acUHRfel0YHdMhHISwmL4ysAFxB2FxnmChMBx6X9UGeclA7cw2i5IDif85R+VcgaPmd9uKFP52O6lNWcIUFsZLE9jQ3yVsy8GzgLvaCA/SX1M9dc9x3BXhXlBoz6Aw8m23uT4Z599nt+ksMVd6NN9Of0V4emK5+2XUFOV7709mHi51O7SLtvnYaY677gDYhKP0zVteX2+wJAqu0CNz9pBoCBk2DLk63Lq+bjy1aPrK+aYXk/1gscMXY3OYTGRlr4ZX4WO+0/yONT5W+mcMNz81WNfYSDnxP+kstFpsXowlb/nXeFCr6lO3TBOnu+P2AwNmyCsDAHr5jPT+Qj6X1bUDJwtTiRrMVi1BbEa4pgDAgoo0gBwpOMlX0hQZvuwpbmLxGxt7+J9ER+WJe+4TAhKVKV0hp8kKjelp61r3jYC5hhKP+OxEkpAG+H7tuh/qG468YDXnirYv9FMBv3ay85tAN8lc+9hZMIW2f8y2GXYNXC4Wnc6JrB91Vo5zhn/SSqZgBaZSiVDpQkdvNZMlv/GoRxlLf4gwkTq4U+i6bOj+sjYVkstHKZ6xKpFMAutSC1U9paOFTLsoT9m7WFR8Q05hsIHKbr9YMJcN0079GTSejdvW3KXo7iAUg0BiGF9CuLhnCrTSWZK08h8GQ3GZGdn5Ib2lKGP2R8riEPjodYI0LuqayM374GmlNDh2KFmlQZTpf/Vo2A1cUkvmZ6K8OBg7IUMcDkFQ5KDdgNbnVQpifrRFwAl9fL0xFjQjOBJOWPGz7afASmWEmRKsBWTC40FIHthhJ7cvjnETxcMOHs0Exmgznk7zUd6sxRK3VZa+9UONcLHNktND7LUb7EQbAucuMWp8SYupHqcUPsjzsSFUxhz56lpPE0Cwle8eieCnhaXheBqTKjMkfZM/ez6wxTCiK2OVkU2NFe90hJfjcLHaVr0WnyJNNWCGR3siW0kPuXhDKPEmDdNkRWC/Ther1UtAUEtLtqzEUa0ZgG0wIp9i+WGa99DCVUuaQdZn1QMcZeM0K5+URLu3MKeSO+9aZiVWZXt1jnM5BLm92TMXDZrp5bVSLtIhlS1lkOx1bBN183WCIg84n7UmEmnnsshH2JzSIWsrS2ygwA+PJR3dVXLdeImFeVzgyot55cMX0dNag2twmAG8+Z0g4lZpxvviGBhvv1Os0f0k8fQt4RSAf675RW5eSigjz3VWTabhz0XdqdptE66zDqYTKZ2Cmu+aMHSrJ/jQ42C4HsWEO0uexxqwyMLqe9gAdcbFCe2fXw2YUMzBGFo8yBTqw8WZrT+fqJqirAmExrzOoeyBiec3lx8WobdxXaMa2urMX+V6BvUIPgSGTWQRMYyyB6G/7nZBm+KUqcSJesAL6H2jnmj8YSelIuNSr9I1O85qC3lb7eO21nwCjFOlyK+k+kq8OtDmw2V+lyBxVd85Zu2Lc/fYKD97fjWJXjGsRUXqqSQ9Yz/Dv7kQSnvJuI72G5eUNtAleK161z7jC/Xf3CCFUMr3+k7Ois/NLUsx8aOCNrBpbokqNHTgoJqzPJEnaLEOBm2912qY7+Fz1WUnhw2yXnEO7FFa9CSweBey2xqkL97MvaeGF7Mald8t+qql0R5yIdJfghWdkxHH87RZRjQxcH3zwvjoa5vLX7uk5iE7lyaSmHWgVt8Ci/UbL9kbbicz0xjLG+zkqjzXwyB3Hw/5vrgIoulDuIxN0XqgHIWsjnTmhUWjgUgouIxwOJj6MNiMkSlKirHY+VmTE+mUFyQM77hXQYvJxohAAoSnFPrSVufknXDgVEEN+2RGWrOY9R/vUuo3HBm1MmeHNfc3j2bErMnsqcUL/uYErn25KvDK5W085BwXbkfvKGfBoeLTrKu8tgnTVMhgzEO71cWVQyrMZInB9p/IvmflMDJ/IagvP2EvqVJEQ8h8s3nd0w32I4U8MltCusJ69tZwm1RsZgFJbP9KrSNfAhHD4pvNA/s8HijLQyV8cyK/+AT81D/xi0v7NxeQ952l21Yk0iQeD+wXmoXCtnU3U15bkaj47HCqLoNmTQ31QbFltuTC0Hz4krWjgui0x4m41wtwFS/mCp0XJo/Iz01//VL/h1JxTRX52RYH3P7KxNArhZhtmQWwRz93zcvQ9w3jyWNz6vdpExC+5zxeGeFuEr3wNZ9CrWC/VbKhc8iRuzwshU9dImr6h4Xh4t8NDxxKhoT4gac/IeDsRuFEA0WqPylUjwasrglna0rPbexs9tf0zbW9dIW0iO3JzNAv2NUH4/kc4WlQHN3G2DfMQ1tAfYDPJKEfbaal6zyvLsw0GspypLCmnyZI4mcidaoyhKPepGsqVh/GxmXBUI6z9hXsLTDP2PEea3GIHnssKfmlUcdttnHhOOyWiWU2UWV2byyiFKCwr2tzTZgVw0HVOjNHQNLtW7jhGD/R9XzXL+GmRC1tVoeeRxzx3XdwJLJQkiAndiLdwgc6+89V7+EXYV4A4JFvdENvmkG8+vpReuNIFTUtNFg46b5yRjFtsqcJW2hCE8YFMF4M/qKyniJf1xXXSWa6EbOgJR2N1kqYBP9c3+3CsYzQVddFJNRdidsXinY92QRz/ek88PHnNHw0yI/ta9q8pMX+Ga2TE6AmiGxjvuDMF97CwHMHDkRhBKwy4RWx/Tp032QZYYCskztYg5XZiIwzKD/tO5ypM1zmJcD5ssYBjWmrEsohTuWM0Dk5tEueNst46ni7lzUp5D5sCEUAlHWCsYdeUhSCb4HlArjczSn2dUC8OOzl//DEuvEaFKqpx6TOhZD6fPJDX1lAK7Lw5tzX9lLFS5G1uLsNKNHRWMacayKkBdlMKWTB1Br3RV0iv3+E0rpJX2ptSgNjpCyxuCOkLb6wlT+gFD6Ku1YlkfdwMteDUPhJZz5Hw+ZD16adh7n4a+jrwVJuCf5hkBfTB2T53jfsZz4l3hYhkHXCS/oG6rOdYVVtNF8Ro0RZythzWtr8rU4yoo1ZNdxEDaW5epJh2zjeOlBQlsP9SqnIIDsrJBIC5JhFmq5F2GWLj3hjuHG4hMXOdwoU/vvzVwf8tOvMj/Gc9prvV4WDsy4SYqgOzNhQdo/EDYpLum5VmkaytFW/e8kVUs4WgjKWxMAp+zLbSJ6Ie0rGfN9tqqW9OCBx25KTLq2QvBbgA11r6PMLjqkT5kDOzJm8PPeR1YUtzsOJAJL7ECJWbDtSUT0EG4Bffl8WUdMtff3Mx4VRx7PvlFUeizkJrpu2kuAUzBI8VDWmsnXxcvJvWnMk2fohj1uqx/Fs53MOCyXVWv3piHxxb6TfC+hXz/tqn51CCAXvMO3yJrvzaexiwc4SKv45M9nF469JsSSgUYHNfzLY1u/CK4AgFCLSRfaAyt3D1qetHLyM0RAPOoAABUbv1iwGCGAA=</t>
+  </si>
+  <si>
+    <t>SALVADOR</t>
+  </si>
+  <si>
+    <t>Kingston</t>
+  </si>
+  <si>
+    <t>16-12-1977</t>
+  </si>
+  <si>
+    <t>12-08-2006</t>
+  </si>
+  <si>
+    <t>+393665241723</t>
+  </si>
+  <si>
+    <t>salvadorkingston@gmail.com</t>
+  </si>
+  <si>
+    <t>data:image/webp;base64,UklGRkYNAABXRUJQVlA4WAoAAAAgAAAAfwAApwAASUNDUMgBAAAAAAHIAAAAAAQwAABtbnRyUkdCIFhZWiAH4AABAAEAAAAAAABhY3NwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAQAA9tYAAQAAAADTLQAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAlkZXNjAAAA8AAAACRyWFlaAAABFAAAABRnWFlaAAABKAAAABRiWFlaAAABPAAAABR3dHB0AAABUAAAABRyVFJDAAABZAAAAChnVFJDAAABZAAAAChiVFJDAAABZAAAAChjcHJ0AAABjAAAADxtbHVjAAAAAAAAAAEAAAAMZW5VUwAAAAgAAAAcAHMAUgBHAEJYWVogAAAAAAAAb6IAADj1AAADkFhZWiAAAAAAAABimQAAt4UAABjaWFlaIAAAAAAAACSgAAAPhAAAts9YWVogAAAAAAAA9tYAAQAAAADTLXBhcmEAAAAAAAQAAAACZmYAAPKnAAANWQAAE9AAAApbAAAAAAAAAABtbHVjAAAAAAAAAAEAAAAMZW5VUwAAACAAAAAcAEcAbwBvAGcAbABlACAASQBuAGMALgAgADIAMAAxADZWUDggWAsAALA+AJ0BKoAAqAA+TSCMRCKiIRl6BlQoBMSygGSHKG2PsNVR5zAkP4xBy7g5W7Xb7G8vd1l2VEYe0nSH5MdYEGYvbprurAopcIxpcg+RJ+3V1nKAUh6ZmlE0D07qBbBskKks3XTNH9peBsiGyfVBeRc4PR6CeXnO8vyKhSRhFjcwhHfN4w0So943VvwiiQCJ11fWtDtfYQ1h80aJj3dHehXZu8c3mc/Xc4a7XYHqzTCRgHxXDufrG93rt66eXexBGStqUHrugGNwpeZepxh2wFA/Cdvbfs+eZIMUz1REGo+f/R7mtFSu3XT2kH+wGiOvU5W1/x6/reuugudnA+shEhFux3YVp6XAn9cY4RERCSE+gHfMwWWAP4LdzVG9FQjRH24drOO5xNQk9EsSscnaSbKM3EimtU4OOn2EJD4IefU8VkGvV17EXQRBiIfYsGHcTiybkgf5fNIPbjKrS0+5Hcx8CGs0UUW5wyWV6Tiv6WDZaZhx+vcPDcI0kR2pPkrfZCkWxbsDlJbVZBPey4DT0O3dsNTmOgyf/o+CHJk5ouupq+YUhO3ATj8/0EefXsPgyyUjhoObzjjWQrYqh23WeyYFRVcSN4SI2yqan7IOhkOZaaojPxTqnxBE9I++aAe45pDM1SougdmRTuNzwlq9BLlInrk/feV1fc5Btr5QWAD++ZC94a99yzDryXVyiMaQAXxRXftR1hYM/9pO9jEXX9HM/FT8y0YimfElmGoPWNsby6Ie0dDrJZ6Y23g5jh4+EqXHDaMDAa7nn+B8GsFrNZhc2na1Bg/h/oA8oGU0xov9GjI373pg0gRa6t/zee6TatPWRuR3asUBoilb4Ql7rWzMs46eMwaTU/uMxV9j3vdLi+2Kpt5PZ6nveTbwHOZQ/bSg333JDtdKekTBuvvaJkWlF7oBe/JO/SboHdv2rnwhYa5/SnmSn/N5h+6DJva5FJugPhikQMjq8wz6THBa8Fcr8C01rDHi8eLAGhvGaMLbPwjE7TAOgML2MFvpz1B4LeUmCpmtsCUSXlcAzWbD8AohzN582jwxOnhOcXoUefpTGg+SSo0DsBpg5WbkC6iMoJ5k+R8LLXxnenx2qU2BBBuEMMZvxNv4taUWMAsP0JV+qUzbUkr88wfPR1DFniVnI3SPYgjMXEm9+l4eRqAyaOZkJ541ds1FCtMUnxPW8s8JGJYsn4O7M8uhFhKg5E5YG7SQxb9FmukTLxkqdDQZtgL+An0jTVooYlHqYLhnhsDP+Ho4VGJn1gem6G4HnQzVt+FP1c72GBIrJxKp1sHV4jj34LmjVjZExDjRLjh3t2/WCV+mhXRHZT0LvHviEs+nKbOoIXfyVFgqmaqsm5puzlAAyrBCtN/j+KLF/1nXzF7hGqqns1COk81hEkCmAydqJTJ0DmByECAKQcORGGhJeipeb253xF9rXRtmUY9FNVzopgDtdq/z5/zd3CBzuG7+MfE619WSCwMP300KgJSAj1dZhxpIm7K2XxXvYpDFVa/wwomHkR9pGyIUlg8pj1dyxq/N1LCWWQseWxIxqImw++BV5VHCG3bkqHB09+N+pQaSIH+YAp5WoyzBydWEwCGlfLpYJRfEM+9NMzEu5hqML6350XidS8YHZj9QuC192p0Qh/hYXNtr9P1SxGdfRONVxeihWrVmJxekpzWTstwwlEla8fd6E+U/xDTCalq8VpJISq8SxWNzPXS0ExPwKFjM3kVsBnbFLSQCHV3NsT2KVjdEhv3oX+HsoU3iQfQRaRf1lkr++GtFBTqgYvCGckkDaMl+ajtyhwpMIjOb2p1isu7FVmEgAzKnrXTsUTTEm+zW8AqXn+rH3UyLzDXTdToGFkCTFw9IKLN7GAuawNUKf4zNXS9EKc5CiAZJnH0jPlIRM74eESLXj5iYqPFPGYBw32+1/YphMP5KNk4KHBTXRElR0B8DzXSxbw13ZCV2i6jh3ndCqesfLwR1Duyi00zal9T45CJXdmdXrCg4I95eM7/Ynx25eb6nhFmp1nZCDXX3/aqCeMtqxPyrrk+7QBF8JqhlRhDz4o+K5cf7LJkUbyt9q5eduyIZow4oqNvwjfEmTXRH314XJs/OPa69OEObwhaxPzI6DZIY8VpaTMoT9YkC5yOMd7mCKmkWznYnKVK7Kps0W2lPaqV6XK01tPYBdmwoGTIYiYiZrs0F24oiveqCRMV+WMAxNYcqqz+U6o6O4u0JjaN4Zfat2LeKM6dkf0HF/gbGFA8BXNJrzVrB1KXDhTxWo4/CuzJ74/RrYCEaba1Hlj0oMZLo2/zmt/3syXDyZMMMh4Z8x/Rgr5jhp0cQbO+xGucVgNGibsn8t7B7HZeDt049mbotI0A0mkCb0y+eGzVHeqJQOE0RjXawJQhddmFNBbR6unkLU+hUpXvYr3Lqxh2bOsQD9jEHb5eAjJUoPx8XOl82UmWgtDuwlyzJxLv11dKz4zXmgHzpGo2JZZpV+YLazvolWSR2vAPzoSL5tTHyuv7O4f+q4SCmhs0Br55VSkThV1KOdI2ixuM/2smkvOG8e72awOjTBbxCZoOO+heMSPsOMS+dGP6nXyzmITIUsjP0uiHnp+WTBbA7qI23BPp2xKwPn8UnSgqtjnUEnwlCsINsOx4hk4gi3Cff9QCV27pC18nzlMc19QXNCfU5Z/ELvBkgsJsY4mCDbKgDLCcaQ5WAp44zBHx6qKAut12n/1vFGE9BOTu3F5j5BFNOI0pia1xcMd9WUKMspTPG3xJYEGLPW7ZBqRr2K+LZRMVHLHbynWo7J1yq9aSDMZqpYVPFD+77b6XmPdNmnhFJOKzPkFnXg8j23PzD9p3RzBXYoFcR/9MNqXCx/84EXKtH5/tPUFqndHeq0C0f78h5B37fJE+UQ9aigrsTPZbi/ZYP627XNgvyeztcC4xIO3w91UR/I+Vfp2OD19DMErwLm+fRIoJNyh7G23X5u4A6VN0QmxbRXM5VkRQQS6E9BCwXtRCJDifihlfga6GKC/rPBwmlePRffRW25sU35bjT60XIbrVcz3rabTvVt5qSGxC6cv0wltYc5LCkIKq/nA9M0ibBr/mdNxT5X1q+druUn0k5nb6G7UlZheKPeVwT8ZBiz2gAT4lrKWmtgqXPMxTZf1dvtMOdlOjEklzcIIHXBsyik0wnF2/ciz+gDZjdFSNHHGy3miYEg95BvrwSxGnzMIT2h1PfZsYIrJRHVM82UmgXyrdE33pdi2OHwF/WHZZzdHAaIoAzFLmcwAGmNG+WFw82DBBZo6sy10O2EksPrBBKu1nrm+vruiny88/Le8dbl0NcNpRxa0L8vP0Nbh1Ndz+E0CoPQt1/Zm1HjpMYID4BHAL6b8gLblk6Bh00SrXU2Tv51LqUPLXMwW8qlyDSY7vbF8uxJvoUUxBYoaP7N3Kn4rXVE7FYCcOtToAq94SIkZ4ln3W9BpP9pslPREwYWNgweRqTuF3UjRi4vG1QZyrdEn28gq5fj1nq44D0RYRzqPEk+8Je4S/BF0PxtzumOMZxR88IvRbs2c2vQLcLdetYnSRvVGT1TIa4pV99ierWXumqsCQHZqwRbu0ZyaXsh7FZ1R5On0ga4Ioe/O0rc1mn7kuhcGijYAPAYk9BiYpYjmRdLdeTtY+tNR3a8nT7kTIHPZyhUrWkW0cZJG9Iz98tQKYlnV2ia6h+YImz/yemQHxsWBy/q7Aj+uSKzVmxxWCLFIeL3an4jfvnK6Js43s9HidbTbZsOHR4U8KTrJnagdVYFEQjnQGA0CHmxLycvIQf+mMm6RwC9jdlWoHYNToKn7cGrHPdVLU70QRrl5Z2DUkFVYumg/vRAOcyDJ00rAAAxql+7CviABI0c4MAAUP6/QAAAA==</t>
+  </si>
+  <si>
+    <t>SCONAMILA</t>
+  </si>
+  <si>
+    <t>13-07-1947</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 26-04-1975</t>
+  </si>
+  <si>
+    <t>+393394638370</t>
+  </si>
+  <si>
+    <t>padreascon@tiscali.it</t>
+  </si>
+  <si>
+    <t>data:image/webp;base64,UklGRoILAABXRUJQVlA4WAoAAAAgAAAAfwAAmAAASUNDUMgBAAAAAAHIAAAAAAQwAABtbnRyUkdCIFhZWiAH4AABAAEAAAAAAABhY3NwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAQAA9tYAAQAAAADTLQAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAlkZXNjAAAA8AAAACRyWFlaAAABFAAAABRnWFlaAAABKAAAABRiWFlaAAABPAAAABR3dHB0AAABUAAAABRyVFJDAAABZAAAAChnVFJDAAABZAAAAChiVFJDAAABZAAAAChjcHJ0AAABjAAAADxtbHVjAAAAAAAAAAEAAAAMZW5VUwAAAAgAAAAcAHMAUgBHAEJYWVogAAAAAAAAb6IAADj1AAADkFhZWiAAAAAAAABimQAAt4UAABjaWFlaIAAAAAAAACSgAAAPhAAAts9YWVogAAAAAAAA9tYAAQAAAADTLXBhcmEAAAAAAAQAAAACZmYAAPKnAAANWQAAE9AAAApbAAAAAAAAAABtbHVjAAAAAAAAAAEAAAAMZW5VUwAAACAAAAAcAEcAbwBvAGcAbABlACAASQBuAGMALgAgADIAMAAxADZWUDgglAkAAPA3AJ0BKoAAmQA+TSCLRCKiIRmaVQAoBMSxtLKs/NLvt3SQjnRN2zc38MQfuIiu5TtDqTGjMNE7J1vI3E9uZGIOV4XxF8sihGj0KB9l0VYkkhtbM4Gf0/Be1hwxFxh9PAiTmVO/7Mm3UvuuC0dS2a7sSgXarPe3peKYQOxn8uZRUwFixBhYRFNPnKHVIwiBEOfpfT9yHTfoyGF2Y6NB+KPo7iZmCxhNSuBbJlW+zfIJEiBHzkDlmm3wFFkoyk8rGNmZ678hcX7GmRaeBASylE4wMZL8F7fPgEoevwVYnFj5LikCikQjIKhHYspFaYTcO7YExXC/kEP6oCaFtg3R92k9eZoSEhy5mU4isOr7dAgt1Uc1aaOxQ4+CE0gq7QZeEmjnSRz+hpdBc13VNSxI947Bj/1QDhibHq22LuZLgyU3UBqYYq8KDhTHwRvpdSv5iKBtW6TkABcfajL9YuEVDs190ltVE4fVf19Vol2B+YONAkAA6Dazz44yIp5TukrD9uiiQdLR6PRKVbqZR9n7OswPLfsB+qGxVv6E8Isy0EAUOHGwzShE+cQPTeUSYIpL2vbq8dgJjMlDx6KtTKtzv5XJ+BUJGlCHYAD++Ey8syiC/H1/rj/OxeSYHpD0hOLU1cZVANW8wKmZfnXpkhu5cQYBZQPhpSu+3maVV4zeabcWp79ouLE26kqW/Nr2vppQKB5Tyktwe1agAfJr49pnMZJVBjpd5HiJyvLGnLZfPD/2rLBDByufLq+qOCi/y7TuijoQlAAQDWsJHYVSM6A42JhZC0Udv+AdhdnYek8o4+gEBaUmYejwNWaI59Uc+KaLBw8bOiCK3apa3R4R6Q8CAHVeJJbGgooZA9ohRnKUQm8ux7jDeUOOltuKf7ZVxZDLGQYg5WmKkYGicjk5JB4Dtr3WUCMbEPXMbbZaUB9bTMuyElH2cEdYTJBOiQVUfwRVfljMEJcJTTjnXnRyLVm5XMRNWrtciQcuXdFQ2hVbn7Nsv8Vdpzdqw2wdZ5QlmEZC2rSiU7UoY/2iFZIs7lSJzFE9EWYUt+5njgO0DUEF+FUEC3xJ3I8ufuGqjGgmiY8Uraj2NC6ebT+beI9/pBGhK9CLa3z2Wz9sRyUf/eMyVEtQfOj8fRoVLf82d2QHzFXo3poLCV9qLnLEgeqvbRlU0xpRoGJkmiBH+sY4sRGg7mhWZgKDLYGWLxpsN5E0yXRxEICx47mkrO6oqD/+T7FbF7Bot6ug0kOSHmvZxN30VggdKPhqyhQrOf/aYYVt8ZrbYXv0p91NZxXyrfyPxpRzbzZYng1dGwWnLh00liPeHwOGUoRJh5v+xQcwIEKHpP2ct8ZcB8k3SJQLToiRKVIhIDTpCTOzGRhu755rWjRUhG3WEmAm+ZIX2EmLtc3gi0s9/Xx58l7iiudjesUsTVS2TM7EeCfznk0Vvq5ZwsGr2GZnKdpiaYiJO1R7Du4CzMWXA/7qJDh/1P/Sf2WDuO4iJ6/n6sGQCdIDBEQVl4rDikjGn+zcFdCydU39CHGdTCR2aFtULTma2e+DOgleTDKhwOm4qOisxaCIVuMgd5XkyNzIA9dpN/eyO3wapusVieV5iNFQH9suWq1d8sPGIHxjgVO05uuXZisoydiG3fy4ZJGlY2aMFvX75bxgr97Izn+JRjGaIyJk/0GlsU9A0bdPzzSfOZjQ7LxtHr7eqhxD5zShO4AqIdJs58z8knLB1o7a2QpKW9V+S2fCVs6M+PrfR6THSnwgDj7x5sk3TCv9pBhALj4uaU5h//fZNdxIvoGIPA9wEEMYCOhnlTPQ2XHovfXazKC+/NUo/AUBPJkpVpxS0l14B85LHZncyrBTX3mf4l/C9gvpvLi3h1ZP1n3oX2wnQnwCXLkZ6L7/Y8RJPyDc4GEx6mC6byFpuJve74PbiW9j49ymj86SYvb3AU3ttvI3jl4mLHYlznX/b7oPJnE4/Wsb0yHMa2w/DdSEnvlzQgBcOJ4TnnxcjhC0iK7iwIaqreArNGi/ttkT0Dbe8WXs++ekecIv8ld6Kfrjc2OV6geSbBqh14rLNXLTK6WOPdDuuwGTxolNv7zL/oqRoQ7QTP81kjUmr4C+gA/wNGouuZDmbnQ/OcGYPjIONnPGF28Scho2Fx2WCRzQ2pQA9yqJW+3Ol/ndLFLjc63x609sAoVb0x1oxCJBIzyEpeP1lBQ93Z692H9cTfHEoG+QRgTFZtGBxKm4o0i2sg3ygVRNFtJhc/hxm9B9b4Ep/RbdKAN2hWoF81ACVmHC1xSDaZYCShVMLqTLtyqEosaQhIIJbHN1WXpnu14HNAwBCxJdrO5HgyGRPPrp/i2G52e+23yH3lXUAsR6eHOcGcncnQ3G93hwr7kl+E5/hTer61TVXzKnSTpc+LvpKPe/ntf7xdGvbSvnr2NUEEeIq6jSf8W+1D+1zapoeq+IGesqe0fThaub2sAUUtnSjwnVVrllVYdgRYFCUg/oVpykQz7VKb4upzUZl3hpF+fLWQXpaA6SodRb+/nPTGR+BNEsIw8/IT80qhn8PAAuUHbuNt/fO7kP5nzYU16MSDZeAMtSBvkdW01/oL1Ylur5DdI/RqXn6v37/xoy7E+8BR/ZYyWT0+Xdp6PXf5QYP/AYtkB+/jtNFgizAhqExXnbKcv+3jVP767GpNWFK+7nWrIgSSof+Ah5L9/b40tV+YNTbAlCiP3PIP80NH6w0ebG5R8qBV6whkvfPtYQZUGZghIHNxIEfhsKawmP+0mem2gpnp/T8Fqf6aEz150cyE8Pn51PnWjF8leXGt7JVwUVgyhn4dfJbTnGgkns0ta5XLuzt/mBSMV6Qpz7/AhixDugGh7u0kJvmx/ZVbVt4Gj8rL0qQO0OHXGkMMB+TluOlk+R561TTRgVFmbkz/J7HmZ60tcGbwWq0bMTCuQw1t5sbUMeV9nSZSFt2Pn4AkmeZMZfTWToG+JG55x+heBzFX3QK7uO1UGx+nHs5gdCrJQzzM4Ua+MFAVkZJ7kL8rr0TXm5ofJlA654BVmDI/aPOez8yG0f0m2oJWnvQV7sDxkM6HTF6o0HUp99Ahpzf2z3xLkOy3Wu/IRi5oKjSS3A210oHpbflYtjY/rTFD9WWhzFCiVEFUr9vs7Mw3BYHGDESjBYSezpk6zpkHQCFqizdBb25xLcH7HFYlhKt4/iQ+BDoNXUzQaJqVQ0u2Kgoaa6FVFWagPhehEbXwLuXA/d53Evl+rxHVac+GicQ6u9bhvJDUrI1aqTqmlyCV5AAAA=</t>
+  </si>
+  <si>
+    <t>SIBULO</t>
+  </si>
+  <si>
+    <t>Rogelio Jr.</t>
+  </si>
+  <si>
+    <t>Diacono</t>
+  </si>
+  <si>
+    <t>24-12-1994</t>
+  </si>
+  <si>
+    <t>14-01-2026</t>
+  </si>
+  <si>
+    <t>+6282343976530</t>
+  </si>
+  <si>
+    <t>juniorfsmi@gmail.com</t>
+  </si>
+  <si>
+    <t>INDONESIA</t>
+  </si>
+  <si>
+    <t>data:image/webp;base64,UklGRlIMAABXRUJQVlA4WAoAAAAgAAAAfwAAqAAASUNDUMgBAAAAAAHIAAAAAAQwAABtbnRyUkdCIFhZWiAH4AABAAEAAAAAAABhY3NwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAQAA9tYAAQAAAADTLQAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAlkZXNjAAAA8AAAACRyWFlaAAABFAAAABRnWFlaAAABKAAAABRiWFlaAAABPAAAABR3dHB0AAABUAAAABRyVFJDAAABZAAAAChnVFJDAAABZAAAAChiVFJDAAABZAAAAChjcHJ0AAABjAAAADxtbHVjAAAAAAAAAAEAAAAMZW5VUwAAAAgAAAAcAHMAUgBHAEJYWVogAAAAAAAAb6IAADj1AAADkFhZWiAAAAAAAABimQAAt4UAABjaWFlaIAAAAAAAACSgAAAPhAAAts9YWVogAAAAAAAA9tYAAQAAAADTLXBhcmEAAAAAAAQAAAACZmYAAPKnAAANWQAAE9AAAApbAAAAAAAAAABtbHVjAAAAAAAAAAEAAAAMZW5VUwAAACAAAAAcAEcAbwBvAGcAbABlACAASQBuAGMALgAgADIAMAAxADZWUDggZAoAANA8AJ0BKoAAqQA+TSCMRCKiIRiKvlQoBMSxtGys4PX1nyuOU/GMD55BLT+y/73jhxOHgDJEePYzKD9YGdilif/D12rVCYL+pR6FP35D8tuUi6O0OjptFTnyiZcsSKIstLQUoVZ1AdInmsP3uXQN01k77KhKMR35UQsssf2isreB46Qa3MvPD0R/c4O/PB1Zldt6QMfOXUWkxXTOOzzDsw/BdXMBTe/e2KZFLSUSiMbCU7ej2/cN1IesVVdftqZOcITnRl1TzncNRdiDISUa+qYoAWso/IIE5R7Nx8oy6CRvyHNztcXxaDDs4sA1zDsySO3lA9ooj7ZQv78HXMyhYG/MkQBt/QZfu3kbxd4T3U2OpLib/m8zpZodcTnUKl/AgPY5FaL26RiFjAsH0KIKE+SYponIVIg6TLcIiTVW9COSYOCB8XtmCum5wvnImjo27Yw+wJ3o1MVPRmQ+PA2OPtleQZNd0wRayMLy8cnc+1AK91ZqISec4hHR3Gh5Tcr0K8AnJGe8W17//DMSy3NQ81K8KXtivMAAWNMZ3T+iOBJcsGXfbSstxFCaDXWoxkDK4eeYGFzrIkkRAbukTVDd70VjCuIGeMaUlYpKWZx4M8tiMQycd1/jPVrLNylS5yRSH50u14xfI49xA+8tJtMMAAD+HshkD0jZg05r1cODXO8+WrvwF6DMJMm9Ll+OiHCiRmRBcDAyreX0WClSdAbksr/29Uyu2tksWVRDB4Az6H17AdfSyqF+j7Dy0Smt9QfhjYKfNaQp+JzGYyp2SeB4Zk1WWyB5MTNt1O3R/JdJb9oylF4SAY5UCCtD04fLP7o/LdaLwBbvwUS/6fTS/Iia7w9ijHgnFk6fk6V8hsQJNKAC9WitiHvIx7RmPw8ARxPp6JFykFJs+EmJqout3lXO1r0awUyj0bQ1oTb6HjWmisOt3kkfbTk/G5ZqIFxgCocs0btGqXold0zaXNckDLo5mm8iugKhZv7bk9BOpDo13VWK+XCG25TsMv9ZgdeMfLanHUWCvluxxBcIIwIOdOLdLwsVRAi9WSOlaQt+j1ZI9VNJZouy958tL9f/QHubHL68VQv8P5HtrozQmSk9OBaBQ2zNHQwHEjobtjwj0ut+iaebnqbIFng/QQwcEDwPu6n4aQq6CGXA1YK1HPSla7nFXAykJDl200XqOT1G4QJtH2cxSL25m3KFoecsOK2JWXV+HPts8gzK8yh7Ao667ejlGYTh4RkxxVWQg2pFDaCy6ALniqFkfYq/SI0eZgyQQNvxJTd3CC2Q4oZHr5trMaGdGpaFGaS/JHVqhTeRNyylQLo27/kPHUptxBugS4GFTmAF79kmVChllqG5rrOPw7tYSrlsubkK3FutIBJsRSRNz8m+RdAECRmrQ0umep1cdK98IW64LXko58ZXD8Q7N5fJ+/Wm1SCnuCPJX14v+Vw0pYcxcnmZxRB9BzGKiss9ttMin4aT83GH6Nx3xaYUBAG1BwLp8Qr4iCeI0bVMlJvMg2RU9G7XUHEZV0wlraw1nwuqvriG62n4IBRcAgumR9w954dP2T58zNpNtAPw+l+jSGRRcyuo7P5nZbihyjYHpHH8a4p1byWFMdGGjeWu0jk9/TrI9QQJG6qanZcRGDbtaG+eBdKuottuDc+NUxdRY71SeWuE29i5t7KZHsp69wLMX/NH4mJ3tQ61Rqv9F2uus5P+TJo/Ev0taEZXW9o2A4uHV3t9HuxhJb3Qa5zNpQ1NSBCyr4ahix1GCK+mdYijwPUikLTUglfvfST9paUXdu9DCB1vuUD5joFrgiObCKRKFsmd7KuoEn8KlURLBT01AdhSW0ZOlQc+VoLFp4yb5F15P7rdUNfUzD5yIJNQmXGTZQBtpc452hKyCRqEhl5mqJnVyBCip+s4D5W7ry8fGO+KOhFHB5mYj39/v0sT0L4i1FF1Wj4fD3gsYgV/cmohVFcJa+ifI2KqfUdJQZoIE3xSER7mvuqmyi7K7uBZQoShdyT5wu8Ao6arDCUDtjyixXt/IRvdnGo+aB2bfqfYxwfbQ2cfBB4ZLZomFqr/VvMaRTAY4ycKvMKt9ySwEglhlwn5E04zXlbJ/ptjad3melCqdsn1YicrzW/JUpn1olZeAAcfCVZmoLvTWpKlj2C+qNPP63TZT2AgPDQX68Twl/3utdT1mdkD5S0vWMvgytPshplQy4tPuXQSzSYIXi7MEBw38Cxzweiaxjsv5vZtcW9iZghxCAWUAwJZjTEDdNfncuMmncpb5ThlgdKdzJ9Pvssqm59k6fK1+APwWhNVY0K+jWdgH1BLoa4IlF3CSam9ba9giD80wjSgsdXqNUCJCpaeuNgywodEDdMjKq47Yiq4V6vBPJ7yc/CttOrs8xzETG1G7G9mmo1Cv02fzOGvCgd5LVItZA4PsFRdZsivrI9HZUooUfAkVxhIBQFQlmTLQES4cAm7vldErVLw0mVnVQG1sMCT8XISovOSHiQOuV1VnPTbzD6OxXv6Y3J04k77vVVpqMMnmnwC+l7i27koMrvKcVrD9kRVlH48K2aLihBIkrZcI7iwSO1pXTUbQe9HBj0zFctO1a+iJXRXpigIZl7zayi09j6Mq3o+NTbvUqVHOKdnbJkYQp/pIqUx9qSif4x/8X1//FDxW9GIse1SgrCFWC+KHWUpcXv64cD2BOVJRrEMVRHeYo8TyEFNhn23Cwx+WoQQ6PuiLXlBIisDHHZJMoa7J3DnuQxg6nhCOzS0iYMSq0Vf768LjATm6ddeFna9CaPokNsCwmvLI4JY2W0ls3DmgEG15fMrLCdbLsQHpqd09yavpVD5KhxHnvr/U/gQsLJl3is6Caw2aSREnyq8O4SuxNT3qR+HNo+h5Y2YLtJ0Knn/2qvYnKE066vFZtCTgDK4ydSesxeB0w3K0vr85n2cJCvF8k6Sfbpr13LIuulJ22LdIHtqo3qRqwJJellif7FvAWHRYlMnrphJxcYu5NH9fpWlodnGqc5oEo3jwHbhXmL40tZKK3dIP5BgYRZi2HbDqN83Pw70kMgX0ltkQQwXHtiDbEg9aKQ/DPK/WYSyGdvpy5LCb8+a20qyRV3UZUr0dW16pdB1R/aZyZHPp5FnRJ+ZuHGUKY/Qboz8LCwK53j2b/wQBlK23Vg8ijWkRTpMgKvIXA6oXW3nbVXaWwI6+ZMl3+dHTMOBsd9X9pYsoxhciReNh2iIlWO8XFDP3sGzkJ1upETfOuzcNUMHKd9hLDxGOsBoNbvrCnqvFL4HGb8ao8H+53lSZtw1pELwi4VmecNIjusixr65qBJM1yry4ZabHuEWVeAo1mPA4ZtfXMvnqtkWS0kOZhgcrVVKB320SKX3OKozphI6uPs+IL5u8MrKW4pLTzSylS4TwNunk8LHGG3hp79a43H0ynTjZZNNulpZleOX7qSRp9F89ceUa/ebK8BQFV6actMSDxFIPCFjUy6UUQBfCTZsD9No5gaxwtQcigDvbUTh/JvmBX0a9fdN0c6sG7jHyIDwBUJHBlC+ydnj9MiOWKtdwfG9QAAA</t>
+  </si>
+  <si>
+    <t>SIRERA</t>
+  </si>
+  <si>
+    <t>Rubén José</t>
+  </si>
+  <si>
+    <t>27-10-1956</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 11-02-1984</t>
+  </si>
+  <si>
+    <t>21-05-1988</t>
+  </si>
+  <si>
+    <t>+393892564217</t>
+  </si>
+  <si>
+    <t>rjsirera@gmail.com</t>
+  </si>
+  <si>
+    <t>data:image/webp;base64,UklGRjwMAABXRUJQVlA4WAoAAAAgAAAAfwAAqwAASUNDUMgBAAAAAAHIAAAAAAQwAABtbnRyUkdCIFhZWiAH4AABAAEAAAAAAABhY3NwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAQAA9tYAAQAAAADTLQAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAlkZXNjAAAA8AAAACRyWFlaAAABFAAAABRnWFlaAAABKAAAABRiWFlaAAABPAAAABR3dHB0AAABUAAAABRyVFJDAAABZAAAAChnVFJDAAABZAAAAChiVFJDAAABZAAAAChjcHJ0AAABjAAAADxtbHVjAAAAAAAAAAEAAAAMZW5VUwAAAAgAAAAcAHMAUgBHAEJYWVogAAAAAAAAb6IAADj1AAADkFhZWiAAAAAAAABimQAAt4UAABjaWFlaIAAAAAAAACSgAAAPhAAAts9YWVogAAAAAAAA9tYAAQAAAADTLXBhcmEAAAAAAAQAAAACZmYAAPKnAAANWQAAE9AAAApbAAAAAAAAAABtbHVjAAAAAAAAAAEAAAAMZW5VUwAAACAAAAAcAEcAbwBvAGcAbABlACAASQBuAGMALgAgADIAMAAxADZWUDggTgoAADBEAJ0BKoAArAA+SRyKRCKhoRv7JXQoBISygGHwLWvmWPyjSe39Xx3J7bP7PjK7zV5DenL7R3/yC4EtLmyKtDsgzeS3sce+ivHmZHt0qzxJJsc2UoOzTt7vAkQ1spMLdxf8/qWwFxYNIBkWWPHSomMGNYXX/kn9GqVqUEfu6hbTkvYUg3w16d/eC87RupeyuA82KzAZoClCYSUXeugidSlPa65kmbqdnxPL3smWRcNxPIGMfLMWqynghiKK6wRS5nMTfjnpMqyZ+d918HXuTaTgh4QRfYXY4/jpRJvSrsEAwgQhUB5aJE+V5Ht9kGOBt1HaJDilbTCLZ3Pi9dKLhlkO5FOWOdVyQCOz67JoMmyh59EKObkwAgznkOVaubej9ZYC7lSbAR1/fOVPJwpuWDyfmB5okEpGM34g0GCv7q5T6F/3odc8aTgbkevORbT7QdnP8Q2OowK8nWM2bfvPz2QRttVm00KVByuglGcrL7gfps5s5dxC7AZ7CeF4ftOHZMGBFge7YJ4JhMZ0v8mFUhxNIX3HBGJEEBQy0IxgH/Tdh93VFtph7oqvtxHjfWMZ2PEOThiZrTDptIa2041wiGNYiMvElQ68rQw+7ssipX/H5FzCIDt8/zwP6nK4F9l8wIAUCUfNkYAAnJKnMR9ztFerL3HxksrCxw9716dGf3AaYB8yOcZiIoqeiqTjvvud6CSSKCl+DBpGXlL91a1w/UyYVXd5BN548uUgAP7mN7eQGaIcNfn0b0steBjY4FJqgKfEPX96iJ3qH7xEFzHg0M6c1JJLBfS6VHG/DbGEndoUnxUddaiV1OCwXhRdtbwdQv6U9C74LZuCpcwaSMTjABAGG6Q76nHZ8qPm9vogT1WqAytz5KwhO3p0PS8Ednoh82pFOdP6lB/G0WqupyqWtTQQXUEzdHsAh5QkllBqxf2zsfdf+s7i4xf3Aph0D0uWZ2tlh9Hsb0Kgsm1M3rpNJySNcJabPLRoza1Zp2Rb7bepEnDnD+iTToS+W22Jd1A5kwnxQPI0G6ZzLSZFp9rlp8DDWwFNeBYZqIBKRpiZlucuU92tIZAS/phN57QjaMynGw81AhifzKcoEbcJyNZ0l5jp9VLUsWeVwyz+Sfb9bCirgLmdwcuAM/+Qu774FGeowkquT6nE39gp9BzT9BX3piS/bnpoOy9FRCE7ITVd+dWfuxB8Qswc7VrVVrtb5/iGUBUGjgTBj+LeUCeETh0LmGJSl4E/W+Qmh5pA+ZKsb4bIZsb8EFNEvqWMAhjViKJyKIGgFIV8MIyAIiz9QUFAQpe9t/EPcUhqH8Ka2/uZ+mbmGCvOdN1BCrO03zaXsIENg9kMMBfbNR265CTr+XTBmhr2sM8XHSSaot3Hp7NBay+uDloMfcwYK5Mm2O7t2ny9KufLNDyR+0NRFsXBrDpT12vduzLZLXqjomHUHuP3CWQ9aymqxX+YAm02zDZuXe02T/g9PACPvilkYRY1CC9fzawEdDK9MeoBG655szDJrmgnurodQpZEcZf+2x1uWqkzIbrpjWBzz+/rhXfg5bxj87M6E0/XI6DjlauNb/VFnjczT6QSphaPC06tCEJqti1HmeH8Zuz1f8nwDzdnMejqbrDDvv2sr5Q8Zp13vQd0RYpdn6Z6bogAlUNgfumwjN5dcKOUVCPt9TpvfJ/JJwsxMWnogy0jUrzWHrcfWzDqJdVjSHqPRQ0ggCVWLwG4IN2+vHixbrrM6lUVcwkbdSclsdIzz5Yl10jf+O6vJRGBKB1rxp/2+GRWTTqHtffP0PThyLF45o/TWE0UaHdCvG+bmpNlnzjWFj8Q+y7pw6ZwDIhqj0ufr7um7ITvkKQXpw1SbYD+VzwyZ/qSCYJckYDaE3zZC2S0tOdCicWEsmlSP295QdieVCopCMM6TF60e5Bs5kVTxLhGuuyYlGn3sRkGL9Ou+R6VFLamIOIF2naUZzgpKr2JjMdnDRcyIs3qH9JK2UJZmTVJ80Ah/WZxKjGEsCkYpSxqSV8JNVadsMQzl8inA4XM7LRoqbD3BiWpp5VTBf+OaGFpvfhCUNd0b35Pm0PZD6qw8JCAFUVO0l41SR/HGJwkiftpj7xuKbfVqgUWLaHNwjhXJoLv0mlArfiDs/dEW8/MKhh2P0Th8T1KrmtwqvDK4w4sImCSbzfz2uhxki/j6rMlyphMf+cU5O2zK6NLBvIW/6CFN8AJGJx6U7JmsY/w4a4Vc0g9VsUHHKbgnndoxU0Z4vUr22Y6nL7wELTAnncHKgz5+xeSK4Or5bRrOpg6NjS6vv2iCTHl2i/swA3wABx6G2Jo7s5hLd6fN5kiP8Jj8d9amswkDS2+QQLuf5ab68ZIg3JEUMiz+qZiHnxReZ3YDS7s4bnda2OMmZIrxJJaP+8sI14Df9h1rj7ctKFOOQTIn/TCOvmEC6HinqHxpikfqhtjwSVfIimsMk84Tj4rlWwfpr9Oq+Hl2wMO3tRxxw6B6CBVMwdCZNnICKENWZIyDBcada+U3OD9jblYUVd/d65uPDoUmJl0RX9xGl045BYbxqjqUQSXBjntERIk/DCU7ITpJFdC+ZI6VePIuNX8VCDjnBCRhGwVEGxhQYY46OQa4xxieah+HWd0F62J5ql93Z4gXQqbsRH0XXUwjv+2kXaz58rQ0i9awQpZ9pWx3c5ReUfGTdgH7HZ+m2EqDgkQldI7F+UIkqtSYjXEe/nhyRdJCmNbxGFayPx6XOfDUM1uqCegko8F/DVQWOjeyszW+E0mkkwcB+T7+0tFtcukt7rBfAnqV402seK6fYq7qiMxIj84XqbBY3NvSYq4gezT/3oPR/8Pth/ubYVUMg/VAR0NgQ17KsD/aK/+4QhXijkmGDscPCOeUHiNaXxUwHy7LzhLUF1G2ZQD5hYBG1dpac5aIfHv2eSyxRW5npxHAf7o/brLjLulZhstAliAoohtFThDdvSGofE2z02L/RfE8QLXux7PLWirsse7hpBFLuPNygj8YCktE0LoyBoKGbyrKMavXg/ouvDF7tg+VUSYvd+ouEfiLTUrOTXtm51lUgBuW6K261+nNY+MXXt3gEvkrFZAIUcdWFcuH0UMzTRd04iKDQ+VwaA/OWKTKmK4hS7gx/6G0Dl8MX/+ku5OadZZVZ2FqK3/9Q7iwIfQBthuoVKSAGWKeM+rXMWB+6GfVOaIzyL2uAM7LP2e6d+ye0iHarMxE3GbhXE9VA4Dh0naCo7xiSO6xp6CBpd4/USQA72wozweKbTLTBXqps/w6VadfnoFEe4tLX+1NR1vVLVbpdfC5EUvoEmM1b/N7kZzzM+KrKmZVwexbA6MkcrQoDHQCRrlTsdrRrugZwPwVs/NaZ57ydAQoVFB5V0Lzfmg8P/of/ikxbJ4ellV/zGUsuAzdoIW5HpfiStYoLejhsVgQRjiFGE2DULo9nUccA3DPLZrELljtObLsCbFMWQeOdR6xMcmZIcMR9OKRt+bWaX0iC2AWZkLvQpYZrJVRtKfy/2s82uHSAgAAAA=</t>
+  </si>
+  <si>
+    <t>SPANO</t>
+  </si>
+  <si>
+    <t>Enrico</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 23-04-1968</t>
+  </si>
+  <si>
+    <t>08-09-1989</t>
+  </si>
+  <si>
+    <t>07-12-1995</t>
+  </si>
+  <si>
+    <t>+393405426161</t>
+  </si>
+  <si>
+    <t>chicchineddu@yahoo.it</t>
+  </si>
+  <si>
+    <t>data:image/webp;base64,UklGRkIJAABXRUJQVlA4WAoAAAAgAAAAfwAAoQAASUNDUMgBAAAAAAHIAAAAAAQwAABtbnRyUkdCIFhZWiAH4AABAAEAAAAAAABhY3NwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAQAA9tYAAQAAAADTLQAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAlkZXNjAAAA8AAAACRyWFlaAAABFAAAABRnWFlaAAABKAAAABRiWFlaAAABPAAAABR3dHB0AAABUAAAABRyVFJDAAABZAAAAChnVFJDAAABZAAAAChiVFJDAAABZAAAAChjcHJ0AAABjAAAADxtbHVjAAAAAAAAAAEAAAAMZW5VUwAAAAgAAAAcAHMAUgBHAEJYWVogAAAAAAAAb6IAADj1AAADkFhZWiAAAAAAAABimQAAt4UAABjaWFlaIAAAAAAAACSgAAAPhAAAts9YWVogAAAAAAAA9tYAAQAAAADTLXBhcmEAAAAAAAQAAAACZmYAAPKnAAANWQAAE9AAAApbAAAAAAAAAABtbHVjAAAAAAAAAAEAAAAMZW5VUwAAACAAAAAcAEcAbwBvAGcAbABlACAASQBuAGMALgAgADIAMAAxADZWUDggVAcAALAwAJ0BKoAAogA+TSKLRCKiIRjqJbwoBMSygGV0OwZFAxLaICQz2ks5AbK/KpZTWhcRyaewx7vwMda7Uo8MFnqsDo9qqC3h14ZyVFTbzeVxK2cud+xKsjm9horZjP2T+eIXIxLU5R9by3zLX2o2YuxksrH66YHtbmIasffm6LAbBOLA0RsaKL2wbl9gf8RUHzeaWVK7S/3TCtOXNELc5ukhuZUIT/F6SSCkrqhRCa4AqfJIA3JqCKEY7/rPCeph51bTtrmSP4z/ccFeGVqkeKAaVeivdHafbvHx+TJ8dV2AbLqZF62I6iBPj9pmlIw2OjFVQ1V1YEz6rqtSGB2X0OZYzQ+8uYs6tz0WyPHRnrKC//aUwiV0hvoaWBCxbN3apEMEcsw2sxF/lu5u4nrSNMHFevFXXV+j/ZmZ111FOV1711wLgHzRuTiNp7wbOcWZEfFDx1qs33KQT0bEBdZ5ItIxxjG19R03WAb4nwu63aCirFWQ0cBYh5XoRNwlNg2fmk5vo1pxupjkLeGwQqgAAP7+Ep8eZ/rUdKEpUkdTnU/aK3LiGDp4V1Wk6kdWtp1ObjGcCRG+8QhZPmnuCO8CR4KN9CuDAbRx/T0YbpPbrLMd5HjfOWkbG7yBxInSaY0h+0JwLV1yO8YFsJXQ9ZhmAFAgK/OrA24qSNs3MCkpNAkv/rMtH3jXKflpHM5vNJ7kStD5iGb13J4KsF3r2MSmpbagGzM5NAs/LaXzDLL3s+D925JybJK1jUQCxZlpZN8LZ9010Xx69JZ+D53UNN7dTrRk6i6uoiiilZyX/kMMo7+w84Drx5t6QrVkrEECeJ8fshyXfLzo2sbgYrSoVulZCSqwsfqWHhqGTGXFh9TLjU9g962RnZ8WRDiH5GKZPEs7iDt7U39ulxgQ8V43H+NQsybQqzKtJ8LsKCJZaYFd0rW5eCTkAfxysuxKQEXjbtBz1oZeTQwXXJCdKHXc21vWxI4Qz7Ksw8ZOQcMexv5Kz4AZgH5fsKafcGbh7lykpkEe5QmOpdAkVXkcLSHvy1Fy/ckeA+tpduRYhLmNuY/7KrfX4Q98g++tRt8dDZ+/kGm7KVzrLwP5jB7VR+w34Sp1FBwBbEXXq3n6dTbebMUvj1NwD8iJlC9UmPmBZr93zeH1nSDEaLN6UPLQ8q3TOTJBnnDLTO5V/FYG9LYhOL04wgsuDSYPID1zvkp36rB0H3Ewah6vCNXrDRiCsKQ80qy4cKy1IiveW+jE2EAEMRPY61xRELwZlp9wdhxG2Ov7mnPnBdNcZJThKsmbltJwJwvXBuWUuPX5oMqnKipC7sFlaBmVyUbY9Bqe4AjZpqYJYzWTPA+eRndP2OjqWrbHdLwvhbpgGgMeGhI36slaqSniOjn277d63kZ0GMPAi9piIjkLWRQJrPyygqHABt0Km8tZ0o8ZHEZQRB3Cuflz79EEC9Miyir7LELBojZQbaK0jQF4SNvbCmOoyl7fM+H4wL2P9H2sYP09mHBPOnaY9uQ/oq0BztXkTGHJyo9kxmcO0ewA31WPRSjgTVyIc4g4W4HrUZTFKkptadle99x+4ryJcEKXbvC0niyJM1qLRmH/NpO3M0t7bjCGFxAZn6ItyrHrMh86VZN8cAm6HC+l7EHGS5qkKBeII2IkpH8Dhe9DgEoF2lx3BwPB6r4jutVDPRwstf6OEdioZMnb3LUShlbBRu/2AMOPd8NnjVhcf0KxIfWfAb+hNDEu006ZT25Vg4jixr/TcZwiS3daOQubAPPE5uqQ3WSyC/cM+CihWiXEreQi/fXjAeNULVIga7BTcdtj7Z7YPYGU/U+X5sZQq4qZAE9K5Yt4mKfMutieyNcFgYLBstEpozedYwcB2h8r66Snxt6v0G4kdJs9bgXYKsEsfWGaXDv0XbvOXsC723yfkU/i/tSkpQOATkkiYerBrsGvx70wzp1ViGyOvaHAHV23eZmBmg5GD71Hs1Bqxov17cvbEXGD3ymzR2aUoevYcOr07xNzuAhTQMM29u1MINRTvK4XlGSwtZM6pWQAVyiqo4n1M5fZ+wAubcC12OT9p/p/vFHikVR9zcvckHuEFeLYL8QpC2K579Rgqk5PXnX9FGn9WhE+U4IQW9eN4hdg/lrV3Ab3edQuXyC0VBsRYJ964XB/sn+aRQeyypAvuGWO2LbwyTaVfVN8to4O56bofj3hgWR6wdAnehDEMbi0MQiziFk2RV8rdWKPKQNqPm71xVDRwqajaqDk5LYBgfZZiPKRQWTUwEg+3Y+PHYoZYxTBPNIXVU6gnfutiTVyIrQjf+cONDcwEroA5RDlTZsr5gmgQjluHKgFEzWZcP/twmq3NfAV4GTofXJCpsNjzc1DVLXQPA79JFHw/RxOvsmZnWMjt9nPZwi3JEhsi1kkeLEtRJaGCZU/eVMZmN8YpLJ+eTyIAJk4pAUfCjCTtOh/QZCLhrxJzmYolF3bwJaWosCdZLvF38+SNgDFv73gtu02cPRdfmAAAAA=</t>
+  </si>
+  <si>
+    <t>TABAL</t>
+  </si>
+  <si>
+    <t>Dominic</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 11-04-1974</t>
+  </si>
+  <si>
+    <t>09-04-2005</t>
+  </si>
+  <si>
+    <t>+393273427428</t>
+  </si>
+  <si>
+    <t>dominictabal@yahoo.com</t>
+  </si>
+  <si>
+    <t>data:image/webp;base64,UklGRjIMAABXRUJQVlA4WAoAAAAgAAAAfwAAqQAASUNDUMgBAAAAAAHIAAAAAAQwAABtbnRyUkdCIFhZWiAH4AABAAEAAAAAAABhY3NwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAQAA9tYAAQAAAADTLQAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAlkZXNjAAAA8AAAACRyWFlaAAABFAAAABRnWFlaAAABKAAAABRiWFlaAAABPAAAABR3dHB0AAABUAAAABRyVFJDAAABZAAAAChnVFJDAAABZAAAAChiVFJDAAABZAAAAChjcHJ0AAABjAAAADxtbHVjAAAAAAAAAAEAAAAMZW5VUwAAAAgAAAAcAHMAUgBHAEJYWVogAAAAAAAAb6IAADj1AAADkFhZWiAAAAAAAABimQAAt4UAABjaWFlaIAAAAAAAACSgAAAPhAAAts9YWVogAAAAAAAA9tYAAQAAAADTLXBhcmEAAAAAAAQAAAACZmYAAPKnAAANWQAAE9AAAApbAAAAAAAAAABtbHVjAAAAAAAAAAEAAAAMZW5VUwAAACAAAAAcAEcAbwBvAGcAbABlACAASQBuAGMALgAgADIAMAAxADZWUDggRAoAAJA+AJ0BKoAAqgA+TSCNRCKiIZhanZwoBMSygGWwNIxWW3yf5UhFEyc2vll4j2QoUG2qFVH1RzvTk+4dpGdk4U40OB3sUtpBlKBorbD5vGYte9JqCy8nrIG3p6LaJVkTvttpLMkWW04t+ylkS5zIimRhBXmb5Jqamwy6gM/I9H8l4zxtEfAxLqXb+bzv5V2IN3o59ACfPBu0/u/9so8knhDcV6gTtDeg8tcCb0dl4TXZgTHfQCtpoIwswuu7VwsSG6ivBD7UqPoTdIGZJ2TG1yvvucbY5Px9211gis7m0FeekTn4LDOxh5sUZiMBe44RhxOdeWe1lcCgeQDU24xIoOS38XO+NTOAd0XV+9dPXQFHDs7vplcqVV0Ram26Fi3+flghTSH6K+PJGH9Pgt5mZJXegDFywTfN19VB3zXeuVfb+4QrtUWaFH+7QLvd27z8n9wAGBEY4TCBrmRYhUCZvyKI/fG0RzgRwt7qOGNQ6fBlkOWp5peSz6UY9bXhNiEMGMCyb2R1pg/INAI2KwShRQ1hVM6Fnchmpr2xn/zSPU54pBarubOx6pFeTrwRCVJMYWZTERpBYwrmx57YRgcfzSmI80S5/E2Q+Nl2HRAtVQ57Cuy+Lm6Zw6lHrInlEz+mEC4ENSvdWFGCwVp1oRDPal4JsSXEz00o2IXs8ZygAP70410tocSlp4Y2WsN4wDI/2LH/Xo3w0+mokSEMf3Mzy5r3HwPMvm4n8DUBeQNvlCepnGl2LNCn8XtoGEIDyoufBftebQX+GCqgz0aPqm4XN/8G50tZd74o943UFY9E3lt3eaJZY2px/Iv3hF6Gt607QatoJ6mOmmeguYNYg3i/n5k6qAg6g1snvJ+sngV/kOmdgs8M5rgwGiKe9b78roBbqslpStZoCgnKSIHr71z1rM9lorxe/RdunRDVn2YFZrSMLlZeIELmLK6EhD/YDT7xalnu9G9PQUTx51VJZwi42Z9VKZmCE1zAK/pf7tgVWqCPntgXZl0pL7iX8O1JEVaB9UUbdiB02Tgv11/D8FoPJswjUsGFj2A24CNRszV6LgXrwKYNNP5rHxZjCqE9f8Um6TkM41HXLGims2z5OUeq5K0iyL5tYdR0n0soiHaNpr8whdff4IbyzcX4RQjwzR8o7VM+CV2Za5sxWrYTdzfGkCpenZF8eRn53bcrDDu0YI6/Nid27Ae53lcXC0pdxGScMv0fDhDXWF3BYfGao5/ZKZiJFnmo6menMJrz4y4TDpaARWgwQdmbcDIyjZ84Q76T94U90Q4YtNZ8X37dsN32JUVWkoJQe/X5/WgIGEmo4eLX6MBl9BS9pPtsXuDG+H/6V5IY9mdblau07XTMtOAWkpL6W/LYLjd5oUp0vuL6Sv1A+V0NtA+UeVdmCAxU2Ev8GZBqGZ35FVEYlXGbX34Pxpnrpj/6eS2vZBt/k48KT+gUGYpbCI6t2L3BzU3STqonx7zCh275Vd8ylYRsF+5OHcT4JGJE+jHApwzPLM8Cc/GjBma6pReZjldi7i5cBAx/vq9svgJIseMSn6G43dIMa5cVGgxCEw+XGAGQi5vDE3Kz5EpUHjIgL4tyENkH/vVxIZbJJR8XAGJGCueHaXLdcs/j+fHkoJrirIKrvHOZD7bBtVj0xFaBdBQRU1MXr6GXFmpaD9GKQUs+lizZcVhj3AyZf3Ccfnq7JXGg35fakH7N0CCqnndaDtv6SVVVvKpk7QmOzn7sg2+7dfvS8Xov44TQC0qA+KBNWjaWGCQS8y/K1sJzoCiMNqKZOlOt7HM+AQdgMsTQLKr8eaw0J9nY+rSu8SBNAhfIMmiCn6Sls8/qTCiJ7SWGRcGK+e5IawBtREQuZXEij1aNALVxPPkHILcmWErmIoeIjAFNlYjTYGVJPUSwDNsaxdDSbJ48UkoTJbRTepJciyye7j35DPBOhPwhmF+b2FS7gN5vIDFBQaWnfpURpAkf+BIrrAUfH7N2HJUlMUGZ4F1fLdM6ZIQwGOG9OZB4Hv6xmuvXZSWz/rDb1CTbT3on1mVk7TGaefTJ6Csx+Q2TCYiRFP2ZYm2GPr/IHyMwUDyvvrJtLmzWM33zQaQ0bSec7CPtkcSwBdESEDovN0N+UKSVxL7dzPXRt5qic8mDKjJVPFGCjJiFbHqF7uRZyORHs+us47+apdFjUcDaU6ovqWzDqbnjr4V3GTi/NgYBvJBmJnZiZ7GIFrcHuXfi6bRh8jgipVSvGYGbpZt1W7m7qiSRhpy/GuZeJus+sD0UQU6CWXJ2M3vZglYnNLtPmzDp+7ScUysYvFdOJveN45bB7ekzjwZyoHQfQCnqOMloQ5E5KcMhXDhhdB0GfcqRRH8GOUz/EOmMJJ+83GPmWAGSIyOGwTqrc7q+Bk2oBRtBIuxstJ7uglLMKyGBcyn0kv+rFC0Jl3W5sdy8wz6tRP+vqn6mRb359RyJeiKRNG8Q6X5EwvXyo1aHCDUWBcEIRmNnJWK0KY3q4mSIkX2fh12tajHeJzl+frddNv0ARNeTJw7WBlzJA/jeXuSOlhELfVp05Mz+aOQdiNwNUC9p1tL8d9Ux9Cl5RbyZeS/NdgVNO2//qQVN7WpA93SzY8ZOpOXuOssOgqgAg/IdQwUnplutdlroo3a+0klkEnTHQadOzEYhsePTy06GrQpDxO+N/zod5P+g79OyJciNOLvRwfjwhvHNJoF9ZlUHexVsfWveeHM4NtYV+eXGnDzydVrduM9ozG9BIWw8OkECaCuOFWiVG41Z7Dkcp3EzRtQQM6vZiP+QilZKnmRF/5wuMQA9Kiv1VUiVq86GumgXWfbKGNAH1w1j/EuSl5TEi2Q12SJuzlNfYSgfBenH2WOPkm8BcUaEwJ+WrJT+82fCd40ENxgi44AQuXOK5Yx4C1QFzb5ORH4SdjN9pS9+sMMsmnFpCTVjuQ6uG2YtwF6eYxRxJMwZx9p29t1qvh+OWVeQIBspX9sZUWol8M2ZfvW/MNkideVnvIllsXMYFxJvSauE+G4YatD/7QC7Yy1TdQWgeM7Kh0SuTRJmQ1BSUzw79DPrWlFlpiAzvSNbTWGBae3sRO+UFGVUt83WjJBpMl1lCD4z66IUOnEUoW1dcPcNsFp8pqfo9rQ4C6j545BRlxGuFsTMI1zmT3UDTRFs/QrzTXGYtnu3wCry3MlnkL3PIyPclBkSACnuvdcLMnitxr1H/8X5E7/VWP4D2MlX380tovX1Rn8TSr2YTl6UIJM1qYrLyeoV0fdTEA/E2Yatyq4XigxYCFjNiQzlLibDsfHt96G3b8QhLEbbcORbzRup0ZbzJaRALLf+nJPinblJ/HU5UHStX5XI/qjHLNNwk3tC2ZXwhwVdjAJRbZUkHLVoxKV47Ls7PCqe+UXqkEKyRoN4WGIjFTVxtcaeIGFg5NKbsn1HXZL7YBL53kCH1dQPoMfVsVb0mMc06pmAEnoFMqWysAF9xMpiTVe+KoZM+QQ0VUE/mEOaIxp/ympHvvv5gAAAAA==</t>
+  </si>
+  <si>
+    <t>TOHOY</t>
+  </si>
+  <si>
+    <t>Fritz</t>
+  </si>
+  <si>
+    <t>09-09-1982</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Filippina</t>
+  </si>
+  <si>
+    <t>31-05-2004</t>
+  </si>
+  <si>
+    <t>30-04-2011</t>
+  </si>
+  <si>
+    <t>+393209085074</t>
+  </si>
+  <si>
+    <t>ftohoy@yahoo.com</t>
+  </si>
+  <si>
+    <t>data:image/webp;base64,UklGRqoMAABXRUJQVlA4WAoAAAAgAAAAfwAAqwAASUNDUMgBAAAAAAHIAAAAAAQwAABtbnRyUkdCIFhZWiAH4AABAAEAAAAAAABhY3NwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAQAA9tYAAQAAAADTLQAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAlkZXNjAAAA8AAAACRyWFlaAAABFAAAABRnWFlaAAABKAAAABRiWFlaAAABPAAAABR3dHB0AAABUAAAABRyVFJDAAABZAAAAChnVFJDAAABZAAAAChiVFJDAAABZAAAAChjcHJ0AAABjAAAADxtbHVjAAAAAAAAAAEAAAAMZW5VUwAAAAgAAAAcAHMAUgBHAEJYWVogAAAAAAAAb6IAADj1AAADkFhZWiAAAAAAAABimQAAt4UAABjaWFlaIAAAAAAAACSgAAAPhAAAts9YWVogAAAAAAAA9tYAAQAAAADTLXBhcmEAAAAAAAQAAAACZmYAAPKnAAANWQAAE9AAAApbAAAAAAAAAABtbHVjAAAAAAAAAAEAAAAMZW5VUwAAACAAAAAcAEcAbwBvAGcAbABlACAASQBuAGMALgAgADIAMAAxADZWUDggvAoAALBEAJ0BKoAArAA+TSCMRCKiIRnKZWgoBMSygGGWDCnuWZgnAbJT2sWVa2B15mZbzGgYBTfM3Txnzbt1IPu+h6WflbtQv0TOPr2LqjkhOGhbv8gEypq3+OiUWRVbw2zml46c7G2ZBNf9kOM77c0saASCzM/3plM4oPOKflPSHnMB+DjhwH8MY6nHbnbF/LmP5KufjHIVMAgAIf7N3juwAlyJcGm1wkv4R93EYV/h4WHSkrxGaiF8qSe/NRX6nrBaH5sUg/wJPY4woOw44G/lNWSREvGGRZGxyIcDUBwouAs1zo03uqEee1Y2rxqKx3tkVWLV78yOnboPhrRflwJl2FxvReCjE0nWBsa8T3b1QGGAN6Mv6uZvF77Uhy0PWdfVmEAt+juwfDiLKMPFQkp3Q0VUqkNfr4zo682+2Z12RFh3NYpzOOsQfgFmy91IytKJEPMz3+VPnsD/9ZHI8Z96kRD0fw/cj+M7WyzmNzixL5rxofWND/ppfG7hPh6QkiXevfe0H0AFNolv/bnpaE4hoUt59WPiWCVkVQhaq4m9/EHeu2N+qO3GIxwedICdLHUcZ/CYayXzm64u5tSxrL2SCd9aGw7eZ7m0KcRcXd5Ij9K7bOUSJKJ+3jMNE73iQAZZO/w3WW4tsqytkFz3DAR998swguB2epyDkL1ve/mwwwBgH5WmM81C41hOgiKugPlZYSB1eOEBzqcrLfFmuQ1AuqVmztLFo60PJ1XGokvHAAD+70vrsi0fJXSZdR4zd4laxj5bymp6LsBteu9/Ad8FFg3TK6OCL73b+Du0w+XUIkyjNB4aSehEFO12IPe2phgZJE1/Tn1lQUUx0dV1W2XFXzNoWnB1zx+C1yB9GjztKg8niQWsJy3EKv395yQey4LK8L7RS+4KDRXwiw9JRLioc7SVu3uAsCK52OCaZJy7keEcBjtSrUhPfjGJHuUSDiiPeJy6taz00hhRUL7F7G7WtKm/jy6j9/qKwV28eKElN2DIW6t8VKmrpC9KAO4gy48nGdee0icT2g5RKDnaVufqMvRB4fwqEGUxpMTVUfWQrk+M6Izbzp3dmgLzcJnxrBZx5zwcrW9ytMCAwXCxRTRG+0H+E71quBerVFP7mN/YVVonYhJpOpVv6mGd4GcjBDkur9zuU+ZGP15FRYtypA+VkEhAxOwKtseXYCY41Cm6bjBC1KSiM1Z/M7JIP2Wxdtl4BQuHNEIED7WGB6q6KF5aV2pgfTcckVBcrV+eF7lcqNXX4XAjW/BRL8MatEhYeNSCGmMI2f18ENRCgX79J0xslqIqrSxCXG77E/toKK/5kYqcKgRWHYWCtWNPHLCQHFwoFpnS5qE3EVnqPWN3kYxcXP2UixTjMKv9cQ/Q+pHPrYEb7QPKXHAUhZujwmRgH7Ein+2LTDQIYOh+FRcwKVTemnhUb4k3tLEuHt35tUjJcepT42c07lv5G9wQPYejJLp8OF21yGfqEHw40py0oTfsTU81KcKZS4FXtmLGjByn93KvRsByeI/nRg6twFjtvvtiXxf2sZKreS7/cfrgtqjS1BFOaH6tz7alH8En1FO3pNZW34KuXc76P4p1Yw6Hman6QikYpKB9w8Ob6PMGjpe3ZyjeobPvLeWVMqLlBhs5ctdGBE16Md+KcseIVXFB+/Kd7AeQ1GpjlkgCwPmMbcchArCxxN5fZJCXIbP82ifHWHY6F5WV28n+vB/tBT6V7JoeKLfAzt6En0ltHVhsA4n1a5KEIzad4hu6xDyJIVSCx4fRZIgBHyB8p6HRiz1ohNz2QjEvMyRJ9jw3BWMFCiAwF40S1kgimw94vm+A/foHTINU5OL7J6jKQ1wYjB/k/K0/EPU/KLavCvat46N5baQM/RixDfQAbPptgVqhV7HbRasc+jqAsKzZ0foryPtgfJSNxkAji4NyX9TvYrLFtUtPWiz4adTmTtA30OMNbZl2wpjULiBc2N4dJALnhNZDZy0lALPhWws0yR+5H7uMc/2qxD21/u3zr0Tkiy44F5iWD3CwklOIqh7jHy9qGuRfgj7va/HIAh7HhHKV+xAzh3sUwx2REyDWJPj7wxT/xnDlFhIbFMfSP9IOvVp3bUqvV2GIQ68+O2+goz6Wrjm1l4N0O2bdmfE2Oe+iQYpQYSD5uD4rn0kz7FmVJswGJiYkdhU0QlQ3vw34hk8QUzJJpYtmcrEBTvuKfclk9RlQkZYSbmWpeRGilZR7suAaIQ8Kk3BeW0VHta+3zVoRa+L/zvyERQ8Lxy2noD/bY7W/6SR+n+CNtnnu3vpHarHdbfNZLgCOAVCjnKPQi+RyZkCmqrR7DPeA9ZNsx+ZynEZcgZ+PVAdY6qBH7HeicvWYNDWw1Fb6Lj/Y+vpCrxnPsuxVIzyYO1KasnzhNCQsZk6CH5oLh7EaHmTddyAltb2XVxZ6959HrieRy1Dem+hyi4N+Sh25s3XtuWgK4uaTS9EEVZNUsfE6lGeHeG6sDPBkc4vrQPugGmVeqkwLUHTC5bGvo7Iq5wWXFzN06dE94mRg6BcgUFiNhssmCPoF4TIaPay1DVUk8fsz/2O2C2o5kBrznRiRZaT+7dhHwWl24Kb0p7kMo4tZiz43OAGCYElsxAfjfmBkeQI88p5ZmMKMpL8H9U+NTYit3TAegM8dcb+JMsPjWyC84p0HEIOBqt6fl2c8RJZmH9Zx86wEeLgNAl5LhRJF7kyW6G3ocOxUwsWp/AkTqfqeyE4jQKscncDDQSfttTR3RfnN1r8OF6Lb0zXQu9mLwBB43TqUT9zi9Nh1+ft0QHx0XKK3ulmHLalBQhkxpzWeJlIS0tLquIN6ulzGleCXDUgD5RgA+jT+mm5H+yTacrtYOfkfZNVNfSfuQMwM/46AYbS713NR1UVRtSLJR5r+R7ltNepcPVknmUl09y1aqe+dRPqYcI/lo/PDKXvRXGbL4+eGIl0bwql1Ak7aslHGU6mH0cxMgSB1R8epQ1NHhX/bzS2/tmxwkncHD3P6r5L06mHYpEEjY19V0v5TMaaGVSV6p3tBVKTwHOzVRSfFZaGfYuKIk7vEIC/VJFnutQJYt2lo8nNN+S8HFT2T9XipUIOkchgHd3KO4LfS7ymtmS1K+460cN77QzJPvMRTPPctQWpY7r15it0xHR/nP8QOgk0hc99hRMUJhK6lB5V94iX3+WZiPmPY1ehS/IT1B6S9+hPJHuYxV4au798sCAdxf6eyKYQmIJiLJATO2UtqLSgILKbAUmnqwONMCd15aeZkVAcadbnGv/sHda6KZP0kfvlO4vcq0f7WCNNCoGMbrDZkyBapgSanPkdNzL3ZQyU41ByXWgne1ZVALpt0yvPUWbS192hxJgQREdo6z5UAzgmanfp5LGC/BsvKtaLOqRHfhWfB9IhWMT41TOeAf8RY32cDcSnX9+cgr5APfMP/NFTkRrlNNRubWZJZaONWPD7RLR0xDZyu4U/Am/PSRxYPVrZbr1ELwIbKCJIjHAHdfjUFcjCxInOGEXtXv9WAFNH1+ZPXatllyOvmmtPnFG3XFKRGNDQ+yAGmYgDyfImMJ6rfv3KsGMfw7GZk8oMORbkH66H4SZ8+wKDI6rEeY0tlaXwbjGdnqg1QkE6LP+Ik7QSC8/RTx/7XlVnAqZcXTCmC+NxzehIbYweLRXgAAA==</t>
+  </si>
+  <si>
+    <t>TONEL</t>
+  </si>
+  <si>
+    <t>Jennil</t>
+  </si>
+  <si>
+    <t>16-07-1979</t>
+  </si>
+  <si>
+    <t>31-05-2001</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 18-04-2009</t>
+  </si>
+  <si>
+    <t>+6281246153189</t>
+  </si>
+  <si>
+    <t>paxte6945@gmail.com</t>
+  </si>
+  <si>
+    <t>data:image/webp;base64,UklGRioMAABXRUJQVlA4WAoAAAAgAAAAfwAAnQAASUNDUMgBAAAAAAHIAAAAAAQwAABtbnRyUkdCIFhZWiAH4AABAAEAAAAAAABhY3NwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAQAA9tYAAQAAAADTLQAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAlkZXNjAAAA8AAAACRyWFlaAAABFAAAABRnWFlaAAABKAAAABRiWFlaAAABPAAAABR3dHB0AAABUAAAABRyVFJDAAABZAAAAChnVFJDAAABZAAAAChiVFJDAAABZAAAAChjcHJ0AAABjAAAADxtbHVjAAAAAAAAAAEAAAAMZW5VUwAAAAgAAAAcAHMAUgBHAEJYWVogAAAAAAAAb6IAADj1AAADkFhZWiAAAAAAAABimQAAt4UAABjaWFlaIAAAAAAAACSgAAAPhAAAts9YWVogAAAAAAAA9tYAAQAAAADTLXBhcmEAAAAAAAQAAAACZmYAAPKnAAANWQAAE9AAAApbAAAAAAAAAABtbHVjAAAAAAAAAAEAAAAMZW5VUwAAACAAAAAcAEcAbwBvAGcAbABlACAASQBuAGMALgAgADIAMAAxADZWUDggPAoAAHA5AJ0BKoAAngA+UR6LRCOhoRqYnew4BQSxgF8976kPar7Ul0bvIiiIIuy+TjyLxudVYt5yXV/44D+oCtqmA4G01u43gZosyycD5igaMIHcrPFmWBqHBt14V0Sca/CYSG36PZud5BavoPZHzdZM/nEMYxxC/oQGDkwh617i49Aiw1MPDgbocS2xsxEDYuXdO6YERo+lzCibp3Q/oCM5buFjShqp5Eqrda7HJtMJeRPp6EY4ldiX4hoYMPqIs2exsWuWTYdE13pWr5BfF5wWKzFgYJS0Naiwxy0s1yrLjluEvyYLy2/3A9BuXlkne2BQhC/YdWzfSDPI7GMNIt3UepkKoUwQxAAGK0qN72Xp6IZXY85Q5d5iX1mj5Q20JCX/Cr+RA/zMOFNwZec3b7DSOku2WeUfzysUZteIpKYkfK4SL+RZMKaN3xIMDnllQRowCycU7y9PATzrne+7yMw3OFVoHFe5/bhaXUn7OapzntMgH+4cIGgPDrmNYi22kGxOrBlRsrqQeKL+e7l/hPgoDzuIeinzcPJZxDyjbgtldihNvhK6+hyh2f5mmranPy/Qck8gLelo/qfdUCEfeCbdZAweCihKcTVsIuMSgAGC84gJTW5ZZAD+8HRliSVmxD/4Spb84Fj3/8Ckj1w98crYH5uAO8fwLYz907K2Bj0zeAz4j1VsyiVI/2j5aDa1t5kG03FS7S7eBM/byWspoWlboKrSlopFuEL02vfCc7pMwMPxgQ3bxTz18f1O1SCTZ+XzqeCfnsbEy9SmZ3NYTmWh04QduV528XsQUwl/n20zRk5Fpk7PWep6/pgJYmnJy0g8jPp4xNY2CZvug6reeXm5V+D0ey3ajat/yv/rVAwOIqjUyXOhjZ/GGb/V5E9QVG5ApCJoN/7urd7HP6KIbDZkR+NqFfCWNSBgfDIapdCdfZYzy8a4OgSN5vQI5tN7BALh+9elWAoJN0l2dOnqA0rqBqnCsr+/9U2vfx+SDVpNDlDfZQHYDInwDloc0ixckic3WjdcS5mVuiHqrpNL2GLXMGcsyVU0SGWOXccFcaP7oChQalvZlaVPThZMyhBDGKcVLB74AaSi66fOjnQ9tyb+wWzRsOHJ5Gty66J58XriVeSOo4zXkDFA28YrUv88UaCfG8Tw8iAJBH0k/1QED7lPBvBf42qAm1IP/m2gwpbE5d0DX+j1acoA8LbCl5GsWg4msaruYjz5tq+KEvGEe+JxQDI4BHmK4/YcIpL1Az0PLft5eoMxJm+M8mHlW1pFfBKNYgRGI1gM3d0dsvwZ+9Ff8xq0AuXhdZcVWKZL3RCnYuBXSTKhgz/DFfQ/bOnLFay130Y+M61UzVcu7SmaM+OGTP0JpWKgn9P8ccnaoa/PligX9n0YDF9VUc0alEjZigOBRIFRZZvmlv1spAI7+oSJwdvjm3C1OMxzSMfWPyMapkAJXwA9O2LeFLG+k33Uq11J9F6ULOGOB3+t1CuXiuoM6cWQBda7/crE2TR006TTJkH/4XL9K83k0OWbdWcR+ya9JWMxSiAezrsZ5C5VmfsQqYCpaD7yD3s4Tbmgm4aFM8nww+kFMg21HI/qF2ySEZZPbMj+h5nVSSlNFWXDEdHq75zb99QE2di1ABIz0fPhUu/hxevFVwHKQRyqljBvPlqD7B4JRUaI4NRFtpX5F2uYxcRPulBgN8kGM5/jGZ2TJneiig2TDfV2Gk4GvmX2edN919JOfSyYEzPvKHZZBeKRMorV5H6jjm5Sso9xm43p8hWlJKfsbg3YzB5vxvSbLXejqca2uJjriB4C4qROHc7tE9MbNisWFt+2O8sa8nu2tMIoAj5rLKW3IYrBCBeM2ZKLvPlLeV9Da2dj87HjpiRdVtTnEG1Spe6gwibgnILMPm6GQDqxdvG5VuDS1azBEjYHxIbDnaccmhFmsIlXa1KnGKxFBWVSkcS6KmFF/1gXYI4QR3i1ct2y7px3H2Ht6ICUhQxFP8tKJp5qzjX1ciPYXMcTlE5XpcHWYFULOLSSpOAliqvC3LHMnOtoTw4uIhqbKKXJNf4EdRIUI1lKqGmkCd7r4i8mfbms8VvRdpje3IEuH3ExHhAs2dKHFxspW/nghI6x9qctadTbS/68XLb4KHjocYPHe86yjgohrAiAFvSdPS8EyrPHPETIdQuu29rJeGRRX0L+MXrjGXGPNutvLCdJo1rreioHqG2bFE5ocLQiHKceADAb3YsvcXtdyc4eNNF9tfDHMnWXqgUafIN95joWWELS0LSx9yYlfAuLhUHxICp6AOOIJExGpZsSPasj8ZOQ+CzSYSiC7YzgUzf6jBjQeXihNAD4xykVhcT7xbPoxUuXinoUbaGHwZLAbGVR1xzTDgNaziOg57NClmnqBkeMT1wv6T8zGCik4UEbX8pUuuJsP8aJHqoGHRwGPERof2Sn7YqPyHLEh13kgM2IQsNkw2xZzvHKhDCzKimamiBHPLA6yftrSVaZCfVUdI7Ab71rxE8ei3A6KEAuk/GxdrFTwG9Pt+mkgIbK07PEHKuMDMRDalLlsV+GwJrcsI4qv4hkvGs1N8xbGeukUkRJqs3z1/ktkONFAHXvsk9LkQQCLkwO0AoQK53RA+HydPu0aMpA4TWDgtKQCqBxFObUbrNf/lbl4WIbgz+qfrd9zz9duXmOU7UUASOluVzXxzaI/1QtaPWTAK40iAwrshuzDs5xrfHur76tn7ISfc3xH3qK0cf4yQE1qg4cOF2Xf+YwVN860+snuLH0NDu/G8he2khg0J/xSoctdoK+ITDa0lUAYBX+ZKpJ2v62oyBs5jgGlKLMIk5Ib07EWmWJj8KWK0BU8+rVbZNwWnwCWrUoAkxExn7Ea+5Zy6dwhqQLHBrS6CClSjQa9ys9p6EvCgxh4YEoyt+ssc0Qw2lylx2Ak3H/R+dVdBFfgEL+BeMpri/GSmuaquxQhCOsTh02SrKkG9CR4FB9pYyS4TYu5iD+u09ynGH1fQeb6p8OhQSli7zAybBrDRdU932swHySLG/ZWJ0e2lJPHOUklQ/XUi87VbJLwCikuyMede8ghZ2+dn86nVUNF+/08njXogC2jwAUTlq1cR6CpcHWjB7rcmj+KJJZmwPWwalZKeRM27O8x52ghR6La81RmUBZkw10eWNCm27t459OhKDLdltmzMauvO3k9YLoaxtkmo8l0Q7svT6rNX735elXLqNe3MkebG2exWggYpars6Pew2MpnfPNQ+GPhCFCeZsFImLmFmuxEYqL7iwLlqMjG/twsjSdcfBiI/ae9A4Q1HQljk191tMU+MohuC7RNy/5T3oOJGTx1L/1QJwlUt9bxdtxEU2pYCnjQRzFkpX0EAvw3LYryCh3JIjICdvACy2wY5rRBM+085AQ5oeYucT29jogSHjQYN0V+XEr9qbmO/Wzmq00Jjl994Qze9sJSATLU2pHHUQf+hbon2KwbCDxBBqSABTtC7V6lmDs/kuB2fYs6wgAAAA=</t>
+  </si>
+  <si>
+    <t>TRISTAINO</t>
+  </si>
+  <si>
+    <t>Giuseppe</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 03-11-1959</t>
+  </si>
+  <si>
+    <t>20-09-1981</t>
+  </si>
+  <si>
+    <t>04-05-1991</t>
+  </si>
+  <si>
+    <t>+393489256247</t>
+  </si>
+  <si>
+    <t>tristaino@hotmail.it</t>
+  </si>
+  <si>
+    <t>data:image/webp;base64,UklGRp4NAABXRUJQVlA4WAoAAAAgAAAAfwAAmwAASUNDUMgBAAAAAAHIAAAAAAQwAABtbnRyUkdCIFhZWiAH4AABAAEAAAAAAABhY3NwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAQAA9tYAAQAAAADTLQAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAlkZXNjAAAA8AAAACRyWFlaAAABFAAAABRnWFlaAAABKAAAABRiWFlaAAABPAAAABR3dHB0AAABUAAAABRyVFJDAAABZAAAAChnVFJDAAABZAAAAChiVFJDAAABZAAAAChjcHJ0AAABjAAAADxtbHVjAAAAAAAAAAEAAAAMZW5VUwAAAAgAAAAcAHMAUgBHAEJYWVogAAAAAAAAb6IAADj1AAADkFhZWiAAAAAAAABimQAAt4UAABjaWFlaIAAAAAAAACSgAAAPhAAAts9YWVogAAAAAAAA9tYAAQAAAADTLXBhcmEAAAAAAAQAAAACZmYAAPKnAAANWQAAE9AAAApbAAAAAAAAAABtbHVjAAAAAAAAAAEAAAAMZW5VUwAAACAAAAAcAEcAbwBvAGcAbABlACAASQBuAGMALgAgADIAMAAxADZWUDggsAsAABBAAJ0BKoAAnAA+hTaXR6UjIiE1ND0IoBCJQBcrSzsz10zt8vwqyVh44Yqei0OM5Dq18N5r1SkmVubHV3LKZuu9AxHRicgTHGAvv7BDVwBADCZ+KFNfvunhNk2APF01tyBV8GxGX+xZEMtcbGxNUu5QHd+PLfeDfraDQlJLGJVBI++TS75SV0qnkDKQ+mx2m+j9OJ7YfzR7eAS4DsTS0TFOkkJE19a7yCsvt+BN1yjr+GZ6rJ5Fu7zFaAZ2GxShbCqZmWQJ1jKsjnLp6Fm6h9O2htbQm0qXgGbp/hssVcg0SvOSOgfIfmQJgd1Vom9oW4HWHM8h5EaXQUnjnrtxxdP0MWzXiTJk1GVNxXYmMEeSka23i4gDltFKLTSL39Jc3dkN0Cwlyli/qMWNLwlHrKOgluk1WEcUHGBIH5Ij8dzAeQn8WBeZHEBVWwPARs6tlNQJ6gAJ7tBkBmDY2yGtft2rkzThwjJrZZL6wUKBSSNx8nBE1xdAeQQk70ZUwdCL9ceGEwDNPgYH4H1aT6RuKJg+ec9MGqo2VI6AWTiH99chXmgWNdM6TCmGLW8+Y3puSW1B97BgGq46kmUgFE5iIbIWcKGhhLbXW+sECKz2Zbn+u5Ee+hxizl+/u8yxbeTgMOREPWySbfQ6VjsWNaE6Gx2xzTkfrF55Ts/dBAesKl2raimACUf6pmbAAP5e2bSOQwb2d6Ec6IIszypuN+5M4Nj3ClxQ2h7VhxU7Oz9enZoEc7shAi2BRjm6XRKKyZeSz+mCWnCDIYxqtTVzKHV8huO5y4HqjTU90UGrHnTGpJ5Z4eZbGNurzbt0oG83Aa0ymn2m/PVgwOV2JXQtmnf11Gwru4z6xxzn51Iwi3JblWydyIrgimvQVIzX5AUsFmJBtlBYQND8gsd9qVWkQKP3Ob8KUdEn+ZslK95nq/zVxPgGAfxCozWDZTtpTZz1gUu0ofMMqw0DRAJEb1GFiXk/LWosrfeCr5Uge/3v9z6D04h/rOe1dtM/wes2QslOBeqsxg/4qO016I58IwaYQUPwHTOT2Q9fejbuy7Jzm5LP73qv2rrX8oQRJt4y4OS+O6ukZoiSKTtbwu8663vraO9iRhYp6m0+Cxd3P048iZ68WK10oeSDIsbH517JhmXR1IKQJvwoeXBqb5p+Z0Id5AigHWE6KbiWyghugdavtt72KtdjV7OMvkVjvhF65zWu6cEQAv8D2wwuSFXW4Vjbe7oZccY8mgfRDavzSQV8JJsJMH9+JZD3yvqMNKoEWgIWnn3qQv+08KGbwB7i6DAOH6uqmxrZshhDVjxEfDwkvGi9M7GNhlJcx5Wislz/psFHS/NJWcJiplZJX38iUR5j1GRdCu+s/7ZjVcDUTwmY8/U6Z4wsdwr2JvIACqFkO5bT4XLe6d4UX/cFf7J79eN6b8IZYwsQe+Fseaq8t+YWoZAFkdOWWjWh7VneqLTfxXbt7TrgOFc7Y32xD1412G7yJkDSw/UW38nXWEzR+stILUYBEUmTFNpw4VC5ieVYDLkhCpg+kJ70fpyKstRuEUOxoCbmNCIrDULQkeNmSK+Hj52QA49hvdmbcWcOu9mhdkgj7uf8PR1WaDAUtw9z5BBVweb9JzHGpx0zIlBN4PYtjnMMr3Jz0ocPLb+VzYt/cGs88S5cRd6d5VPpUs9kczyZl0y64GaBGqK/vEk1Erro8pMBd5xdrZBaKU2WbwuVvV8qxNO+/WoYtbZ1h+DibzBb1VNxxXDiKOe2LMwSRLVR+M1MQmWPYTVssqJSoLGufoUu7xw2OR/5vOaQn6PWs6QzpkcrLicO5FZgmk3AVvZ7JnL+CfNoTxmW31zTok1BZbtNby6P7X7QHP2eZ1QmZXpH6Hgm6mnXCNbOYSlFkV0xOxnP7mApCgoMrZxlHJV+wGBw05rkYAb6GDu17PYjKSPG6MqfVLbCJvJMCmGUNha39/1dIFwk7k8Cl5dxDCsgRglxUAySlvvk5FVpQ0og5Ab1agXIDlmI8yC83LAzDh3YiGO2jLV0HlRXBiB6meZxAJJl0jo0P8IaZk4sXlNjFUodd4nrQAL3/RG0DiuXQa5DSZTKwtKfOYUtJEdMAaH/4NtTokPhCFVRviFzSQ5pg9NkKIYnURZnOWT9Agtu9+M6/zKy3SVaHnNyqxfUQQfirsY0dE6KdACnNWmLSZJ9ZYDn8+vKQnST3maBl5ldbMnUbF6xcgAj3S5S7sZ/rLEg+TonNIEWXBWcc1Mj69Rr5MgGcOijPO/gSOLYap4pqdeODOmIotCdiwvA4TIN7BD5LLAZjfstnJ6NzSYZKn/x4Y3yznBsJBHENh1gju6Gbo9b1haKfv0SG++YJrUBroxrsODs90MlrQ7wvrLtuNhOkxqGGp3WYGAMNTJfzLcR+GgdwhrjUzOGYmn+l0mqM+RgFOhwObupPCEYpiMW/YCPxCuEFxqAiw76DbwTCJ1t4Om7nSMYp03mtRWuLM755UY8+WJm3KvAscH6J1X4dmNj0nXEzy3u6ZovFJDUa8tLjaeUQe+d+Wh22fU00G6Ecy4cK3UBBkGAIxOewnNeg/5b095If5tWyNrv7LfdQhFTI6HBIRBsk9lCk6EKOzFqnBTNZRfC45wJYUtMwddSgK10v6SW7Vmvf6Q4OPgJ1FnCQMSYbe6Y6Ck3Y3vW49c/BlqUYEFeseOtbcL5bEj3RiP9CWuFts29J7Wcwhr02oQb1CwIvuqeLK6WQL4+gnFm3/5AgGCqukayHcgQRsSchcyElCS5i+VyH6heNXC5C8yar2mDIAKkEFdEBRBh3o9jFgUuYqaFpHjgV8hcM3yWViVv1+qgpolpjuM9st1bsH9CswZYnGIhs7RKTQ6dR0U4m8LYtT9TgNF1SXIiczUc38ftWXrKfsGaRhokvmFPoig+ebgtU2/T0nsyyTsn0ricN83dDC1NkZtUsSrb75ABshj1vv691ZroNaUYrQMtzhqP72VvchuqIlT5qTxzUkMjYcH2TILQh3sCqwf6tpyKJmffZKm0/AWhI73cgrUjFLeJgwvG+eJLk6zDNGPIyQhP8TaDvR8rE1Xx+hNn6WtmifppVRecPYC9tZ5WkQSsHVdioLa2CNHs1dfUo4Mh/WFMHAVDusTr7ldMfoCyWePYjSI+rOnDMuO82FdeVCMIBf8yzaDc7RYqKjKcmbP6tFmB0NGEN11ukRnYMC4fPtteZmdMN8eBY8u/oB8zQnvOaeAfEuywLdUZ0YwwBiXHFJbQkRJBEy1rZkxwsUa2VvYa1jSdAQ0DUwk3QvAwDMoGsEyClnRzPCZs6RHxh9JMx4Nah4akzPBjyCFCNnmy0F/zpHU8KCv8Ea5ZcImZwdqJuo3LErXlWtDyKewhFTNLBWe1W/5ImzAnySQ7zMYw7s/EgT0eTo2ZCZtQ4m/z6Pii7qiho1HU5HLexX1wnPjPLdZTfi4QSjGasuuppCGvXVKZbcUvZWhgm0bItChxiLr/MoCe+zydcMVnCGbpYdFmOSE38aXkVfh27iUz387leHB6wJW7zuNLxwlc853M6WBWzXDsUTcCWfOj1iqUm7G8yi9Wp1oiiBZFM3FXXcB3kw6u7vZ9nhjuDRbtqWeN9PBo8GhcV6hD+JlCE2rWnKBQvexy1N65RtQaXS6rXq4TCwwaIi7x0opDcf3IZTS8f+v9aLUg9TgTiOp0PeD5yFH6EeG327+PxvINmU5UOaJcv9Kd4rsukplViFlJPiHJ+ArEx8aFkDP43tbxf2ov42H21L1ZTl60G/Q8ELTPbnWdUJuhMzx9JMyGztFj52/nCYKmxzlk5GbuWuaCfvAgPE/HTy6PcEdzykOUxDQgx8sbmQT96Hmu5HEV2+W9G/E5ytROz8grAQLd+MZgy0ivz+TxrE9JvRfmYVMhzJPMVNCk+UHgRhakEYRuxut1+VkbEvY+iyWBJ+tHY7vmftuJcC2owHXYqw2WtZIGYVSZ38u/4AHIOOMpXJkjgTeMAAA=</t>
+  </si>
+  <si>
+    <t>VERGARA</t>
+  </si>
+  <si>
+    <t>Francis Dominic</t>
+  </si>
+  <si>
+    <t>04-07-1992</t>
+  </si>
+  <si>
+    <t>28-09-2024</t>
+  </si>
+  <si>
+    <t>+393513669404</t>
+  </si>
+  <si>
+    <t>domz.shmi@gmail.com</t>
+  </si>
+  <si>
+    <t>data:image/webp;base64,UklGRowJAABXRUJQVlA4WAoAAAAgAAAAfwAArAAASUNDUMgBAAAAAAHIAAAAAAQwAABtbnRyUkdCIFhZWiAH4AABAAEAAAAAAABhY3NwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAQAA9tYAAQAAAADTLQAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAlkZXNjAAAA8AAAACRyWFlaAAABFAAAABRnWFlaAAABKAAAABRiWFlaAAABPAAAABR3dHB0AAABUAAAABRyVFJDAAABZAAAAChnVFJDAAABZAAAAChiVFJDAAABZAAAAChjcHJ0AAABjAAAADxtbHVjAAAAAAAAAAEAAAAMZW5VUwAAAAgAAAAcAHMAUgBHAEJYWVogAAAAAAAAb6IAADj1AAADkFhZWiAAAAAAAABimQAAt4UAABjaWFlaIAAAAAAAACSgAAAPhAAAts9YWVogAAAAAAAA9tYAAQAAAADTLXBhcmEAAAAAAAQAAAACZmYAAPKnAAANWQAAE9AAAApbAAAAAAAAAABtbHVjAAAAAAAAAAEAAAAMZW5VUwAAACAAAAAcAEcAbwBvAGcAbABlACAASQBuAGMALgAgADIAMAAxADZWUDggngcAALAvAJ0BKoAArQA+hTqXR6UjoiO0t0qQoBCJZQiQJ0tBeLYjfbg/+m0tmPCzPrXLrwnWUzrATKOCpO5SQcAF2NIrvG2gJuwP60scbZ6ZS2h+0iUNR/M6YlD4hgvCpc5kXX7D7M6Co554UHVjYgLhsJW2nXlaU3DwVXAfqe1WCF/XWYY3nV5fX7MaM9Q7vo/I3RtPlTXSfVHAd9apiaz1DgwDKMWeLTmkgzyEAMfiQqEApqsN7ocDJ1JhO1kNjUp5pzs5tOrpKVUJKAnocjqrh+b7evr19sHKdAiYSnoUvVRcHJWs9KCq2sjqByrqUQ12qjTD/SeE11Bx6pN2IM4nCvdHUcD1oJbm574aU57zcSXYrj/+c8TF23ayTsqO1FX9bZwIk7W1XzDnepOz1HOL+IraBiLkQnZoaMhlj3xx8V3EHqp4s5S9VU/hKVX3+l/cp9EcpecJoPbSLzGHNaY/n4SLRjwkm4DKO9/pj9l8pnrgSfyVz39jNUlC6jqQiWsTuldDnTwSEAD+7hwTlEcGUtXUjWt8lKkDBwf55OcMn5hiKul3cWQ55w+IlA3XRWIro7xrriiM8TlBdUJqzGI/u5us243zXUqkdnk5H0XygC0Ak3Z6g1nKq89N9BjPD/YvFEU/h9bCR21VP6G18sSIKhX5e10Mndfnh+iSn58RWOzwqYAvruvhoiFBZn+7PBnsVHbA5epfz9n+Tma043Gnr3Gkf4V9pVouuLq9tN0m/hK/SAiUnLot8penp+jKVE9Ikhczs9S4cpQOZIiB6gsKx9828HxrN2LaoE6PCO6oPFMoaqb5AykYvYvITqaQvICk4vufsE0yYkA/mVEbrP4Ej/DwDwf8NUWZVpKXhH9W/jduQKSCS0UafipQSwI7v1Mz2DQICsrV8pwy8BG7nLYQBSz2Khe8TKEIk61ZZ2q9tqo570H06NY2Qxhg+AUPvMmDeYGQGPag7G+gn5wLFpZyUYD6QUTrwa5CfgFFrkqNoV0kYhmDhPPHrlv5rCOkON9culzcJRH1cujQEO1OlRMWSEuAj9xm/NmEZzr1FWeqIvSqUMlhY0vyLRhUU9kL9104JCQxTFV0QENrhX4mDTWT1A7y7ED8yPKmVLFlU/LjYdKrXByLiiNqIQZ+wxoL3lIeIVRgmLSzdBf+livo1u5R9M1I23OanEmuabgBFZ9ms8hQqVRY53YyH1uxxNAxJLFGUBmdQsmm+9yA0xTZJt/577xDh/0JyDZIzxY4tFivQBgQQtvjyCK+DRCTDaB9rQnEsqdoH1yWnGDVYqe7JkmBaDVU5oS11lNOH4tWKpCZs/2vfe0TcJ13EN3hmEocIZwgNnKdbFrBs1ukvOaZbhUUDIBI7Fd+6jMU6zDTKieyIwxHOBwn4PtlKudPvGGp4NCWGwzVbSYA5txB2FRQeKvGErT8NhnzOLWlvGvXtcoSursglRoR4+sneM8FeGBbWDn+FW4fJWuxcXva0uCqbPDgyU6wwGQxVAwdKX1eAu330RkNnpfqTeUbcVFggSh+1U45+aLrZ6O3eHZLk+4kAlVi2rSAvooYUSx079iF2sxaQxVSkAKu+u6EQObxaNScstHUsp8rr/wS2yuci6mOIU/JjZaWLYCbLZdNjIFcJ3q0v5vOAh4+JK3w1xOgtT4WXHI782DH3nnf2BePc3Fn5moI8z/Qdn6NbLWfXZ7M9DNv6dMQUxSS1VGG2sB2xO6rjSucJ5vqNM49w3JWUXacqgW8BqLogCIzy52bfrrOL4O2LtfMlkGjN/A4sETTznq6E5I8OX5WW04EoqdIn9PYYg1qD+gyR7qWolHZZ0Ts+r6yQ3R5aGZrxXkxmtvEL2uxyXyPa0lYyzAFXfY+Y5Dzn7JbQ49fmo+3DuPEUaXGM2VpIkf4865uDC6vEzBVx9kLbirLrsb4wy9gJABaFDBxl0F2XNEyBq2WIKFst+69TsPZGhOzvrR33y25qiaAPQw3lWv49yYx742rVj0FLZuM6CKd2f+GvkjVWIUmBgLEbpum62A89yKP829DiY4UbXAYZGYS2y25e8VeLzYbp1GcfmNNV+QAAb8aMDqyXzsc+PbMtqQm7HM2uTS6Vw9Wa5Ez/EXhDuwxhKNHRBJU077I0ijwxQRej56A7vZ1V0XULUtU5vn+OSGvD7vbJk14s4wVuklgZrQpC43UFJtK6MtwM+T+4ZVerXN2EBNhNb9ppih/agR54zNteb5DGFSTyvVe0EVYC+/5L9Nx2VDb4fv4oNKXRN5tOBiYVCWWnXEhp0KSIKaagMvZf8VWXEhKwg7GADvsptJH65bZ0eWKVMADvCHG06+i3jlGPmfmvFc0pVW/288AT7lRiyUJxfLrwslkgzN9XaLNR/FDHR4f7tyqPjpPyqeL0LsfdXzF4UxouyMF2HwUbOgSAbrf0g/Cj9eWX2Ru79f8b06DZ60m4gW2790REMYkBNTffALR+IKRaPEhwyDAyhrhoW1qnrb3mbKbFBippKkpbYOcfaDUs7TKAuSJAp6OOjN/L17FIWN/sr+qxqKxq0hd/R6XELsf0d6UYnWxBzWRhfUmeePpyg8dPU4qSQUbk+9O8ZZnH7DVAAAAAA==</t>
+  </si>
+  <si>
+    <t>WITZEL</t>
+  </si>
+  <si>
+    <t>Leopoldo Federico</t>
+  </si>
+  <si>
+    <t>13-04-1971</t>
+  </si>
+  <si>
+    <t>08-09-2002</t>
+  </si>
+  <si>
+    <t>18-04-2009</t>
+  </si>
+  <si>
+    <t>+56984117169</t>
+  </si>
+  <si>
+    <t>federicowitzel@yahoo.com.ar</t>
+  </si>
+  <si>
+    <t>data:image/webp;base64,UklGRi4NAABXRUJQVlA4WAoAAAAgAAAAfwAAmgAASUNDUMgBAAAAAAHIAAAAAAQwAABtbnRyUkdCIFhZWiAH4AABAAEAAAAAAABhY3NwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAQAA9tYAAQAAAADTLQAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAlkZXNjAAAA8AAAACRyWFlaAAABFAAAABRnWFlaAAABKAAAABRiWFlaAAABPAAAABR3dHB0AAABUAAAABRyVFJDAAABZAAAAChnVFJDAAABZAAAAChiVFJDAAABZAAAAChjcHJ0AAABjAAAADxtbHVjAAAAAAAAAAEAAAAMZW5VUwAAAAgAAAAcAHMAUgBHAEJYWVogAAAAAAAAb6IAADj1AAADkFhZWiAAAAAAAABimQAAt4UAABjaWFlaIAAAAAAAACSgAAAPhAAAts9YWVogAAAAAAAA9tYAAQAAAADTLXBhcmEAAAAAAAQAAAACZmYAAPKnAAANWQAAE9AAAApbAAAAAAAAAABtbHVjAAAAAAAAAAEAAAAMZW5VUwAAACAAAAAcAEcAbwBvAGcAbABlACAASQBuAGMALgAgADIAMAAxADZWUDggQAsAANA8AJ0BKoAAmwA+WSSPRSOiIZrK1ug4BYSxgGCLjOsPbvR62wkNwZTe9MDp19Ega9pu1/jZ/9sM1O5lGtgWgcXgFBK+uUb9tERY/U27fnLcNrpcpihP/vSqHjUVtAyO1xr3pT5bIuJNGhaGyHD77vl6EHZP50LXurZukhioDm8vY4N0YTNwaGzq6dQq4TjTjCnbcmtIGOWffr8dUJ4UeFSwhfL6teqzuOOerzIbhGOa2OfxcvMW2CRYIMj95FUUK7q/nTPlb/2LR+dGCiprJ77/of6H7zoVbVsmxJ+dfrl5TNmgMxYUC1bS8BBJDpsQmjIB8NgQ6NtFau5GzXNeVBBUKZy50ZwLcQK2tM7gqpV8XrzPaWlcnzhD+qPAUHGwOfyKrjV5E9BseO15blEpLMPLO5Igft2FJCPaXMCo+eUPP7vTqbzd6ukpcIWQC1+spALJVq7IiskvL6eJ+N2/MPzO3JAIX4UX7HGhNqErBZxytXQSLvG3aqdny9RLZpAfITZGNE8/sHy38AaCDX9kwb0dvDvfgIS4IhS7guhHet6T81oaTbxEO1h28vFo/4dzq2ZxtnR1FHEwic4VOeap4eMd44WuFQY3fxPF9aHYe/9rPnKiNJoInkVwjrS5uus2zJHyiZOviSRmTJXYZSBEAAD+8pdmt5bO8csH1KFUAUXARiHK/+IlnrfbJf/xrz+jYINWJ8SJXK50BeJXw3QgEbiNh29njksz9eiQPwEQDxdUQS4m99/fUenFigX29h0CKr3w3jPZD4x0QJDM19HvEwPMZMxKHQ+ulx5F5D52JIEDmq7BbFOahz++HKRwoGyAd8GoPbT8NOEQxTaYl/KE1GzVdCy84vJ+LiuCVX0CFSReP4ecnrZjaWlrHg1qKNo+DKEu0+otK8gFc8o7Mg1X+1GijcVw2oad4jk1X75/FEdZKGMwfeeapAKxVEWxajpr21jwhpB+7Mk7yyHy/IOqFAloZ63fVyL46QX8IDB71RA+WaXM2MbOX1OT89759DjerQDDEa6KX+CCtbf8d8dK1IeGTCTF347mTkuK7VCLUukv1Fo2img6B6fdbU+ue0usFFkfbjugXj7kXKKykhZ7rQ84+zgI2X4shAfpE+2ifXPVn8cvXqsr+7/0EqI8wiJwzsyyXu48SKA0fQXikx+w6FNAIFiUCJvwShIsbl0VAzDbMAwWXFMe0L1Kl1idXaPQiaigddOo3XxpuARpy14USEmr5IRHajR9JkFE7UioDUVA1WX2tHix6QNKnv764AnpDW86wd4w8LGqqVU0MGCkpGVNAd5pmbAqayHkyf9fDLt5CRk8IDuCtrWb5T97UFlju5AzP0nwYPEJRTvgL8CowwBh2LiLvLK070Bg4zNYNTPDsjWI1JF5HKoKM+MAd0bMF9RE4EtrNX1ahvVQLYmuwOYIL6Y6HJ0lxWd4E7vk95wVV9zoQ9oSJAIB5zHahlX6MRLrKUkzHF7k8zeJy0Gjp9mzMVULMMkYYCZ+J1OvUW8yIAQ7lwoZOdPTZIZXjpjJ3IfhKe5ZJOHbn92ZHkridy8yxLdk4wsIPEJpq/DeCpz0pv+7sLg+MLyb8w6/zMUpJzXtI4NMvH5ecPBdIezPrqCwjhId7+21kLNVqZu0kh6XfR0se9uwQMpGmQV37bYS1Ij7lefC9aZvLegCr+Hahd7HLJLsY6+PBvn1O6F4srvbvYSa0iuWJ1P5YARSpKRr4Rk9mx65I9IprvQmrz6OMz4B2vkfVed37TQkTsMeRfmRnmT7nrwXm7//AhmV3q9Aar6uyjvQjknkh2foB20ad7T/gXtg9RY51hx5TI2QDWn2i7/Ya39tb+BLOv7VN4PtrDMwZ5CVh4ov5zID31mg8w1jdkoFqPfesKBqUbYuMLiNRx3rJc9Jf87KYEuoZsDM+Vsw5NF9yXRrDpKW5ypILrwUFNLaSwl9TD6Sr3j6dXtEbNdHvw5hFVCKskdrh8mipBWBX5ioeAHAvI6JU11A3a9+3eBnPAaVTRVPP1KDqUpzlV/SsQm0qZ+p8KcI0uUsrbtrGzNuGmccKGopGDDsL5TZbHe4snqxVjvY49j5c+CA3RSozkfyU7RbPKIgqqCkgP/TZl6TLKsL87wUA6IHhWG29Rx/cAMbXkObro1O1mXtbbQwts7zv1CUeAQjvu4AbV2JMWqiEFLRH3JO078+MkyhUEjueuzrlen/BN+n5/TQEltFe2s+S7HYvnHifxpBgBagZWFuRTcoxCBAF2VWFUdbbgaEx9YIIGmam3N8buYMZrqTQ8c3KfScp9p1Dflmh2DIY/x8WnHjmiM0Ne52uwaw5gUeuttcgnxJnEQMd+t/4TJO2i15vyku1m1eUvpxjeBwbyCWenVd41WaHJvhRc9GiegtdPK1PWkRAdxHbEhKOueVZAszQK3yMyBMG1ID3xETJ+9sMt8NI2dtS9Q4R6GNRXCtz2UMhNt8CyYtW3/VlpYfhvVlMU+AU+Qh28trC4X84ZFyUQ9QzuOZfu/7pIqzpXoPzcrCaD/KivcaHOmEkicaT7jh1S4z8ZEaDE9yDz4uXhBX1VU6c5qy+jEpKCkCvyQQOGx54SfKV6T9nJsA3W1CyEKzniM09hsszIHjZAOEJI/7b+VIEmO3bnbuN3ZW4X3nMTIEmUKzCduLuuHFQfsY8vc+dN+lz78QJew3ZRMIO3JyJsjmRp9oTvQv5oj/o74dgvlNO5fJSr28j+mDW5SCK41nWF3mE9pZ7DHtFseWNuzzY9yp0FYxQs0v0Shd6yZkTDM10J6kLv7rvH6zgvZ3opp16Ys4LKHF6QVkOKay/00mY6Uizz5sx+HgSnEL0FEHsCILlfCtuo4ypsCyy0raeObIiTu6expXGhY8IDqqQr3qaBx5+WUTPW7xsEmoniOe6kFS6wX9BlZKLPD2SBvHhq1RRCC9fAzDdHluXpi821L7Wdh1ekg5XL0kVr6L2utwVDVYUn+Dr60ZZ4S/1Vm9uxIpkUtg4d4e5aIz1yokA3+efWc8vu3vQNqktV+AqCfvBDdAr8NJBe7RoHp2xW1gRhi5w/RgRoWAAeY8GcQh79aQZC3lcH/1GG44UfRLsVF+r4oJYga87L7HHeULt7sNPPBOIFTL7VXkOOSXA/56eUIClY3dCOz96PyWOsbSiSz90NEiNov6De+xkNPIH+1LLlgaHPwimYWs/b7AicjlV+/MNVGWxN7RzvDgsoktmwpV5IXGvqyvi95c0TkYj37jwBTvanJL5KAdFDgTux2wAs3Cm1ZrIQFIHjfmrDmiPkDqfV+p5bvrxJefMtbIlsxtzWXCzbeM99dv1Wk/XLTz99EyFiV4EP6xRCokiOZhXl0Jofr/PvBaAqj0hT41mI9UZjde+jqV25vXJzG00MdYf/sXZGOxVpnO2pmvY8XqIU99fkZIBYoRTDFyfNMVYgCP7SUHU0DiZGC+HB8KTHY4M2vRyL51QSQKeUOJs74imQhaO82C0XzygpDK1mObikMf69qwJilTR8X5hLJbEtqW+kjXKTAeOzRt5OwZ1dRPJIDbH3FyWU9ltPmfjhIQ4Tg08iTJBLG1cZp+dp6bbc+BhhqpwGeEJP5A953Jvf9nfPllrmBq2YsO4vrPujGEmq8Gw+LlHQhVcBxXtunSbGyieKe7yKSjWdgyPBBWiIu+NejxJIdrHqZ5/euBhM54+M8fB8hi1MPymuq3K6YsNB05pZCjDazVh2249tHRvGwJ1dXQiCRCwiP8PSIJxpcoB6+lyFB/abwpt63CaZigtDS72EnwE8G2VNtACM7F8PP1fVLBkwcVw5CnxS+shhnzigruQK136ayTg4RdUckAAA==</t>
+  </si>
+  <si>
+    <t>YACUMO</t>
+  </si>
+  <si>
+    <t>Diego</t>
+  </si>
+  <si>
+    <t>18-02-1979</t>
+  </si>
+  <si>
+    <t>+393896342371</t>
+  </si>
+  <si>
+    <t>diegoyacumofsmi@gmail.com</t>
+  </si>
+  <si>
+    <t>data:image/webp;base64,UklGRsILAABXRUJQVlA4WAoAAAAgAAAAfwAAngAASUNDUMgBAAAAAAHIAAAAAAQwAABtbnRyUkdCIFhZWiAH4AABAAEAAAAAAABhY3NwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAQAA9tYAAQAAAADTLQAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAlkZXNjAAAA8AAAACRyWFlaAAABFAAAABRnWFlaAAABKAAAABRiWFlaAAABPAAAABR3dHB0AAABUAAAABRyVFJDAAABZAAAAChnVFJDAAABZAAAAChiVFJDAAABZAAAAChjcHJ0AAABjAAAADxtbHVjAAAAAAAAAAEAAAAMZW5VUwAAAAgAAAAcAHMAUgBHAEJYWVogAAAAAAAAb6IAADj1AAADkFhZWiAAAAAAAABimQAAt4UAABjaWFlaIAAAAAAAACSgAAAPhAAAts9YWVogAAAAAAAA9tYAAQAAAADTLXBhcmEAAAAAAAQAAAACZmYAAPKnAAANWQAAE9AAAApbAAAAAAAAAABtbHVjAAAAAAAAAAEAAAAMZW5VUwAAACAAAAAcAEcAbwBvAGcAbABlACAASQBuAGMALgAgADIAMAAxADZWUDgg1AkAALA6AJ0BKoAAnwA+WSSPRSOiIZuaNiw4BYSygGJrMu3vXEtK4WGvmwwxy9Bd7l1xLnOC+jr8Fx1JiLCLD/8uZeRA5/XnUIkUgJMvDWwgyYJKimH7fnw0ZqaHUnH2D+h40RBW24ZLriwh71rdw0DPNM+28awiCy8AHoE5WLBARUmxinVeS+2c1KZFCIYV40nObe+Ey1Gj/w7u1R94LOLz8/D4n2U1SKT81/h0lgNTD40e3IAsJ/BJjbagmWwenBWfuqq1CID+n6HRV6DPdFmWlNtpJu/bgPkHG4MadLh1mtaGnKkwHtGbC/fysybEU3shstuNkL/fcIFXK2MDT+ZPS6XJ4gU9WJNIh49xW9Wl1HEjHmxjtqbT/4UxyS+J7ACCYGlr2jirPrXGPZxsG+bssGT9KRjBLYtOMdvG+VjCQ+tne2xvQDW7b0M8nR+V7lN3umgmabkSckr/XExJSvEVqIrrXySfbaQZQepTEj9qgUPZujUxkt2xoK6c8iXlkCQpMZp0bhIifwMA22E/1WAbfGzEer7Exqbd+gCe24AjAp8CB89Ere8QKhoHfk2SLd9IyvGzfXhl6DJvtX3T+Qx8YFvGFN+55Pfcvy7XJ6yQ/XzUGADUzt8FiyvPIuud66gA/vLZBvX0lESzP8IKL/30zxWwzTs+WBvHwIAdgMAudRsTglkuYyIEMbf3xbhNt0keanhCGdIBGUXHTSBt/1IAg+jXWXkSMNjU4cTZQ/Krlu+dSnEu5JhtjfiFFkT1OX1xAvOiHq8Cmwm0JPDtKze/velkx5cGoQ0DFe6xDX0nSlQNkEAJfF4pI4VSlR2XUO4W2nPIYGv8lQjTeA1qM6yW5C71P3N5wXQjLZS+ZqZgAnPMJ+GDc6nEgXbMS/3DDlVnARl2KP94EEAu3DZk0gJC61tnlL33Sf3p3fftJOSNDE/G3f/3Txgzp12GWwqxIyKyyY/8T5GXrlUTd/SiDjS/qbzduLRARfPLFQbFinbvVGT/3fGaasMtxM3Xc9j2UvtegbtLw8NfNUrweCiAtxvcUknQO1pLcxIMMfGzTt6ghj2ssciQRrfFNzwPsLZ46EtF/mDcj5g0KOUHomD/6RrzUU2xWRss+LPkQD28sIQgTDsjOSaoMqV3aPGXqZp7OOdqcOjvJMJSkQbS6XTrlZojBYdEwCT/KFvX/HMxWqTi9p1JO6NplLiPNaI5qKVKnN7KcXFFu9tEggi+Wn14TeFHNnFP39VqTYMnrVaplWo/5TPDd3gspcvvxGgJgFePBf+KLzkXiHk5UjBnjdFAHs3EUStE9ea6NBklYrDzvvUHq1ZP7pCpk3qsevL+stjVI/1bfnm578r4vXANDX80Hap5HR70myOHL05MS8Yc4Cb8kXAjVPa3aTX4ycYOM6boePBWQ/6jQ6DMNTqZ++R/F7B6tQwoo3sBSrH5IoZDRzDAKI57GL56xGW8t7lKJWK69l/JvI0q3uEdujfnoIqhLV/0rt9OcxF7k+9oQdCxgHgK2Cvdln99K8Z2nWROFcSMUlU5RGtsDo8qV79O2HJbTgJTKyvqExXRrtxe6gPnHy3CCNFOLXgl+AkZa1y6MwOQaD/3qG6sX2vQNns0dIHdZL4KTtonpBlR5LPW/K69fw4qCk9Gz95ve0SLotibV9s0Lh/0s4hemhF/FHHKu2qL+vFmzoabmIOhK54mXuYBDg1FIk1/c7kArYaEyzafKLeKwbKEpiC5P1Y87e3az6sCwWUqRRvjGAQ4Jx/sBVa40GjLzQ6QmmFUpdz3+e3k7FEf6VrZul8brKUcxq2tdkjj1AulupvtT8gLAw0CN3IAY0yxvXe79K6ug/GURVRzrNoh5/qajEGtMaOHbicZqYr968jKCtYobwox3Wi4v4yxri5fLzsAynBddpxHP7WX20Bpxbup8Qkj0gCMp2YZjeZbLAfebe4rk0llphfcLBJxEsjTioymP+/oHHmUTSxEeejC5bd6FngBXkix//UpN63BSh2N9VpBGW3Azf85dBha8sQrUPbb0cBidZDlWystZE6LrFzdvr5i77UsRL+R6fYd3YT+tzqSY9sTNG8wf08UpoPkqiUQte2cilgJjLTifdw+ekpXnXsTECpuJ9Hx8S9eGeu7gqKv8iTdWJm3NP8rsaj5uTavtvOqEB6MB9om8DXVa51LqSV3cXp4iGUKBT8zlO2I3eYF/06Wl6TqCVX5JEDYGo0lsYyIOXNOX1sX4xcvOaM/mvJTQpzL/NUt1KZHZ/E+IRBODLkd9rOBXaXd3kOpRahjNY+Rg1tKEan3RZaS+5bLGhDetbajdUs5pVim5FRPRYSw9VnHZjcNrWgbPeHQQqiKvqjDTysIUWQ40/xO91nK5CsXu4N+FVMOx6ilISqQA8npQK38D1t8Te2P6ejiK1Ov1lDpUcI99FvUA3U/TyBynSEyzahEYgQNrK6d443d1iSYU4DqiFfq+x7xWzBrvi4C23Nw2vlBZRc1WEDygYUCUB8NaBFWFlptNbGO07l5JDw4qxmyZFhd4kuRLykAfdqq1XqocGkAsefEYuZVYnhE4hID6aLeCuCe250AeaCTmY2vnzFn6vdGc9VzMBsiYs/JiK7anNa+1qd3bxcUPDAXAZMxgri6u7F1c97MwvFukodTpIkFpqn0Zs7EUDVHqxPClLVQFAw4+ApEIJuek99CwOkUpgTmbBWnlvFC3dGm6O+CBs3CNAR5kxB4xhNuC9zd07Yxm+RjJntS9jlVSZTls0OQVatPnarD3q/H/YIVRCZ4OXeFjNYELNGFY8NJisu28OhASqTit8QanZdTUI/z151BrFluSgHGLvmiTdFIdBiP64SvRfwrjzGaR8wFdIhRHSivALYB7o4E0OoQkQpt7OKLgNssK3liiLhZEkAO/EFKyHxArFkQbZXvMXKeCQarnwxBEbbLZkMYalLAYGwSIOH1iWIfaI5h22xFSBNlNARkxglUrJEjluJbSpb32qMMUmEnXqk9qa35qQYLAfrC3YoTRtTdsl+R3MCJS2kgFCjBFQ3JIS26ZrGcnlf7JRKPCV3dbHj7nCrYG/ZYJFgFIShFR5xmI3XHlcuPloALcHD986UpGKpDKiJ26VYAb0NHINB/hg5niFC2ldQ4rmf8HXG98kFfkS4eY6L85i+PoJqj3iVFNYWCwXFyiT4JXkF+jCG3+bvQEQWJlleputvs67egKXHmHXgvKIDRab6Ig82d20ScnqAB5CQsGiBKQrr9N/aPBwFOXAEWSgRn44IkezDEwgtEDnfp77hO2SWf2626TwxZqPdemQWF99StZEayOWvJGL/4BQ96gBSsiimyLSy1fft6XFHBDrS8Kihyic/qAAAA</t>
+  </si>
+  <si>
+    <t>YBAÑEZ</t>
+  </si>
+  <si>
+    <t>Alan</t>
+  </si>
+  <si>
+    <t>05-11-1970</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 08-09-2000</t>
+  </si>
+  <si>
+    <t>+639479656721</t>
+  </si>
+  <si>
+    <t>alanybanez1970@gmail.com</t>
+  </si>
+  <si>
+    <t>data:image/webp;base64,UklGRmYMAABXRUJQVlA4WAoAAAAgAAAAfwAAogAASUNDUMgBAAAAAAHIAAAAAAQwAABtbnRyUkdCIFhZWiAH4AABAAEAAAAAAABhY3NwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAQAA9tYAAQAAAADTLQAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAlkZXNjAAAA8AAAACRyWFlaAAABFAAAABRnWFlaAAABKAAAABRiWFlaAAABPAAAABR3dHB0AAABUAAAABRyVFJDAAABZAAAAChnVFJDAAABZAAAAChiVFJDAAABZAAAAChjcHJ0AAABjAAAADxtbHVjAAAAAAAAAAEAAAAMZW5VUwAAAAgAAAAcAHMAUgBHAEJYWVogAAAAAAAAb6IAADj1AAADkFhZWiAAAAAAAABimQAAt4UAABjaWFlaIAAAAAAAACSgAAAPhAAAts9YWVogAAAAAAAA9tYAAQAAAADTLXBhcmEAAAAAAAQAAAACZmYAAPKnAAANWQAAE9AAAApbAAAAAAAAAABtbHVjAAAAAAAAAAEAAAAMZW5VUwAAACAAAAAcAEcAbwBvAGcAbABlACAASQBuAGMALgAgADIAMAAxADZWUDggeAoAADA7AJ0BKoAAowA+WSSORSOiIRt5ruA4BYSmxnVjzOKkJZl58AkizJj/SOvP0LCJ2o7anmd28uiZ/oyi5BviqmMdtLq2NiTkYNIRAfly8tfMX9GKJb7OTS2sEsNg/R5yPWtuX+prgK+ASARxPIn5HITYbnQ0iazw7QmFAFtIJecDdcrwTyhOVviLGfzcnlzazChMEYyE7uW4983EEJsAezEux2aCMjy8Jc2s+b+YMrDRg4Lg49AAVicDFP6yig9UapGFqHdRoSa9qN9nF/+UqvLZe8J44kP4qqxJKjF2UAYl5pp2BnUdI02ouybEEjlTr+uY6gSbL3PhfKMFM+jrXNRd46gBIFvZCc8H8hhsAqN0chiseE4ftRndlI668RVcgukL0gouJtkdjvZfS4iAOpKmYUO+e0RgXwz7d8eOB8gBAxUyIbdv4RLyy4jweeru3b+otitbYAZ3FbSh6rzrRHJE2/wVHgaLJT5Ne9IoUuHFJ1a+/t5xcxHq1Ltw/VfVYkeSrGgEwRd8cXIgDuEhobfny0l9ZuC46NdcXpbdumR/qy7jkRuMc7XAmA6+9yNmD8hhDvp+eYWh1grvybEtmuORX6/PAdrrUzO1ca4Kck1Sow3uxxiWi5NimCj+TDF5ZH/AAP73KaC9EBJXjP/ZZ/1X3pHis2xo65bH73iJ/m/6s6Q+B6KMjDkS6qHJdoEE7q0KhfFFpVddyxbiyrB1KCzY/Vy35MSqxpKA9s2dZ59dXjDQY2pjfi+7g3nmgB0B0fHnfKrb7j6v66w/8gcSukGA4sd2cIe/8Zc8Cwi2Yncg/QR00LqS1epakGlN9WSUujZbk6UBAiG1I1ELJaEMk3Gr0oWVe3+tlLzAncdaDfTG6tuIB0H6Npe577bBt34mdE4Ri793aJ43i8MkhyypQmVShrePV3TizFCX/8umCvTxh5un4xx3Hq1PcwjtRvXMFT59tdSL6b4gDYLyhAUFIj/NPljz2CTU5pdj/hGlbXTdCjHaXLW892/pV6BALr2PUXNqilT2fDS1CD3nz8Jzwhz3ENHzX3hncUmd3GoSBvWNnUxKL3zQUoq/vcKEkrYZGUmeChvJFqdvvjLjNAoO8ITs/Cb2xx26++GLIkvfkwpeLBpsd5vUV33Wf+CcTX7aT7jAjudJ7zJF2a1Ai2RoqOYdAwKLrpAz3sCNLQeh5V6ghYmCH9XI3COSA4lX9QDHqsEtP0/LIL/uxu95TGhC+IK/PyV7T03s2P44y9qCCBcevsPCHcgTQEXz4qbgSwfoF7BT7S2Eei4x9cwGQB5AFsAwG3dpifSAmTOi1Xi529zCZtIX8eGjiuDHj1/ebT6FGImLLVoMoDf3DbrD8QQAv26v03+o3Uhj1c+XCGM4tCBWVGsgSwT1azzgCSljloCHswOkaVkp9KUwxJzGRMQYRLBH7K1+Q0G2TY0bmSeQ29XVPOVLRX7oWYOyQA5Y7SitGJfzuNCSyDse1+syc/gbV/kmuLLu2gBxK3tSXhTjxogMsU2wJCUWJVoVkUE+346ZZ9LLNYJkQWaLRLmj9hCKtoPVwwOn5sZuAkueRN5byGdjJ0H6AVTzizyEad8INIk2OiANASqPvXrY2Bv5jFAurGHF0wUsKvwUP60eetLVNUd5PaHK63Dlvk4qJzQf3kKzppZLELfLN5dCLgvmQzt2zwrAu0OAB0EGc0OpSxaPmk/UTorT1XkU4eCLmUToaBwm4eRwXiKKSAIn5hIvYEsiR5x0sLlvLEXjPyrjdUJBEZ+xJSgEJb81KYOcyiOTD1OsUUmK0EcGExPAO4NreueKBuJpZ/6Tgb1MbWwoFhzYPAblYv5zSGqqDHYJGWrbjUhe23UAWcXfFk592lJ1mrOdNWR06H1C3u4KVCkzYavW566nwZmXT3N8mwKh57D9Ux+x3oUJ6/oRteJEqBKAdZI5Ca6isHsgy7ZNzb9CH998N7kr2eur08yOm9m42scuZ4hkSCNcc0a4v+xSnP0sK4v4kclG+py5KWOIY/iCmgjmyeZZ0BUu6B48PSJZLuSTd1Qqbhn+3q2zZ76C6xHoRiCANB5TNRpYgC9IVjKmqtoc+qkSRbhTt/hpcYa900Ba1cV4J5tlAHugmaRZYY4CurCD8IfdU7pFiS/QHLbzdNSw3SfXsY3lPhtjnIvf5w0wY92SPZoTgnf8qd4NOFINlHFALbYJRMNs1uJ2LdVNmoNrXtWgyBvU++8c8t0up8mxcgR7t/jQc8IG+4kjCDysOricbWTmNwGJySaXY1cpi8fI3uNxiao7KQzTZHUrzNCK0nbRNN25Ih/lvoLYFUW1o6ZVMIaWBk/c+JlNzq76jkf73tvpXRwd3Mbo0PNr1J2po+ZfWz5avwOUN/cH9hDv8fSK/4qWmhZq9VuXQmUWHsjAdZRbcDk6Pj8h2AHQm8v1TDR1OM9vL0xG6/XHQhJ0fNPhoau46pylCEQfHbicyhtPMZWPycKD+Y0Kojy0lKbZvmG4C+WPbw0rbBn8X1+ZE3Fs3rgdPQhzAIVVT1A/ySCORKXjpB+Gg4msFeJWV5nF6WAvTfPv+MDcxzncWaGmhI7Wro24+033yT03VlgjrBAaQb2FkouHQ93Uth2hJr43Zv7/vzAZ/gMn/0eUnXEzizmnNv8i21uVQ5nUe3StJcvLsKUr0LalL7hF2Du6va3k518hxJcInkAde5Qx2ylngOsO75yiINtKqOtrtom9TComWJZmyF3GYcN8yYi6x6dNJ8dxLtxuncYKFBAFZ27fC0QaUYGp7nUTGq8CNrppIX2W/6UGiNrfSJUSL+R1RNGgWcQxwEGbRu0aUMwRPWNr0Re09nnYhZlU2YcZXaJ6bLl7ri49cScvbT6WukfQDkpc9oQ9MknpZzPJCHEkrD/kb7Qf63YkbVtP4Bco7BOsRsmWO8N1GyVfzC+1vN74P9wXMyBdLfhQrYlvw72XmccdTGCV52QgK1bBYcP5jFtpSrvpr0fZY/aEas+BqFFA5hBxHFz87/WqdafF2c0s3AzG6r3cjQoJZt8Pwc2nga1N5K5Z0ewXqwEpJBqzWaZwJ/Qu/+3bgtRu3C4coebae4RhRNnvxY6BzC7w217qobGbx7psDy0Nl5dyTrVe61lQ9vc4g3Jj3++5bEPd0qF44dH/Mfz/+YDmnfsIfX9Z7JkmgGijff2UvaGMk9pp/dutb8k57X/FfcfrxoBbcxXgSQ04sdmMu/3CWho1HGVxJ261h0vN/7R8KiLBICwsYM3b6eDHjoFVUSJw80B8ZFbQu1EKkk+DpZAiAdv7puOj1PYDb2XaaWqzprL2O6TnBulPzZS6HRKt7256shnJFIp5RE41+5h/BTEv2M0r4jFn5mSksTA9m2zeNU9Pfv4+Aa0l+hhIVgQbXAL8NLWABEpzEdfCWy511kPNKuYYQtvjwugG+NWo3AetjqLEOOaeygR5QodyNpkJGQ8AENYLVqvynhjKIHxf5NHENgIwUQUYLSUXtEVZJIQcBQZ4kQiqVcyZ+vBFkCNgeaLHVO6xnoie04KehU5VGjVCv/ui2QDqUcvwZ063fAGFySli62pAAAA=</t>
   </si>
   <si>
     <t>GARCIA</t>
@@ -1320,9 +1944,6 @@
   </si>
   <si>
     <t>Christoffer Denzell</t>
-  </si>
-  <si>
-    <t>Diacono</t>
   </si>
   <si>
     <t>31- 05-2016</t>
@@ -1534,7 +2155,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:L59" displayName="Form_Responses" name="Form_Responses" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:L87" displayName="Form_Responses" name="Form_Responses" id="1">
   <tableColumns count="12">
     <tableColumn name="Timestamp" id="1"/>
     <tableColumn name="COGNOME" id="2"/>
@@ -3625,7 +4246,9 @@
       </c>
     </row>
     <row r="51" ht="22.5" customHeight="1">
-      <c r="A51" s="5"/>
+      <c r="A51" s="2">
+        <v>46298.595985949076</v>
+      </c>
       <c r="B51" s="3" t="s">
         <v>400</v>
       </c>
@@ -3633,314 +4256,1367 @@
         <v>401</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>78</v>
+        <v>14</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>402</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G51" s="3" t="s">
         <v>403</v>
       </c>
-      <c r="H51" s="3"/>
-      <c r="I51" s="4" t="s">
+      <c r="G51" s="4" t="s">
         <v>404</v>
       </c>
+      <c r="H51" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="I51" s="3" t="s">
+        <v>406</v>
+      </c>
       <c r="J51" s="3" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="K51" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="L51" s="3" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="52" ht="22.5" customHeight="1">
+      <c r="A52" s="2">
+        <v>46298.59675931713</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="H52" s="4" t="s">
+        <v>413</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="K52" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L51" s="3" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="52" ht="22.5" customHeight="1">
-      <c r="A52" s="5"/>
-      <c r="B52" s="3" t="s">
-        <v>407</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>408</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>409</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G52" s="6">
-        <v>35952.0</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="I52" s="4" t="s">
-        <v>411</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>412</v>
-      </c>
-      <c r="K52" s="3" t="s">
-        <v>48</v>
-      </c>
       <c r="L52" s="3" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="53" ht="22.5" customHeight="1">
-      <c r="A53" s="5"/>
+      <c r="A53" s="2">
+        <v>46298.59752188658</v>
+      </c>
       <c r="B53" s="3" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>417</v>
-      </c>
-      <c r="G53" s="3" t="s">
-        <v>418</v>
-      </c>
-      <c r="H53" s="3" t="s">
-        <v>419</v>
-      </c>
-      <c r="I53" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="G53" s="4" t="s">
         <v>420</v>
       </c>
+      <c r="H53" s="4" t="s">
+        <v>421</v>
+      </c>
+      <c r="I53" s="3" t="s">
+        <v>422</v>
+      </c>
       <c r="J53" s="3" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="K53" s="3" t="s">
-        <v>48</v>
+        <v>93</v>
       </c>
       <c r="L53" s="3" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="54" ht="22.5" customHeight="1">
-      <c r="A54" s="5"/>
+      <c r="A54" s="2">
+        <v>46298.59825917824</v>
+      </c>
       <c r="B54" s="3" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="G54" s="6">
-        <v>41495.0</v>
-      </c>
-      <c r="H54" s="6">
-        <v>44420.0</v>
-      </c>
-      <c r="I54" s="4" t="s">
-        <v>426</v>
+        <v>428</v>
+      </c>
+      <c r="G54" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>429</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="K54" s="3" t="s">
-        <v>133</v>
+        <v>338</v>
       </c>
       <c r="L54" s="3" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="55" ht="22.5" customHeight="1">
-      <c r="A55" s="5"/>
+      <c r="A55" s="2">
+        <v>46298.599005173615</v>
+      </c>
       <c r="B55" s="3" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>136</v>
+        <v>433</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G55" s="6">
-        <v>34312.0</v>
-      </c>
-      <c r="H55" s="6">
-        <v>36312.0</v>
-      </c>
-      <c r="I55" s="4" t="s">
-        <v>431</v>
+        <v>128</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="H55" s="4" t="s">
+        <v>435</v>
+      </c>
+      <c r="I55" s="3" t="s">
+        <v>436</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="K55" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="L55" s="3" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="56" ht="22.5" customHeight="1">
+      <c r="A56" s="2">
+        <v>46298.59977959491</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E56" s="4" t="s">
+        <v>441</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="H56" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="I56" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J56" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K56" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L55" s="3" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="56" ht="22.5" customHeight="1">
-      <c r="A56" s="5"/>
-      <c r="B56" s="3" t="s">
-        <v>434</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>435</v>
-      </c>
-      <c r="D56" s="3" t="s">
-        <v>436</v>
-      </c>
-      <c r="E56" s="6">
-        <v>34915.0</v>
-      </c>
-      <c r="F56" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G56" s="3" t="s">
-        <v>437</v>
-      </c>
-      <c r="H56" s="4" t="s">
-        <v>438</v>
-      </c>
-      <c r="I56" s="4" t="s">
-        <v>439</v>
-      </c>
-      <c r="J56" s="3" t="s">
-        <v>440</v>
-      </c>
-      <c r="K56" s="3" t="s">
-        <v>48</v>
-      </c>
       <c r="L56" s="3" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="57" ht="22.5" customHeight="1">
-      <c r="A57" s="5"/>
+      <c r="A57" s="2">
+        <v>46298.60066869213</v>
+      </c>
       <c r="B57" s="3" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>444</v>
+        <v>78</v>
+      </c>
+      <c r="E57" s="4" t="s">
+        <v>447</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>26</v>
+        <v>128</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="H57" s="6">
-        <v>26673.0</v>
-      </c>
-      <c r="I57" s="4" t="s">
-        <v>445</v>
+        <v>448</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>449</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="K57" s="3" t="s">
         <v>21</v>
       </c>
       <c r="L57" s="3" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="58" ht="22.5" customHeight="1">
-      <c r="A58" s="5"/>
+      <c r="A58" s="2">
+        <v>46298.60134778935</v>
+      </c>
       <c r="B58" s="3" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E58" s="6">
+      <c r="E58" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K58" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L58" s="3" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="59" ht="22.5" customHeight="1">
+      <c r="A59" s="2">
+        <v>46298.602029236106</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E59" s="4" t="s">
+        <v>460</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="G59" s="4" t="s">
+        <v>461</v>
+      </c>
+      <c r="H59" s="4" t="s">
+        <v>462</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="K59" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="L59" s="3" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="60" ht="22.5" customHeight="1">
+      <c r="A60" s="2">
+        <v>46298.60280813657</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="G60" s="4" t="s">
+        <v>469</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="J60" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="K60" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L60" s="3" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="61" ht="22.5" customHeight="1">
+      <c r="A61" s="2">
+        <v>46298.603581655094</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E61" s="4" t="s">
+        <v>475</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="G61" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="H61" s="4" t="s">
+        <v>477</v>
+      </c>
+      <c r="I61" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="J61" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="K61" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L61" s="3" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="62" ht="22.5" customHeight="1">
+      <c r="A62" s="2">
+        <v>46298.604309386574</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="K62" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="L62" s="3" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="63" ht="22.5" customHeight="1">
+      <c r="A63" s="2">
+        <v>46298.60500827547</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>489</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="F63" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="G63" s="3" t="s">
+        <v>492</v>
+      </c>
+      <c r="H63" s="3" t="s">
+        <v>493</v>
+      </c>
+      <c r="I63" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="J63" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="K63" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L63" s="3" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="64" ht="22.5" customHeight="1">
+      <c r="A64" s="2">
+        <v>46298.60593244213</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>499</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="G64" s="4" t="s">
+        <v>500</v>
+      </c>
+      <c r="I64" s="3" t="s">
+        <v>501</v>
+      </c>
+      <c r="J64" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="K64" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="L64" s="3" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="65" ht="22.5" customHeight="1">
+      <c r="A65" s="2">
+        <v>46298.60668774306</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E65" s="4" t="s">
+        <v>505</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="G65" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="H65" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="I65" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="J65" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="K65" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L65" s="3" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="66" ht="22.5" customHeight="1">
+      <c r="A66" s="2">
+        <v>46298.60833260417</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>510</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>511</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>512</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="H66" s="4" t="s">
+        <v>513</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="J66" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="K66" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L66" s="3" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="67" ht="22.5" customHeight="1">
+      <c r="A67" s="2">
+        <v>46298.60904207176</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>517</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>518</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>519</v>
+      </c>
+      <c r="I67" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="J67" s="3" t="s">
+        <v>521</v>
+      </c>
+      <c r="K67" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L67" s="3" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="68" ht="22.5" customHeight="1">
+      <c r="A68" s="2">
+        <v>46298.60975021991</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>523</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>526</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="H68" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="I68" s="3" t="s">
+        <v>528</v>
+      </c>
+      <c r="J68" s="3" t="s">
+        <v>529</v>
+      </c>
+      <c r="K68" s="3" t="s">
+        <v>530</v>
+      </c>
+      <c r="L68" s="3" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="69" ht="22.5" customHeight="1">
+      <c r="A69" s="2">
+        <v>46298.610478229166</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>532</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>533</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E69" s="3" t="s">
+        <v>534</v>
+      </c>
+      <c r="F69" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="G69" s="4" t="s">
+        <v>535</v>
+      </c>
+      <c r="H69" s="3" t="s">
+        <v>536</v>
+      </c>
+      <c r="I69" s="3" t="s">
+        <v>537</v>
+      </c>
+      <c r="J69" s="3" t="s">
+        <v>538</v>
+      </c>
+      <c r="K69" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L69" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="70" ht="22.5" customHeight="1">
+      <c r="A70" s="2">
+        <v>46298.61162121528</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>540</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>541</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>542</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="G70" s="4" t="s">
+        <v>543</v>
+      </c>
+      <c r="H70" s="4" t="s">
+        <v>544</v>
+      </c>
+      <c r="I70" s="3" t="s">
+        <v>545</v>
+      </c>
+      <c r="J70" s="3" t="s">
+        <v>546</v>
+      </c>
+      <c r="K70" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L70" s="3" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="71" ht="22.5" customHeight="1">
+      <c r="A71" s="2">
+        <v>46298.61228880787</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E71" s="4" t="s">
+        <v>550</v>
+      </c>
+      <c r="F71" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="G71" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="H71" s="4" t="s">
+        <v>551</v>
+      </c>
+      <c r="I71" s="3" t="s">
+        <v>552</v>
+      </c>
+      <c r="J71" s="3" t="s">
+        <v>553</v>
+      </c>
+      <c r="K71" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L71" s="3" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="72" ht="22.5" customHeight="1">
+      <c r="A72" s="2">
+        <v>46298.61392105324</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>555</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E72" s="4" t="s">
+        <v>557</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>558</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>559</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>561</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="K72" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L72" s="3" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="73" ht="22.5" customHeight="1">
+      <c r="A73" s="2">
+        <v>46298.614641782406</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>564</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>565</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E73" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="F73" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="G73" s="3" t="s">
+        <v>567</v>
+      </c>
+      <c r="H73" s="3" t="s">
+        <v>568</v>
+      </c>
+      <c r="I73" s="3" t="s">
+        <v>569</v>
+      </c>
+      <c r="J73" s="3" t="s">
+        <v>570</v>
+      </c>
+      <c r="K73" s="3" t="s">
+        <v>530</v>
+      </c>
+      <c r="L73" s="3" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="74" ht="22.5" customHeight="1">
+      <c r="A74" s="2">
+        <v>46298.61551563657</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>572</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>573</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E74" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="G74" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="H74" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="I74" s="3" t="s">
+        <v>577</v>
+      </c>
+      <c r="J74" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="K74" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L74" s="3" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="75" ht="22.5" customHeight="1">
+      <c r="A75" s="2">
+        <v>46298.61625064815</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>580</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E75" s="4" t="s">
+        <v>582</v>
+      </c>
+      <c r="F75" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="G75" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="H75" s="3" t="s">
+        <v>583</v>
+      </c>
+      <c r="I75" s="3" t="s">
+        <v>584</v>
+      </c>
+      <c r="J75" s="3" t="s">
+        <v>585</v>
+      </c>
+      <c r="K75" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L75" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="76" ht="22.5" customHeight="1">
+      <c r="A76" s="2">
+        <v>46298.617082094905</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>587</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>588</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>589</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="G76" s="4" t="s">
+        <v>590</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>591</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>592</v>
+      </c>
+      <c r="J76" s="3" t="s">
+        <v>593</v>
+      </c>
+      <c r="K76" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="L76" s="3" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="77" ht="22.5" customHeight="1">
+      <c r="A77" s="2">
+        <v>46298.61783195601</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>595</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>596</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E77" s="3" t="s">
+        <v>597</v>
+      </c>
+      <c r="F77" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="G77" s="4" t="s">
+        <v>500</v>
+      </c>
+      <c r="I77" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="J77" s="3" t="s">
+        <v>599</v>
+      </c>
+      <c r="K77" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="L77" s="3" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="78" ht="22.5" customHeight="1">
+      <c r="A78" s="2">
+        <v>46298.61860638889</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>601</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>602</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E78" s="4" t="s">
+        <v>603</v>
+      </c>
+      <c r="F78" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="G78" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="H78" s="4" t="s">
+        <v>604</v>
+      </c>
+      <c r="I78" s="3" t="s">
+        <v>605</v>
+      </c>
+      <c r="J78" s="3" t="s">
+        <v>606</v>
+      </c>
+      <c r="K78" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="L78" s="3" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="79" ht="22.5" customHeight="1">
+      <c r="A79" s="5"/>
+      <c r="B79" s="3" t="s">
+        <v>608</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>609</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>610</v>
+      </c>
+      <c r="F79" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G79" s="3" t="s">
+        <v>611</v>
+      </c>
+      <c r="H79" s="3"/>
+      <c r="I79" s="4" t="s">
+        <v>612</v>
+      </c>
+      <c r="J79" s="3" t="s">
+        <v>613</v>
+      </c>
+      <c r="K79" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L79" s="3" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="80" ht="22.5" customHeight="1">
+      <c r="A80" s="5"/>
+      <c r="B80" s="3" t="s">
+        <v>615</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>616</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>617</v>
+      </c>
+      <c r="F80" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G80" s="6">
+        <v>35952.0</v>
+      </c>
+      <c r="H80" s="3" t="s">
+        <v>618</v>
+      </c>
+      <c r="I80" s="4" t="s">
+        <v>619</v>
+      </c>
+      <c r="J80" s="3" t="s">
+        <v>620</v>
+      </c>
+      <c r="K80" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="L80" s="3" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="81" ht="22.5" customHeight="1">
+      <c r="A81" s="5"/>
+      <c r="B81" s="3" t="s">
+        <v>622</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>624</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>625</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>626</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>627</v>
+      </c>
+      <c r="I81" s="4" t="s">
+        <v>628</v>
+      </c>
+      <c r="J81" s="3" t="s">
+        <v>629</v>
+      </c>
+      <c r="K81" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="L81" s="3" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="82" ht="22.5" customHeight="1">
+      <c r="A82" s="5"/>
+      <c r="B82" s="3" t="s">
+        <v>631</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>632</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E82" s="3" t="s">
+        <v>633</v>
+      </c>
+      <c r="F82" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="G82" s="6">
+        <v>41495.0</v>
+      </c>
+      <c r="H82" s="6">
+        <v>44420.0</v>
+      </c>
+      <c r="I82" s="4" t="s">
+        <v>634</v>
+      </c>
+      <c r="J82" s="3" t="s">
+        <v>635</v>
+      </c>
+      <c r="K82" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="L82" s="3" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="83" ht="22.5" customHeight="1">
+      <c r="A83" s="5"/>
+      <c r="B83" s="3" t="s">
+        <v>637</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>638</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G83" s="6">
+        <v>34312.0</v>
+      </c>
+      <c r="H83" s="6">
+        <v>36312.0</v>
+      </c>
+      <c r="I83" s="4" t="s">
+        <v>639</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>640</v>
+      </c>
+      <c r="K83" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L83" s="3" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="84" ht="22.5" customHeight="1">
+      <c r="A84" s="5"/>
+      <c r="B84" s="3" t="s">
+        <v>642</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>643</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="E84" s="6">
+        <v>34915.0</v>
+      </c>
+      <c r="F84" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G84" s="3" t="s">
+        <v>644</v>
+      </c>
+      <c r="H84" s="4" t="s">
+        <v>645</v>
+      </c>
+      <c r="I84" s="4" t="s">
+        <v>646</v>
+      </c>
+      <c r="J84" s="3" t="s">
+        <v>647</v>
+      </c>
+      <c r="K84" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="L84" s="3" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="85" ht="22.5" customHeight="1">
+      <c r="A85" s="5"/>
+      <c r="B85" s="3" t="s">
+        <v>649</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>650</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>651</v>
+      </c>
+      <c r="F85" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G85" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="H85" s="6">
+        <v>26673.0</v>
+      </c>
+      <c r="I85" s="4" t="s">
+        <v>652</v>
+      </c>
+      <c r="J85" s="3" t="s">
+        <v>653</v>
+      </c>
+      <c r="K85" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L85" s="3" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="86" ht="22.5" customHeight="1">
+      <c r="A86" s="5"/>
+      <c r="B86" s="3" t="s">
+        <v>655</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E86" s="6">
         <v>32113.0</v>
       </c>
-      <c r="F58" s="3" t="s">
+      <c r="F86" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G58" s="3" t="s">
-        <v>450</v>
-      </c>
-      <c r="H58" s="6">
+      <c r="G86" s="3" t="s">
+        <v>657</v>
+      </c>
+      <c r="H86" s="6">
         <v>42161.0</v>
       </c>
-      <c r="I58" s="4" t="s">
-        <v>451</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>452</v>
-      </c>
-      <c r="K58" s="3" t="s">
+      <c r="I86" s="4" t="s">
+        <v>658</v>
+      </c>
+      <c r="J86" s="3" t="s">
+        <v>659</v>
+      </c>
+      <c r="K86" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="59" ht="22.5" customHeight="1">
-      <c r="A59" s="5"/>
-      <c r="B59" s="3" t="s">
-        <v>454</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>455</v>
-      </c>
-      <c r="D59" s="3" t="s">
+      <c r="L86" s="3" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="87" ht="22.5" customHeight="1">
+      <c r="A87" s="5"/>
+      <c r="B87" s="3" t="s">
+        <v>661</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>662</v>
+      </c>
+      <c r="D87" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="E59" s="3" t="s">
-        <v>456</v>
-      </c>
-      <c r="F59" s="3" t="s">
+      <c r="E87" s="3" t="s">
+        <v>663</v>
+      </c>
+      <c r="F87" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G59" s="3" t="s">
-        <v>457</v>
-      </c>
-      <c r="I59" s="4" t="s">
-        <v>458</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>459</v>
-      </c>
-      <c r="K59" s="3" t="s">
+      <c r="G87" s="3" t="s">
+        <v>664</v>
+      </c>
+      <c r="I87" s="4" t="s">
+        <v>665</v>
+      </c>
+      <c r="J87" s="3" t="s">
+        <v>666</v>
+      </c>
+      <c r="K87" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>460</v>
+      <c r="L87" s="3" t="s">
+        <v>667</v>
       </c>
     </row>
   </sheetData>

--- a/dat/dat-rel.xlsx
+++ b/dat/dat-rel.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="931" uniqueCount="668">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="950" uniqueCount="682">
   <si>
     <t>Timestamp</t>
   </si>
@@ -1915,6 +1915,12 @@
     <t>14-10-1987</t>
   </si>
   <si>
+    <t>08-09-2013</t>
+  </si>
+  <si>
+    <t>08-12-2021</t>
+  </si>
+  <si>
     <t>+529991026645</t>
   </si>
   <si>
@@ -1928,6 +1934,12 @@
   </si>
   <si>
     <t>20-08-1969</t>
+  </si>
+  <si>
+    <t>12-09-1993</t>
+  </si>
+  <si>
+    <t>06-01-1999</t>
   </si>
   <si>
     <t>+393394797358</t>
@@ -1946,6 +1958,9 @@
     <t>Christoffer Denzell</t>
   </si>
   <si>
+    <t>08-04-1995</t>
+  </si>
+  <si>
     <t>31- 05-2016</t>
   </si>
   <si>
@@ -1970,6 +1985,9 @@
     <t>27-10-1945</t>
   </si>
   <si>
+    <t>01-09-1973</t>
+  </si>
+  <si>
     <t>+393387413870</t>
   </si>
   <si>
@@ -1985,9 +2003,15 @@
     <t>John Michael</t>
   </si>
   <si>
+    <t>12-02-1987</t>
+  </si>
+  <si>
     <t>31-05-2008</t>
   </si>
   <si>
+    <t>06-06-2015</t>
+  </si>
+  <si>
     <t>+639275330348</t>
   </si>
   <si>
@@ -1995,6 +2019,24 @@
   </si>
   <si>
     <t>data:image/webp;base64,UklGRgwLAABXRUJQVlA4WAoAAAAgAAAAfwAAqQAASUNDUMgBAAAAAAHIAAAAAAQwAABtbnRyUkdCIFhZWiAH4AABAAEAAAAAAABhY3NwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAQAA9tYAAQAAAADTLQAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAlkZXNjAAAA8AAAACRyWFlaAAABFAAAABRnWFlaAAABKAAAABRiWFlaAAABPAAAABR3dHB0AAABUAAAABRyVFJDAAABZAAAAChnVFJDAAABZAAAAChiVFJDAAABZAAAAChjcHJ0AAABjAAAADxtbHVjAAAAAAAAAAEAAAAMZW5VUwAAAAgAAAAcAHMAUgBHAEJYWVogAAAAAAAAb6IAADj1AAADkFhZWiAAAAAAAABimQAAt4UAABjaWFlaIAAAAAAAACSgAAAPhAAAts9YWVogAAAAAAAA9tYAAQAAAADTLXBhcmEAAAAAAAQAAAACZmYAAPKnAAANWQAAE9AAAApbAAAAAAAAAABtbHVjAAAAAAAAAAEAAAAMZW5VUwAAACAAAAAcAEcAbwBvAGcAbABlACAASQBuAGMALgAgADIAMAAxADZWUDggHgkAAJA2AJ0BKoAAqgA+SRyKRCKlIRrs7dhQBISzgGT8UsbbYDZGuNEa6W95+mNbsO5+1Cai8dweDjOIeVReS0T9xhs3OkCOxlkTg0epRJbV9UShmy/dLFt/0/BK0fQBIsAeyMrApxy7QBVANlwzTllBS4GOz0xnFljjV6Jewi8uchT42HoLAGCwDaqVm3yfCcdVqfGfZEvCPv1TrPYwHH2UpNRzQy+947NjpdqW/0OO9gforq1MTlz1QgvafM5TPzUVISrkav4BIMufU+i9ML4ZAsx33MYedQEP+2yYrN6y/5OR0TpX6wtSCLoNYfEAbxLNGE7H+7GSDioSgSEJgxIJVc9fFd/RtVRROTj7g8MHDXIstANQY/GDILBjFkcqpVGLtt85eVEpOYX3xuADwOBgmNm+lrG6RIfMUgBeSBcNZpjNmGZIW5GMrTO60x69WWqJZ038IW1WdMSesa+g76ALHnneOf+VHGXZZKFcJIexLGYGCN5iaQplEfo/wstoJlHg/kW1mIcNLYPVzV8n+6KslTMwbyrLIRSjOLbiLoU+GJwEHYhUjJVpRy/Ir1Z2L6RhKIqApaH5vb/Xrr22vkAA/vpOnXnlDZgj3fENzIpADUMZyR200PrUL6Q4D3OKp7Y6AClB6XvZxR6dCnKNGWEZm/fkbZOu+egR61wS5p9km3yRtZ4Gy2TFCoccKy8CxQVtSQ/840sy7PL7AP7AOF88xhSQ/DeMKIGW4eECsrt46TJGMGU4WBwJnCmZQ8GTIYI855JK1VN1gWlHua+CvF0HHKTzfYNa3tWv745N87QCdeS1BpW0n0lF3AxFWwVhklfx1r5af7aRWwOhrPQQUvLgF/S20Wo8L7wNuYWn1GHVd4BWRVcxtdomi+gNDzpPJfj3E0Hg0yjcplNndtWGSO/e1KGSwKH7UpTz0jaI+Wk8XIyiEdq9KJ1Npb2FQPa0OrMGTwecLBDTXSiN8OVQ7XLkIIK86+j90RAI/ShcAMP6fZv3hBTO5OTJk2WNj0XMo67frllAPucopYD1WIsbnv3jbHRg5q+s+WsxVJe8wBdET4IGFpQiUojucUuHRxkKBDGiJ9XHNp2/WrKTa1LnWEeL2PWc1BfERxIaUa0Wrtkl36PDq/CVx67rBSumxULRhwG045lWb5brF++rz23GW6B2pFy4BWFW1XsWJyzJlNsWJae5alCCuN/p8sVdrJpfnOPQ4btdxAezwtAg+THxoduh6WHAd185TWaa+u9AszeH7eiRAnk0Sv+CbGFdtjnkAAjKq6WAlRNUuLPrOB+tJZ8CXxAaYAio46dg6YhNIE0Hcxg3l3S7+eBt9rMqn8PQ0rrhXuUsL8pbQ4oHwAjPvYo3e/gRbdYPkzQgNFZ92fRjPiYIgXxEDNhbPuLWGReeccm7w5OMrvt9l+c1vytaVn5V8cOBXqCqirmQOipFdUYHvwHwRHWY0qKJkAWjw02LvzWaQMkB5MbECX2BMkLm+3Z42GBmDAg+gc5kTYVwCNmS6gXPc3HlvTvPGWUYU0v5dOgcwvWiqhTzxD33jEr1Bm47p+74BMXdA4MTvtmDYH7Qzlh2P4CiY/cu1b7uPuYl1iRUiAQhcOSBqsIsZQ1A6KjXcuKK3xPBEHVhBARTjgDFOxv/1L7d6keHx1vkZJ/hLhlhsEU1iXaHqIZ+HzPOA67KOY19tGlwBcCwXHtA72XRlALObHH1+FO/bSd+N0rVKYGyHMnIXZJU4Kpr76V9ktzJvM4EaBUC7gsQv/GW3ZQA2FmYtbDlXD//NamFKGZDErqJ5zMlr1miXAMocUib0YFERDW6JqN8uJfd0hPkLoWldZxiTW2e6ZdMLYPW7J//e1JcTLwKChFmZ+by02QEa0BCvPIaF+AMZz6PxbagbM48nWS5hrUcL1SuSBDGzy0cbiSudcULpJ0WGfCsdCl73/6k5TUjfDRDRlaF/NLrfyjmR4ZCHgkgkdIEfV0LuD9kWJxCHK5kSaiWKUBYNzOT9FsRlPf/J6v3QDY941fBKMDyEr12t7c2HmPFMB841DkEoJtQIOqYxcziA31eLQmVEv+Kdrktc6UHcK4CC7wa1p0PCwd2xTGyGwaceau1xOS6h0SK6S/Y8tyXdrNe18xTcbzIBIxOeXUYwEfr1z4cLlzwSSsgbZnK0A4Xmm+YPcxkf++k8cJ55RztYQER8Cy7s0dEB+kUoJQGVoPC/bwEIJYpOmkX1huwdrhA3NZ4SfddgHSy+omOUjLUyEuj4A5c+HvL6UFh0vxDYArcjNx27+yqj+KwxFuimHpvZHijUb1eewveCpAqu3aOvI3xga/tDXaZotG6mfTuqofxmfqj6SjhSDYcfIHg3Tmisoxy0OFjF9XQWl9F4dgvUZivd9+m4Y1etBMCzPbAMReI3PwoupTzuF0he3lGLeTg/jFLytdyYc0GvgxoRW/qllwyo2ESyZrgzBXlbgKKMhf2gNgN2Osu3w9iBS+o3FUeM4M4ALlIj6hBCIqvnSPAWvzzZsLUZGO6kvHfuIb1SdAEAJ21Q/3rrJ6T2keZUCl5fO+j7cbrKoivx/Iv8cc0owWIxJXaAmNqV5bElj2a9oxGO9VlQj/jNdlBpOD3KlkdLFnPrq3Z+6KhL3JK4r/6wAxhklyQTUOpEf8iqBy/icsywAd+jkO0vNlkrT+fUZIFVayL00HH4npx+mn9Co5tXoHtCMNBBIOMc47OM5jx+4CSrc13hBMiGxJhptmJwvdnl9VEXZOQhoE3XOdh/qignbbtf09anWz63QGbDTC2v71/tZpLSuxzZ9XfozEyYem2om9j27lSnfAJPKjeYJXp0yQalFrA2R3i4z+v+I38NT6gnjRYEO72oP25gQXijtsBFdsFAmeUdKoZ4p/5unzqU/XyRV99urZk84ZlN5rxXlKsPRzvo0zB54xV4RB54Hk68O85iUCYuiee8oV11Gq9e1wKP5qbnZ1l4iPfAiWzzqOwmKDa0zZ+YyxxQgmyMB6xNPVvqARx8OW5sRmdaRUdp9yRaCdlcNzYH0X6CzUT/xrnFWmH/YAX1x3keUB63etIA362zx42ikypIyNwru+S5BcSac9pBOYz/FaXEhwAAtyutwLozeAAAA==</t>
+  </si>
+  <si>
+    <t>PAGUIO</t>
+  </si>
+  <si>
+    <t>Reymark</t>
+  </si>
+  <si>
+    <t>06-12-1997</t>
+  </si>
+  <si>
+    <t>+393516547967</t>
+  </si>
+  <si>
+    <t>shmipaguio@gmail.com</t>
+  </si>
+  <si>
+    <t>data:image/jpeg;base64,/9j/2wBDAAoHBwgHBgoICAgLCgoLDhgQDg0NDh0VFhEYIx8lJCIfIiEmKzcvJik0KSEiMEExNDk7Pj4+JS5ESUM8SDc9Pjv/2wBDAQoLCw4NDhwQEBw7KCIoOzs7Ozs7Ozs7Ozs7Ozs7Ozs7Ozs7Ozs7Ozs7Ozs7Ozs7Ozs7Ozs7Ozs7Ozs7Ozs7Ozv/wAARCACMAIADASIAAhEBAxEB/8QAGwAAAQUBAQAAAAAAAAAAAAAAAwECBAUGBwD/xAA8EAACAQMDAgQEAwUGBwEAAAABAgMABBEFEiExQQYTUWEicYGhFDKRFUKxweEHFiMzU9EXJCVSYmOi8P/EABoBAAIDAQEAAAAAAAAAAAAAAAIEAQMFAAb/xAAjEQACAwACAgIDAQEAAAAAAAAAAQIDEQQhEjEiQQUTUXFh/9oADAMBAAIRAxEAPwC7YgjDDoelC2rye+KXaWOMnJFIsZHU5JHyrxrPTCqQQQOw+9JyF5A6cUgOCB2xk4pchqHQkPHCHio91NNbQB4bYzkkA5faqD/uPBOKOpJjGBmnK5TkDtRRklLtAtPMR5NH1afa02p29spxhYIN5/Vj/KifsGRmwdcutwOP8lMH/wCaWxnFvL5JLeWV3QjONvqv04+nyqSbptuzPB6sDj7U02/rM/wScmn2yrvLbUdNi82O/iu+QFikh2s57AFT/Kil5GUeYmxyBuUHODjnnvStI1xO8oJ2QkxxAn9794/yH1pWIOSDyf8Aahua6jnZfVuaxjKT2605BxtGcjp8q8G5HTpT1C7Wb1IA/UUvhaIV25P0rxxtznNK7HLYOeOKEzfDjNRoSF3YPzpyvkrQFBJp6khwK7TsDKCD6YJpjnj+lOZ8HjnvQWYN+U5xRMEaSAeRnj9K8jjANMaRBhWYKXbAyep9BToxgfXk0HoMJG2TgUC8vrWxi8y4nSJcfvHk/IdTVfqerLZM0cTL53ctyE9zWRvryKeYmSVZZfzbnfHNP8bhO35S6QnfylX1H2aG88ZWsZj/AA8LNtbervwDxggDr3oaeMnkVjIzIR2jQr/EGsg+pyxsWXyw+ch1ZScfKn/3g1G4jEdw/nID8B/KR+lbdfHrrWJGXO6c3rLw+LLpX220k2zsCgI9Tnj51Y2XimeWRVmgDKf3vymsaZ0Zy/krOh6q42Ov1HWh/tGeDiKR5IhztkHxL8jXS41M/aOjdZD0zrEN1Dcxr5b5bHKnhv0qQsgKBcEY65rkUWuXSSI63D5Q/Cc8rXQ/D2ux6pppkmIWWIf4g7exrH5fDdXyj6NLj8lWdS9lznOflSbc0CC6iulkeEkhCUYMMEH/APYo+7HWs6SaeMdWP0N5FOUfGvvS5GKVTyKEljWPGRj3pjkjIAFKwBIPU9aR+nWjfYJDltI7+7treXIUsWypwRgEgj6gVD13U7nw5beXLsmaXPky5xnGMlh7Vb2S/wDWYQf9Nz9qw/j27a58TC3ySttGqgdsn4j/ABFafEqVmRkjP5FkoSbTM9eXl7eM29vhzltxOMmi2mhanqQAQOVPY8Cr3w3oo1C/V7j40XBwe5rp9lYwW6AJGox6CtOy39fxihaqrz+Ujn2lf2aSyoHugBn1bpVr/cCCMbVbB9QM1vEww+Gl2knkUtKyT+xqMIr6MAfBcqZBCOvuozVVf+DQM5i2n7V1Mp7VHuYUKncAT2qFZJfZLhF9YcD1PQ7mwkcEEqDx8qsvBsmL51mfbHt/LnBY54FdF1TRI54m3IM4rm19aLYX8sYO0owKkcccUzGz9sXFillX635I6LBtF3LGqbFaNXA9eo/kKlY+Hr6Vn/D91JcSh5n3MkDISe43A5rQBgPbisLmQ8bcZp8aW1jwOPpXl7UindxRBwufSlS9sZtwuOozj5UJhgZPXOAD60/cQcjimv8AEcZPyo2CMgYQaraSMfhYtGT6EqQPviuaaxeG6169uwQRLMQvpgcD7Cug6gd2nXB+L4EZlx1BAyD/AD+lcwh+J2Lg/Dk4AyTWz+OzxZmc1PyOmeCbLydMF3IPznrWqW6QZAVmA54FYMN4jttItd8iWtuwREEfVQcAEnueelaEQaba2qyGe8vHP7z3D/EfkCAKtktk22FF4kki/t9Vtt2wo8bejCpP4lD8Q5FYaDWtLurryBLcwNzgidmH6NkVNvtdj8PTwLfeZJFcA+XLGuckYyCO3UdKhxfpB+u2awXaA9qFPNAesyKfc1mLDVX8QpJPp2Y4Im2maYdW7gKDz9SK95FsJ9smrAynsY1x9/8Aeo8fpk79xLyVVcHDBh7GuY+MrIxX4lUckZB+tbeZNQtoGuYZYbqNBlkCmN8D05IP2rD+KtdtNUtYPJSRJ1c9RwwxzzR1RanqKrpJwaZI8P3DLLaoed25Dnr0/pWuwBwPSsBpsux7Fz/qAEj681vXJBNJfk0vNMt4L+DQ5TtP1qRngUBBuPvRQcc1l4PMFjcSDTuAKb0bIpSeM4oyAbx+YrIR8LDBqm1XQ57mGSe3VEis2CxoFAyvQ8/XNXbMFG48VMiiS609SWKqGJIHfB4pjjScX0V2JSWMPc2jT6Q8Ma5dUDIPUrggfqKfa24nt/xFu4KOMqGXp/WpNs4CAGgXen2gka5juri1kblzDJgMfUg5H2rQg9KGu8I37EaeYm4itgp7qnJocWm/tHVjKrFLaxQwxsnVmON2D7YA/Wmokpm8+71O6axUHIYqm8+5UA4+tT7bWdKjiEdnJF5UYwFX932xR+SCcX/CutdP/C3t/ppdgLg/iEbOC2QAfuOfnVbN4VsxdbmsbhpM5DpL8OfWr65ew1TbJHc7Lm3JMbIwyp/2PpUe2uNelUHNiT/7FZW+xqfL+MhQX2iJc2b2Vg+3fhVJALbiT6friqfxNoltb+FFRVUywNGd+Oc5ANar8FdyyLJqUsThDlI4VKqD6nPJqr8R2kl/pklomSzlenoGBP2BoPPxkgXDYtHPLWynaaCcvjEyKVA4AJ6iugLIHJB+VRbvTbe1gh8tcF9rEfIf1psbkdT6Ujy7v2yS/hbTUq10WMZwcUZjnp69aDCQVzii9aSGAa/mBNK7KBlh9KYzbATQN2WO7njpUkHpWJ5q20wqNMc713M/Azz2qoYA9Cfamqdjq3oQatrn4y0CS1GgaRk4HGajOJbm4VHOIxyfejo4lUGpH4YTJtVtpYYyO1Pp6BuDnkslhCTtGiEYKMRyKr5IvDkwwvlL2yhx/Co+neGrexec6jJLfM5O0ueMcY4q7/D6L5ap+zQFDZK7BwMUwo6Rqj/WVkGjaP54nswhYc8NwaNeNIAJIxlk6j1FAvNE03DS6cJ7OYA7cdCc9cZ9KZpUWqiM/tIRE5wjKDkj3oJRwny/g9r5iBuznFLCFmnQtn4gf4UtxAplOOgqvvNQkspIzAQG5zkZ4qiUlHtk+/Q3XAReKh6LGMe9QV64r011LdymSZstjFeXjJ9qzbJeU2y1LESYZdhwTUtG3frVapyc9sVKhm29eme9BpwN5Cx60hORzSEgV7eNnAokQeycgCvEk8V7bzkdMUhIHOK4gm2N5tcIxx/OtBakPHkHkcisrZxrdNOo52bV3DqhO45+wH1qVZau1lN5FzlSONx6GtOuMkk2LuSe4axUDgZHWgtaEtw2KDFqkTAcj9aJ+OQknIpjUQm/od+FCYySxocuSCegFJLqcIwMgE+9Uuo6/DGpVWBPtQyO1/Y+8ulijOGrOTz/AImTzByOi+9TtPSbULwTy8Kp+Fe2e1VE+q2K6rdbXCoZ38o9sE1RbTOdeoJWxjNJkpOhz1HaiK3bHBFR1cFs5yCOtFRunPasuSaGQ4+1P3cdOKCr5xRAM1Wdh5yeMV5T8IHzqPdXkVvHvlcKO3vVdcaxtGY1wPVutO1ca21/FFM7oQXbLWW5SJRucDviqq/1ny0KQ8sQTn0FU5uZZnaWSQsST3oKsXDu3Jb+FbFH4+EO59szreZKXUeib4a8RyaTcCe4BmguF2zrnk85z8x1+lbO5S21O2FxayLMjDKsOvyPoa5k0ZjJjU9Og9RQYry6sZfMtZnjOegNOXUKa6KKr3B9+jctLeW2RDK2B1B7VGfWr5eCzfSpvhOW38WwvbvO1tqUK7jwCsy+uOxqfP4P1RXOyS1kA77yD9xSTqnF41o7G6DWp4UQv7+5BXeVHtUiztjJIMncR+ZielW8XhS4jikmvryC3gjUs5TLEAdfQfeufav4ge7meGxaSGyU4GT8T+59/ajjTOf1gM74R/6zSa54oitbdtO0xgzsNskwPAHcA+/rWVZ2l2RA5JcEn07mocYeTkfCB3JqxtIdnb4j1NPwrUFiM+djnLWT4b2a2kAjbIP7p6Va22qQzMA58th1BPFUJH/NL7CmTOY5tw4pe/iV2rtdl1XJnD/DZRsPXI9qkIw5rJ2t7PEA8bFkPVTyBV1b6lG6f4gMbY79Kw+R+Ptr7j2jTq5UJ++mVsxa7mBYlgPWol4paQKh5XqKmKSkZIqJDyzE9Sa9KoJLEYzk2+wARvLcAZxSqMIFqUv53PyoE4AlyO4osAZGlQOP/IHIPpUaaPcMso6dfWpjULPxYqSBNF1GTQdYg1OHcrxHkHkOCMEVs/8AinPLgtpkQOMlvOK5+xrFyKASMdqKbGCePc4IKgYKnHaoxMnWXWuf2gX+q6TNYrZJDFOuGZGLNjvWPWLkErtHYdTVy9rFHENq47VDjANx06V2JHN6et4do3MPkKkRtiUKK8TyRS2YDXZz26VJBKMCxgu5+JugpGtA+Cx+lFkObtVPQDiiNw2K4kDbkRkxjgdhRwecjtUaT/MU96kRkkc1xx//2Q==</t>
   </si>
   <si>
     <t>AYO</t>
@@ -2023,9 +2065,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m/d/yyyy h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="mm-dd-yyyy"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -2054,7 +2095,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -2072,9 +2113,6 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2155,7 +2193,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:L87" displayName="Form_Responses" name="Form_Responses" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:L88" displayName="Form_Responses" name="Form_Responses" id="1">
   <tableColumns count="12">
     <tableColumn name="Timestamp" id="1"/>
     <tableColumn name="COGNOME" id="2"/>
@@ -5351,8 +5389,8 @@
       <c r="F80" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G80" s="6">
-        <v>35952.0</v>
+      <c r="G80" s="4" t="s">
+        <v>225</v>
       </c>
       <c r="H80" s="3" t="s">
         <v>618</v>
@@ -5423,29 +5461,29 @@
       <c r="F82" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="G82" s="6">
-        <v>41495.0</v>
-      </c>
-      <c r="H82" s="6">
-        <v>44420.0</v>
+      <c r="G82" s="4" t="s">
+        <v>634</v>
+      </c>
+      <c r="H82" s="4" t="s">
+        <v>635</v>
       </c>
       <c r="I82" s="4" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="J82" s="3" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="K82" s="3" t="s">
         <v>133</v>
       </c>
       <c r="L82" s="3" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
     </row>
     <row r="83" ht="22.5" customHeight="1">
       <c r="A83" s="5"/>
       <c r="B83" s="3" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="C83" s="3" t="s">
         <v>136</v>
@@ -5454,79 +5492,79 @@
         <v>14</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="F83" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G83" s="6">
-        <v>34312.0</v>
-      </c>
-      <c r="H83" s="6">
-        <v>36312.0</v>
+      <c r="G83" s="4" t="s">
+        <v>641</v>
+      </c>
+      <c r="H83" s="4" t="s">
+        <v>642</v>
       </c>
       <c r="I83" s="4" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="J83" s="3" t="s">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="K83" s="3" t="s">
         <v>21</v>
       </c>
       <c r="L83" s="3" t="s">
-        <v>641</v>
+        <v>645</v>
       </c>
     </row>
     <row r="84" ht="22.5" customHeight="1">
       <c r="A84" s="5"/>
       <c r="B84" s="3" t="s">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="D84" s="3" t="s">
         <v>525</v>
       </c>
-      <c r="E84" s="6">
-        <v>34915.0</v>
+      <c r="E84" s="4" t="s">
+        <v>648</v>
       </c>
       <c r="F84" s="3" t="s">
         <v>16</v>
       </c>
       <c r="G84" s="3" t="s">
-        <v>644</v>
+        <v>649</v>
       </c>
       <c r="H84" s="4" t="s">
-        <v>645</v>
+        <v>650</v>
       </c>
       <c r="I84" s="4" t="s">
-        <v>646</v>
+        <v>651</v>
       </c>
       <c r="J84" s="3" t="s">
-        <v>647</v>
+        <v>652</v>
       </c>
       <c r="K84" s="3" t="s">
         <v>48</v>
       </c>
       <c r="L84" s="3" t="s">
-        <v>648</v>
+        <v>653</v>
       </c>
     </row>
     <row r="85" ht="22.5" customHeight="1">
       <c r="A85" s="5"/>
       <c r="B85" s="3" t="s">
-        <v>649</v>
+        <v>654</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="D85" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>651</v>
+        <v>656</v>
       </c>
       <c r="F85" s="3" t="s">
         <v>26</v>
@@ -5534,89 +5572,122 @@
       <c r="G85" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="H85" s="6">
-        <v>26673.0</v>
+      <c r="H85" s="4" t="s">
+        <v>657</v>
       </c>
       <c r="I85" s="4" t="s">
-        <v>652</v>
+        <v>658</v>
       </c>
       <c r="J85" s="3" t="s">
-        <v>653</v>
+        <v>659</v>
       </c>
       <c r="K85" s="3" t="s">
         <v>21</v>
       </c>
       <c r="L85" s="3" t="s">
-        <v>654</v>
+        <v>660</v>
       </c>
     </row>
     <row r="86" ht="22.5" customHeight="1">
       <c r="A86" s="5"/>
       <c r="B86" s="3" t="s">
-        <v>655</v>
+        <v>661</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>656</v>
+        <v>662</v>
       </c>
       <c r="D86" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E86" s="6">
-        <v>32113.0</v>
+      <c r="E86" s="4" t="s">
+        <v>663</v>
       </c>
       <c r="F86" s="3" t="s">
         <v>16</v>
       </c>
       <c r="G86" s="3" t="s">
-        <v>657</v>
-      </c>
-      <c r="H86" s="6">
-        <v>42161.0</v>
+        <v>664</v>
+      </c>
+      <c r="H86" s="4" t="s">
+        <v>665</v>
       </c>
       <c r="I86" s="4" t="s">
-        <v>658</v>
+        <v>666</v>
       </c>
       <c r="J86" s="3" t="s">
-        <v>659</v>
+        <v>667</v>
       </c>
       <c r="K86" s="3" t="s">
         <v>48</v>
       </c>
       <c r="L86" s="3" t="s">
-        <v>660</v>
+        <v>668</v>
       </c>
     </row>
     <row r="87" ht="22.5" customHeight="1">
       <c r="A87" s="5"/>
       <c r="B87" s="3" t="s">
-        <v>661</v>
+        <v>669</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>662</v>
+        <v>670</v>
       </c>
       <c r="D87" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="E87" s="3" t="s">
-        <v>663</v>
+      <c r="E87" s="4" t="s">
+        <v>671</v>
       </c>
       <c r="F87" s="3" t="s">
         <v>16</v>
       </c>
       <c r="G87" s="3" t="s">
-        <v>664</v>
+        <v>611</v>
       </c>
       <c r="I87" s="4" t="s">
-        <v>665</v>
+        <v>672</v>
       </c>
       <c r="J87" s="3" t="s">
-        <v>666</v>
+        <v>673</v>
       </c>
       <c r="K87" s="3" t="s">
         <v>21</v>
       </c>
       <c r="L87" s="3" t="s">
-        <v>667</v>
+        <v>674</v>
+      </c>
+    </row>
+    <row r="88" ht="22.5" customHeight="1">
+      <c r="A88" s="5"/>
+      <c r="B88" s="3" t="s">
+        <v>675</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>676</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="E88" s="3" t="s">
+        <v>677</v>
+      </c>
+      <c r="F88" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G88" s="3" t="s">
+        <v>678</v>
+      </c>
+      <c r="I88" s="4" t="s">
+        <v>679</v>
+      </c>
+      <c r="J88" s="3" t="s">
+        <v>680</v>
+      </c>
+      <c r="K88" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L88" s="3" t="s">
+        <v>681</v>
       </c>
     </row>
   </sheetData>
